--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41679409-73DE-4C6B-BA99-5B7AC41E68D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CB00F6-0C68-451C-B986-0EAD169BB22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capa" sheetId="19" r:id="rId1"/>
@@ -347,7 +347,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -356,13 +365,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -374,14 +377,36 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -678,10 +703,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="9">
@@ -689,8 +714,8 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="9">
@@ -698,8 +723,8 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="9">
@@ -707,10 +732,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="9">
@@ -718,8 +743,8 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="9">
@@ -727,8 +752,8 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="19" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="9">
@@ -736,19 +761,19 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="9">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="19" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="9">
@@ -756,8 +781,8 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="9">
@@ -765,19 +790,19 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="9">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="19" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="9">
@@ -785,8 +810,8 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="19" t="s">
+      <c r="A13" s="13"/>
+      <c r="B13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="9">
@@ -794,19 +819,19 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="9">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="9">
@@ -814,8 +839,8 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="9">
@@ -823,10 +848,10 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="9">
@@ -834,8 +859,8 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="19" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="9">
@@ -843,8 +868,8 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="19" t="s">
+      <c r="A19" s="13"/>
+      <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="9">
@@ -852,62 +877,67 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="19" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
-      <c r="B22" s="19" t="s">
+      <c r="A22" s="13"/>
+      <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="9"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="19" t="s">
+      <c r="A24" s="12"/>
+      <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="B25" s="19" t="s">
+      <c r="A25" s="13"/>
+      <c r="B25" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
   </mergeCells>
+  <conditionalFormatting sqref="C2:C25">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>19</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -943,767 +973,767 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="12" t="e">
+      <c r="E2" s="15" t="e">
         <f>AVERAGE(D2:D21)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="12"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="12"/>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="12"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="12"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="12"/>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="12"/>
+      <c r="E8" s="15"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="12"/>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="12"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="12"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="12"/>
+      <c r="E12" s="15"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="1">
         <v>12</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="12"/>
+      <c r="E13" s="15"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1">
         <v>13</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="12"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1">
         <v>14</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="12"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1">
         <v>15</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="12"/>
+      <c r="E16" s="15"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="1">
         <v>16</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="12"/>
+      <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1">
         <v>17</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="12"/>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="1">
         <v>18</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="12"/>
+      <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="1">
         <v>19</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="12"/>
+      <c r="E20" s="15"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="1">
         <v>20</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="12"/>
+      <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="12" t="e">
+      <c r="E22" s="15" t="e">
         <f>AVERAGE(D22:D41)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>2</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="12"/>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
       <c r="C24" s="1">
         <v>3</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="12"/>
+      <c r="E24" s="15"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="1">
         <v>4</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="12"/>
+      <c r="E25" s="15"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1">
         <v>5</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="12"/>
+      <c r="E26" s="15"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="1">
         <v>6</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="12"/>
+      <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>7</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="12"/>
+      <c r="E28" s="15"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>8</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="12"/>
+      <c r="E29" s="15"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>9</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="12"/>
+      <c r="E30" s="15"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>10</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="12"/>
+      <c r="E31" s="15"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>11</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="12"/>
+      <c r="E32" s="15"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>12</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="12"/>
+      <c r="E33" s="15"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1">
         <v>13</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="12"/>
+      <c r="E34" s="15"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="1">
         <v>14</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="12"/>
+      <c r="E35" s="15"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
       <c r="C36" s="1">
         <v>15</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="12"/>
+      <c r="E36" s="15"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="1">
         <v>16</v>
       </c>
       <c r="D37" s="3"/>
-      <c r="E37" s="12"/>
+      <c r="E37" s="15"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
       <c r="C38" s="1">
         <v>17</v>
       </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="12"/>
+      <c r="E38" s="15"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
       <c r="C39" s="1">
         <v>18</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="12"/>
+      <c r="E39" s="15"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
       <c r="C40" s="1">
         <v>19</v>
       </c>
       <c r="D40" s="3"/>
-      <c r="E40" s="12"/>
+      <c r="E40" s="15"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
       <c r="C41" s="1">
         <v>20</v>
       </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="12"/>
+      <c r="E41" s="15"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="12" t="e">
+      <c r="E42" s="15" t="e">
         <f>AVERAGE(D42:D61)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
       <c r="C43" s="1">
         <v>2</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="12"/>
+      <c r="E43" s="15"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
       <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="D44" s="3"/>
-      <c r="E44" s="12"/>
+      <c r="E44" s="15"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
       <c r="C45" s="1">
         <v>4</v>
       </c>
       <c r="D45" s="3"/>
-      <c r="E45" s="12"/>
+      <c r="E45" s="15"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
       <c r="C46" s="1">
         <v>5</v>
       </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="12"/>
+      <c r="E46" s="15"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
       <c r="C47" s="1">
         <v>6</v>
       </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="12"/>
+      <c r="E47" s="15"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
       <c r="C48" s="1">
         <v>7</v>
       </c>
       <c r="D48" s="3"/>
-      <c r="E48" s="12"/>
+      <c r="E48" s="15"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
       <c r="C49" s="1">
         <v>8</v>
       </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="12"/>
+      <c r="E49" s="15"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
       <c r="C50" s="1">
         <v>9</v>
       </c>
       <c r="D50" s="3"/>
-      <c r="E50" s="12"/>
+      <c r="E50" s="15"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
       <c r="C51" s="1">
         <v>10</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="12"/>
+      <c r="E51" s="15"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
       <c r="C52" s="1">
         <v>11</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="12"/>
+      <c r="E52" s="15"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
       <c r="C53" s="1">
         <v>12</v>
       </c>
       <c r="D53" s="3"/>
-      <c r="E53" s="12"/>
+      <c r="E53" s="15"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
       <c r="C54" s="1">
         <v>13</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="12"/>
+      <c r="E54" s="15"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
       <c r="C55" s="1">
         <v>14</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="12"/>
+      <c r="E55" s="15"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
       <c r="C56" s="1">
         <v>15</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="12"/>
+      <c r="E56" s="15"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
       <c r="C57" s="1">
         <v>16</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="12"/>
+      <c r="E57" s="15"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
       <c r="C58" s="1">
         <v>17</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="12"/>
+      <c r="E58" s="15"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
       <c r="C59" s="1">
         <v>18</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="12"/>
+      <c r="E59" s="15"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
       <c r="C60" s="1">
         <v>19</v>
       </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="12"/>
+      <c r="E60" s="15"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
       <c r="C61" s="1">
         <v>20</v>
       </c>
       <c r="D61" s="3"/>
-      <c r="E61" s="12"/>
+      <c r="E61" s="15"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
       <c r="D62" s="3"/>
-      <c r="E62" s="12" t="e">
+      <c r="E62" s="15" t="e">
         <f>AVERAGE(D62:D81)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
       <c r="C63" s="1">
         <v>2</v>
       </c>
       <c r="D63" s="3"/>
-      <c r="E63" s="12"/>
+      <c r="E63" s="15"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
       <c r="C64" s="1">
         <v>3</v>
       </c>
       <c r="D64" s="3"/>
-      <c r="E64" s="12"/>
+      <c r="E64" s="15"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
       <c r="C65" s="1">
         <v>4</v>
       </c>
       <c r="D65" s="3"/>
-      <c r="E65" s="12"/>
+      <c r="E65" s="15"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
       <c r="C66" s="1">
         <v>5</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="12"/>
+      <c r="E66" s="15"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
       <c r="C67" s="1">
         <v>6</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="12"/>
+      <c r="E67" s="15"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
       <c r="C68" s="1">
         <v>7</v>
       </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="12"/>
+      <c r="E68" s="15"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
       <c r="C69" s="1">
         <v>8</v>
       </c>
       <c r="D69" s="3"/>
-      <c r="E69" s="12"/>
+      <c r="E69" s="15"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
       <c r="C70" s="1">
         <v>9</v>
       </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="12"/>
+      <c r="E70" s="15"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
       <c r="C71" s="1">
         <v>10</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="12"/>
+      <c r="E71" s="15"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
+      <c r="A72" s="14"/>
+      <c r="B72" s="14"/>
       <c r="C72" s="1">
         <v>11</v>
       </c>
       <c r="D72" s="3"/>
-      <c r="E72" s="12"/>
+      <c r="E72" s="15"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
+      <c r="A73" s="14"/>
+      <c r="B73" s="14"/>
       <c r="C73" s="1">
         <v>12</v>
       </c>
       <c r="D73" s="3"/>
-      <c r="E73" s="12"/>
+      <c r="E73" s="15"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
       <c r="C74" s="1">
         <v>13</v>
       </c>
       <c r="D74" s="3"/>
-      <c r="E74" s="12"/>
+      <c r="E74" s="15"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
+      <c r="A75" s="14"/>
+      <c r="B75" s="14"/>
       <c r="C75" s="1">
         <v>14</v>
       </c>
       <c r="D75" s="3"/>
-      <c r="E75" s="12"/>
+      <c r="E75" s="15"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
       <c r="C76" s="1">
         <v>15</v>
       </c>
       <c r="D76" s="3"/>
-      <c r="E76" s="12"/>
+      <c r="E76" s="15"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
       <c r="C77" s="1">
         <v>16</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="12"/>
+      <c r="E77" s="15"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
       <c r="C78" s="1">
         <v>17</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="12"/>
+      <c r="E78" s="15"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
       <c r="C79" s="1">
         <v>18</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="12"/>
+      <c r="E79" s="15"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
       <c r="C80" s="1">
         <v>19</v>
       </c>
       <c r="D80" s="3"/>
-      <c r="E80" s="12"/>
+      <c r="E80" s="15"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="11"/>
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
       <c r="C81" s="1">
         <v>20</v>
       </c>
       <c r="D81" s="3"/>
-      <c r="E81" s="12"/>
+      <c r="E81" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A2:A21"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A2:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1739,10 +1769,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1751,124 +1781,124 @@
       <c r="D2" s="3">
         <v>1.22740707443255E-3</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="15">
         <f>AVERAGE(D2:D12)</f>
         <v>1.3405988398128117E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.21923057588587E-3</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.2107251197056299E-3</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>1.14432918115938E-3</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>1.1901786885313401E-3</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -1877,124 +1907,124 @@
       <c r="D13" s="3">
         <v>1.76494351019696E-4</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="17">
         <f>AVERAGE(D13:D23)</f>
         <v>4.6044642516324585E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="12"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="17"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>1.7489087688418899E-4</v>
       </c>
-      <c r="E15" s="17"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="12"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="17"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="12"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>4.5224030226177498E-4</v>
       </c>
-      <c r="E17" s="17"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="12"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>3.25042909349475E-4</v>
       </c>
-      <c r="E18" s="17"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="12"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="12"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>4.0296400000000003E-5</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="17"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="17"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="15"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="13"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="18"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2003,118 +2033,118 @@
       <c r="D24" s="3">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <f>AVERAGE(D24:D33)</f>
         <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="14"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="14"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2161,263 +2191,263 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="12">
+      <c r="E2" s="15">
         <f>AVERAGE(D2:D15)</f>
         <v>1.4591194330376932E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="11"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="1"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="11"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1">
         <v>11</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="13" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="16">
+      <c r="E16" s="17">
         <f>AVERAGE(D16:D26)</f>
         <v>6.4932430621342815E-4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="12"/>
       <c r="C17" s="1">
         <v>2</v>
       </c>
       <c r="D17" s="7">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E17" s="17"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="12"/>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="17"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="12"/>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="7">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="12"/>
       <c r="C20" s="1">
         <v>5</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="12"/>
       <c r="C21" s="1">
         <v>6</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="17"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="12"/>
       <c r="C22" s="1">
         <v>7</v>
       </c>
       <c r="D22" s="7">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E22" s="17"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="12"/>
       <c r="C23" s="1">
         <v>8</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="17"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="14"/>
+      <c r="A24" s="14"/>
+      <c r="B24" s="12"/>
       <c r="C24" s="1">
         <v>9</v>
       </c>
       <c r="D24" s="7">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E24" s="17"/>
+      <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="12"/>
       <c r="C25" s="1">
         <v>10</v>
       </c>
       <c r="D25" s="7">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E25" s="17"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="15"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="13"/>
       <c r="C26" s="1">
         <v>11</v>
       </c>
       <c r="D26" s="7">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E26" s="18"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11" t="s">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="1">
@@ -2426,162 +2456,162 @@
       <c r="D27" s="6">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="15">
         <f>AVERAGE(D27:D40)</f>
         <v>2.1330410891497666E-4</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>2</v>
       </c>
       <c r="D28" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>3</v>
       </c>
       <c r="D29" s="6">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>4</v>
       </c>
       <c r="D30" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>5</v>
       </c>
       <c r="D31" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>6</v>
       </c>
       <c r="D32" s="6">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>7</v>
       </c>
       <c r="D33" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
       <c r="C34" s="1">
         <v>8</v>
       </c>
       <c r="D34" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E34" s="11"/>
+      <c r="E34" s="14"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
       <c r="C35" s="1">
         <v>9</v>
       </c>
       <c r="D35" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E35" s="11"/>
+      <c r="E35" s="14"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
       <c r="C36" s="1">
         <v>10</v>
       </c>
       <c r="D36" s="6">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E36" s="11"/>
+      <c r="E36" s="14"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="1">
         <v>11</v>
       </c>
       <c r="D37" s="3">
         <v>3.3565148161274601E-4</v>
       </c>
-      <c r="E37" s="11"/>
+      <c r="E37" s="14"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
       <c r="C38" s="1">
         <v>12</v>
       </c>
       <c r="D38" s="6">
         <v>1.2738871373007399E-4</v>
       </c>
-      <c r="E38" s="11"/>
+      <c r="E38" s="14"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
       <c r="C39" s="1">
         <v>13</v>
       </c>
       <c r="D39" s="3">
         <v>3.4164426510307702E-4</v>
       </c>
-      <c r="E39" s="11"/>
+      <c r="E39" s="14"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
       <c r="C40" s="1">
         <v>14</v>
       </c>
       <c r="D40" s="6">
         <v>1.78335406733681E-4</v>
       </c>
-      <c r="E40" s="11"/>
+      <c r="E40" s="14"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2628,10 +2658,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -2640,124 +2670,124 @@
       <c r="D2" s="3">
         <v>6.8494550335423199E-3</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="15">
         <f>AVERAGE(D2:D12)</f>
         <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>6.9163642363323698E-3</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>7.1247468487415202E-3</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>6.44864466466859E-3</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>6.8408648336931201E-3</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -2766,124 +2796,124 @@
       <c r="D13" s="3">
         <v>4.4059430113216501E-3</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <f>AVERAGE(D13:D23)</f>
         <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>4.6542086132795998E-3</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>5.2386490268761304E-3</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>4.5414210107642796E-3</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>3.38376634582825E-3</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2892,118 +2922,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="14"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="14"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3050,242 +3080,242 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="12">
+      <c r="E2" s="15">
         <f>AVERAGE(D2:D12)</f>
         <v>7.5204771451239999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="11"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <f>AVERAGE(D13:D23)</f>
         <v>6.5940540634390936E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="7">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="7">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="11"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="7">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="11"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="7">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="7">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="7">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -3294,118 +3324,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="6">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="14"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="6">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="14"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="6">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="6">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="6">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3452,10 +3482,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -3464,124 +3494,124 @@
       <c r="D2" s="3">
         <v>2.81366470929909E-3</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="15">
         <f>AVERAGE(D2:D12)</f>
         <v>2.8589718670011272E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>2.9086299843656201E-3</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>2.8725109233065098E-3</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>2.7472220866062401E-3</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>2.8395079487722498E-3</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>2.9094927500167801E-3</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>2.9300338678111201E-3</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>2.8954508177678399E-3</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>2.86130290885414E-3</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>2.8834394576333199E-3</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>2.7874350825794901E-3</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -3590,124 +3620,124 @@
       <c r="D13" s="3">
         <v>2.4381599990933901E-3</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <f>AVERAGE(D13:D23)</f>
         <v>2.6530523100631071E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>2.6282434237133502E-3</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>2.3461147455381701E-3</v>
       </c>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>2.7524372879068298E-3</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>3.2472745789499402E-3</v>
       </c>
-      <c r="E17" s="11"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>2.5237854282296E-3</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>2.9887873260404599E-3</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>2.06526349558706E-3</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>2.6816447983030599E-3</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>2.7565596821078398E-3</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>2.7553046452244798E-3</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -3716,121 +3746,121 @@
       <c r="D24" s="3">
         <v>3.3099004965032601E-3</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <f>AVERAGE(D24:D33)</f>
         <v>2.4948066730810809E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>2.0223762558382102E-3</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>2.48460504443907E-3</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="14"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.1925517311301699E-3</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="14"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>2.0210547846704601E-3</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>2.32727791187156E-3</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3527282363668498E-3</v>
       </c>
-      <c r="E30" s="11"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.00939520752292E-3</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>2.9226176336739399E-3</v>
       </c>
-      <c r="E32" s="11"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="14"/>
       <c r="G33" s="4">
         <v>2.3055594287943698E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3877,354 +3907,354 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="12">
+      <c r="E2" s="15">
         <f>AVERAGE(D2:D12)</f>
         <v>2.8999263001501983E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>2.9086299843656201E-3</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>2.8725109233065098E-3</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>2.9094927500167801E-3</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>2.9300338678111201E-3</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>2.8954508177678399E-3</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>2.8834394576333199E-3</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="11"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="12">
+      <c r="E13" s="15">
         <f>AVERAGE(D13:D23)</f>
         <v>2.6829958775808596E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="7">
         <v>2.6282434237133502E-3</v>
       </c>
-      <c r="E14" s="11"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="11"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="7">
         <v>2.7524372879068298E-3</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="7">
         <v>2.5237854282296E-3</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="11"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="11"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="7">
         <v>2.6816447983030599E-3</v>
       </c>
-      <c r="E21" s="11"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="7">
         <v>2.7565596821078398E-3</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="7">
         <v>2.7553046452244798E-3</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="14"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="12">
+      <c r="E24" s="15">
         <f>AVERAGE(D24:D33)</f>
         <v>2.1463692199712816E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="6">
         <v>2.0223762558382102E-3</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="11"/>
+      <c r="E26" s="14"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="6">
         <v>2.1925517311301699E-3</v>
       </c>
-      <c r="E27" s="11"/>
+      <c r="E27" s="14"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="6">
         <v>2.0210547846704601E-3</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="6">
         <v>2.32727791187156E-3</v>
       </c>
-      <c r="E29" s="11"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="11"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="6">
         <v>2.00939520752292E-3</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="11"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="11"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CB00F6-0C68-451C-B986-0EAD169BB22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB8761B-D324-408B-8351-E259A33B1CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,8 +40,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Rafael Vargas</author>
+  </authors>
+  <commentList>
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{B9BDC6F8-C697-4F46-900C-EAE4DC4AAA56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Rafael Vargas:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Já foram selecionados os melhores</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{FA12611E-7015-4E16-A9ED-28719A83CF63}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Rafael Vargas:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Já foram selecionados os melhores</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
   <si>
     <t>Estratégia</t>
   </si>
@@ -180,6 +238,9 @@
   <si>
     <t>FedDEEV</t>
   </si>
+  <si>
+    <t>OK</t>
+  </si>
 </sst>
 </file>
 
@@ -188,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000000000000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,8 +286,35 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -260,6 +348,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -328,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -377,11 +471,20 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -389,20 +492,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -681,17 +770,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D004F6-8B6A-4DFD-8AB9-B21C335488C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D004F6-8B6A-4DFD-8AB9-B21C335488C7}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="20"/>
     <col min="5" max="5" width="8.88671875" style="4"/>
     <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -702,7 +792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
@@ -713,7 +803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="12"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
@@ -722,7 +812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="13"/>
       <c r="B4" s="10" t="s">
         <v>17</v>
@@ -731,7 +821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>14</v>
       </c>
@@ -742,7 +832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="10" t="s">
         <v>16</v>
@@ -751,7 +841,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7" s="10" t="s">
         <v>17</v>
@@ -760,7 +850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>21</v>
       </c>
@@ -770,8 +860,11 @@
       <c r="C8" s="9">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="10" t="s">
         <v>16</v>
@@ -779,8 +872,9 @@
       <c r="C9" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="10" t="s">
         <v>17</v>
@@ -789,7 +883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
@@ -800,16 +894,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="22">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="10" t="s">
         <v>17</v>
@@ -818,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>23</v>
       </c>
@@ -829,16 +926,19 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
       <c r="B15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="22">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" s="21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>17</v>
@@ -847,7 +947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>18</v>
       </c>
@@ -858,7 +958,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
       <c r="B18" s="10" t="s">
         <v>16</v>
@@ -867,7 +967,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="10" t="s">
         <v>17</v>
@@ -876,7 +976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>19</v>
       </c>
@@ -885,21 +985,24 @@
       </c>
       <c r="C20" s="9"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="9"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>20</v>
       </c>
@@ -908,19 +1011,21 @@
       </c>
       <c r="C23" s="9"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="9"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="9">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -940,6 +1045,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1722,18 +1828,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
     <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB8761B-D324-408B-8351-E259A33B1CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D22560-9A40-4BF3-8B11-9D380A38383A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="29">
   <si>
     <t>Estratégia</t>
   </si>
@@ -240,6 +240,12 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Dell</t>
+  </si>
+  <si>
+    <t>Acer</t>
   </si>
 </sst>
 </file>
@@ -444,6 +450,15 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -469,15 +484,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -776,12 +782,12 @@
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="20"/>
+    <col min="4" max="4" width="8.88671875" style="11"/>
     <col min="5" max="5" width="8.88671875" style="4"/>
     <col min="6" max="6" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -792,8 +798,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -803,8 +809,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
@@ -812,17 +818,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="11">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -832,8 +844,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
       <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
@@ -841,8 +853,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -850,8 +862,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="10" t="s">
@@ -860,12 +872,15 @@
       <c r="C8" s="9">
         <v>18</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="11">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
+      <c r="E8" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="15"/>
       <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
@@ -874,8 +889,8 @@
       </c>
       <c r="D9" s="4"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
       <c r="B10" s="10" t="s">
         <v>17</v>
       </c>
@@ -883,8 +898,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -894,20 +909,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
       <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="13">
         <v>10</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
       <c r="B13" s="10" t="s">
         <v>17</v>
       </c>
@@ -915,8 +930,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="10" t="s">
@@ -926,20 +941,20 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="15"/>
       <c r="B15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="13">
         <v>10</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="16"/>
       <c r="B16" s="10" t="s">
         <v>17</v>
       </c>
@@ -947,8 +962,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="10" t="s">
@@ -958,8 +973,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
@@ -967,8 +982,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="16"/>
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
@@ -976,8 +991,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
@@ -985,25 +1000,24 @@
       </c>
       <c r="C20" s="9"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
       <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="9"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="16"/>
       <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="20">
+      <c r="C22" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -1011,15 +1025,15 @@
       </c>
       <c r="C23" s="9"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
       <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="9"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
       <c r="B25" s="10" t="s">
         <v>17</v>
       </c>
@@ -1079,767 +1093,767 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="15" t="e">
+      <c r="E2" s="18" t="e">
         <f>AVERAGE(D2:D21)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="15"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="15"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="15"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="15"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="15"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="15"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="15"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="15"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="15"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="15"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="1">
         <v>12</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="15"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1">
         <v>13</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="15"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1">
         <v>14</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="15"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1">
         <v>15</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="15"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1">
         <v>16</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="15"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1">
         <v>17</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="15"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="1">
         <v>18</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1">
         <v>19</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="15"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="1">
         <v>20</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="15"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="17" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="15" t="e">
+      <c r="E22" s="18" t="e">
         <f>AVERAGE(D22:D41)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1">
         <v>2</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="15"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
       <c r="C24" s="1">
         <v>3</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="15"/>
+      <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1">
         <v>4</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="15"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>5</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="15"/>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="1">
         <v>6</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="15"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>7</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="15"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>8</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="15"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>9</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="15"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>10</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="15"/>
+      <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>11</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="15"/>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>12</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="15"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="1">
         <v>13</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="15"/>
+      <c r="E34" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
       <c r="C35" s="1">
         <v>14</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="15"/>
+      <c r="E35" s="18"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="1">
         <v>15</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="15"/>
+      <c r="E36" s="18"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
       <c r="C37" s="1">
         <v>16</v>
       </c>
       <c r="D37" s="3"/>
-      <c r="E37" s="15"/>
+      <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
       <c r="C38" s="1">
         <v>17</v>
       </c>
       <c r="D38" s="3"/>
-      <c r="E38" s="15"/>
+      <c r="E38" s="18"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
       <c r="C39" s="1">
         <v>18</v>
       </c>
       <c r="D39" s="3"/>
-      <c r="E39" s="15"/>
+      <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
       <c r="C40" s="1">
         <v>19</v>
       </c>
       <c r="D40" s="3"/>
-      <c r="E40" s="15"/>
+      <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
       <c r="C41" s="1">
         <v>20</v>
       </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="15"/>
+      <c r="E41" s="18"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="17" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="15" t="e">
+      <c r="E42" s="18" t="e">
         <f>AVERAGE(D42:D61)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
       <c r="C43" s="1">
         <v>2</v>
       </c>
       <c r="D43" s="3"/>
-      <c r="E43" s="15"/>
+      <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
       <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="D44" s="3"/>
-      <c r="E44" s="15"/>
+      <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
       <c r="C45" s="1">
         <v>4</v>
       </c>
       <c r="D45" s="3"/>
-      <c r="E45" s="15"/>
+      <c r="E45" s="18"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
       <c r="C46" s="1">
         <v>5</v>
       </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="15"/>
+      <c r="E46" s="18"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
       <c r="C47" s="1">
         <v>6</v>
       </c>
       <c r="D47" s="3"/>
-      <c r="E47" s="15"/>
+      <c r="E47" s="18"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="1">
         <v>7</v>
       </c>
       <c r="D48" s="3"/>
-      <c r="E48" s="15"/>
+      <c r="E48" s="18"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
       <c r="C49" s="1">
         <v>8</v>
       </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="15"/>
+      <c r="E49" s="18"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
       <c r="C50" s="1">
         <v>9</v>
       </c>
       <c r="D50" s="3"/>
-      <c r="E50" s="15"/>
+      <c r="E50" s="18"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
       <c r="C51" s="1">
         <v>10</v>
       </c>
       <c r="D51" s="3"/>
-      <c r="E51" s="15"/>
+      <c r="E51" s="18"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="14"/>
-      <c r="B52" s="14"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
       <c r="C52" s="1">
         <v>11</v>
       </c>
       <c r="D52" s="3"/>
-      <c r="E52" s="15"/>
+      <c r="E52" s="18"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
       <c r="C53" s="1">
         <v>12</v>
       </c>
       <c r="D53" s="3"/>
-      <c r="E53" s="15"/>
+      <c r="E53" s="18"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
       <c r="C54" s="1">
         <v>13</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="15"/>
+      <c r="E54" s="18"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
       <c r="C55" s="1">
         <v>14</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="15"/>
+      <c r="E55" s="18"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
       <c r="C56" s="1">
         <v>15</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="15"/>
+      <c r="E56" s="18"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
       <c r="C57" s="1">
         <v>16</v>
       </c>
       <c r="D57" s="3"/>
-      <c r="E57" s="15"/>
+      <c r="E57" s="18"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
       <c r="C58" s="1">
         <v>17</v>
       </c>
       <c r="D58" s="3"/>
-      <c r="E58" s="15"/>
+      <c r="E58" s="18"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
       <c r="C59" s="1">
         <v>18</v>
       </c>
       <c r="D59" s="3"/>
-      <c r="E59" s="15"/>
+      <c r="E59" s="18"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
       <c r="C60" s="1">
         <v>19</v>
       </c>
       <c r="D60" s="3"/>
-      <c r="E60" s="15"/>
+      <c r="E60" s="18"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
       <c r="C61" s="1">
         <v>20</v>
       </c>
       <c r="D61" s="3"/>
-      <c r="E61" s="15"/>
+      <c r="E61" s="18"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
+      <c r="A62" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="17" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
       <c r="D62" s="3"/>
-      <c r="E62" s="15" t="e">
+      <c r="E62" s="18" t="e">
         <f>AVERAGE(D62:D81)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="14"/>
-      <c r="B63" s="14"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
       <c r="C63" s="1">
         <v>2</v>
       </c>
       <c r="D63" s="3"/>
-      <c r="E63" s="15"/>
+      <c r="E63" s="18"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
       <c r="C64" s="1">
         <v>3</v>
       </c>
       <c r="D64" s="3"/>
-      <c r="E64" s="15"/>
+      <c r="E64" s="18"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
       <c r="C65" s="1">
         <v>4</v>
       </c>
       <c r="D65" s="3"/>
-      <c r="E65" s="15"/>
+      <c r="E65" s="18"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
       <c r="C66" s="1">
         <v>5</v>
       </c>
       <c r="D66" s="3"/>
-      <c r="E66" s="15"/>
+      <c r="E66" s="18"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="14"/>
-      <c r="B67" s="14"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
       <c r="C67" s="1">
         <v>6</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="15"/>
+      <c r="E67" s="18"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="14"/>
-      <c r="B68" s="14"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
       <c r="C68" s="1">
         <v>7</v>
       </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="15"/>
+      <c r="E68" s="18"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
       <c r="C69" s="1">
         <v>8</v>
       </c>
       <c r="D69" s="3"/>
-      <c r="E69" s="15"/>
+      <c r="E69" s="18"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
       <c r="C70" s="1">
         <v>9</v>
       </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="15"/>
+      <c r="E70" s="18"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="14"/>
-      <c r="B71" s="14"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
       <c r="C71" s="1">
         <v>10</v>
       </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="15"/>
+      <c r="E71" s="18"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="14"/>
-      <c r="B72" s="14"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
       <c r="C72" s="1">
         <v>11</v>
       </c>
       <c r="D72" s="3"/>
-      <c r="E72" s="15"/>
+      <c r="E72" s="18"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="14"/>
-      <c r="B73" s="14"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
       <c r="C73" s="1">
         <v>12</v>
       </c>
       <c r="D73" s="3"/>
-      <c r="E73" s="15"/>
+      <c r="E73" s="18"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="14"/>
-      <c r="B74" s="14"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
       <c r="C74" s="1">
         <v>13</v>
       </c>
       <c r="D74" s="3"/>
-      <c r="E74" s="15"/>
+      <c r="E74" s="18"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="14"/>
-      <c r="B75" s="14"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
       <c r="C75" s="1">
         <v>14</v>
       </c>
       <c r="D75" s="3"/>
-      <c r="E75" s="15"/>
+      <c r="E75" s="18"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="14"/>
-      <c r="B76" s="14"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
       <c r="C76" s="1">
         <v>15</v>
       </c>
       <c r="D76" s="3"/>
-      <c r="E76" s="15"/>
+      <c r="E76" s="18"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
       <c r="C77" s="1">
         <v>16</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="15"/>
+      <c r="E77" s="18"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="14"/>
-      <c r="B78" s="14"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="17"/>
       <c r="C78" s="1">
         <v>17</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="15"/>
+      <c r="E78" s="18"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="14"/>
-      <c r="B79" s="14"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="17"/>
       <c r="C79" s="1">
         <v>18</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="15"/>
+      <c r="E79" s="18"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="14"/>
-      <c r="B80" s="14"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="17"/>
       <c r="C80" s="1">
         <v>19</v>
       </c>
       <c r="D80" s="3"/>
-      <c r="E80" s="15"/>
+      <c r="E80" s="18"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="14"/>
-      <c r="B81" s="14"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="17"/>
       <c r="C81" s="1">
         <v>20</v>
       </c>
       <c r="D81" s="3"/>
-      <c r="E81" s="15"/>
+      <c r="E81" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A2:A21"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A2:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1875,10 +1889,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1887,124 +1901,124 @@
       <c r="D2" s="3">
         <v>1.22740707443255E-3</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D12)</f>
         <v>1.3405988398128117E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.21923057588587E-3</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.2107251197056299E-3</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>1.14432918115938E-3</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>1.1901786885313401E-3</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -2013,124 +2027,124 @@
       <c r="D13" s="3">
         <v>1.76494351019696E-4</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="20">
         <f>AVERAGE(D13:D23)</f>
         <v>4.6044642516324585E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="18"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="12"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>1.7489087688418899E-4</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>4.5224030226177498E-4</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="12"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>3.25042909349475E-4</v>
       </c>
-      <c r="E18" s="18"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="12"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="12"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>4.0296400000000003E-5</v>
       </c>
-      <c r="E20" s="18"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="12"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="18"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="12"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="18"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="13"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="19"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2139,118 +2153,118 @@
       <c r="D24" s="3">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="18">
         <f>AVERAGE(D24:D33)</f>
         <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2297,263 +2311,263 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="15">
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D15)</f>
         <v>1.4591194330376932E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="14"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="14"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="14"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
       <c r="C13" s="1"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="14"/>
+      <c r="E13" s="17"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="14"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1">
         <v>11</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="17"/>
+      <c r="B16" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="17">
+      <c r="E16" s="20">
         <f>AVERAGE(D16:D26)</f>
         <v>6.4932430621342815E-4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="1">
         <v>2</v>
       </c>
       <c r="D17" s="7">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="12"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="18"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="12"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="7">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="12"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="1">
         <v>5</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="18"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="12"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="1">
         <v>6</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="18"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="12"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="1">
         <v>7</v>
       </c>
       <c r="D22" s="7">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E22" s="18"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="12"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="1">
         <v>8</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="18"/>
+      <c r="E23" s="21"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="12"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="1">
         <v>9</v>
       </c>
       <c r="D24" s="7">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="12"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="1">
         <v>10</v>
       </c>
       <c r="D25" s="7">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E25" s="18"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="13"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="1">
         <v>11</v>
       </c>
       <c r="D26" s="7">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E26" s="19"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14" t="s">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="1">
@@ -2562,162 +2576,162 @@
       <c r="D27" s="6">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="18">
         <f>AVERAGE(D27:D40)</f>
         <v>2.1330410891497666E-4</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>2</v>
       </c>
       <c r="D28" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>3</v>
       </c>
       <c r="D29" s="6">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>4</v>
       </c>
       <c r="D30" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>5</v>
       </c>
       <c r="D31" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>6</v>
       </c>
       <c r="D32" s="6">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>7</v>
       </c>
       <c r="D33" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
       <c r="C34" s="1">
         <v>8</v>
       </c>
       <c r="D34" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E34" s="14"/>
+      <c r="E34" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
       <c r="C35" s="1">
         <v>9</v>
       </c>
       <c r="D35" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E35" s="14"/>
+      <c r="E35" s="17"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
       <c r="C36" s="1">
         <v>10</v>
       </c>
       <c r="D36" s="6">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E36" s="14"/>
+      <c r="E36" s="17"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
       <c r="C37" s="1">
         <v>11</v>
       </c>
       <c r="D37" s="3">
         <v>3.3565148161274601E-4</v>
       </c>
-      <c r="E37" s="14"/>
+      <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
       <c r="C38" s="1">
         <v>12</v>
       </c>
       <c r="D38" s="6">
         <v>1.2738871373007399E-4</v>
       </c>
-      <c r="E38" s="14"/>
+      <c r="E38" s="17"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
       <c r="C39" s="1">
         <v>13</v>
       </c>
       <c r="D39" s="3">
         <v>3.4164426510307702E-4</v>
       </c>
-      <c r="E39" s="14"/>
+      <c r="E39" s="17"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
       <c r="C40" s="1">
         <v>14</v>
       </c>
       <c r="D40" s="6">
         <v>1.78335406733681E-4</v>
       </c>
-      <c r="E40" s="14"/>
+      <c r="E40" s="17"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2764,10 +2778,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -2776,124 +2790,124 @@
       <c r="D2" s="3">
         <v>6.8494550335423199E-3</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D12)</f>
         <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>6.9163642363323698E-3</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>7.1247468487415202E-3</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>6.44864466466859E-3</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>6.8408648336931201E-3</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -2902,124 +2916,124 @@
       <c r="D13" s="3">
         <v>4.4059430113216501E-3</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="18">
         <f>AVERAGE(D13:D23)</f>
         <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>4.6542086132795998E-3</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>5.2386490268761304E-3</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>4.5414210107642796E-3</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>3.38376634582825E-3</v>
       </c>
-      <c r="E20" s="14"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -3028,118 +3042,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="18">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3186,242 +3200,242 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="15">
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D12)</f>
         <v>7.5204771451239999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="14"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="14"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="14"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="15">
+      <c r="E13" s="18">
         <f>AVERAGE(D13:D23)</f>
         <v>6.5940540634390936E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="7">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="7">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="14"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="14"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="7">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="7">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="7">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="7">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -3430,118 +3444,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="18">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="6">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="6">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="6">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="6">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="6">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3588,10 +3602,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -3600,124 +3614,124 @@
       <c r="D2" s="3">
         <v>2.81366470929909E-3</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D12)</f>
         <v>2.8589718670011272E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>2.9086299843656201E-3</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>2.8725109233065098E-3</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>2.7472220866062401E-3</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>2.8395079487722498E-3</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>2.9094927500167801E-3</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>2.9300338678111201E-3</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>2.8954508177678399E-3</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>2.86130290885414E-3</v>
       </c>
-      <c r="E10" s="14"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>2.8834394576333199E-3</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>2.7874350825794901E-3</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -3726,124 +3740,124 @@
       <c r="D13" s="3">
         <v>2.4381599990933901E-3</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="18">
         <f>AVERAGE(D13:D23)</f>
         <v>2.6530523100631071E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>2.6282434237133502E-3</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>2.3461147455381701E-3</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>2.7524372879068298E-3</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>3.2472745789499402E-3</v>
       </c>
-      <c r="E17" s="14"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>2.5237854282296E-3</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>2.9887873260404599E-3</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>2.06526349558706E-3</v>
       </c>
-      <c r="E20" s="14"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>2.6816447983030599E-3</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>2.7565596821078398E-3</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>2.7553046452244798E-3</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -3852,121 +3866,121 @@
       <c r="D24" s="3">
         <v>3.3099004965032601E-3</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="18">
         <f>AVERAGE(D24:D33)</f>
         <v>2.4948066730810809E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>2.0223762558382102E-3</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>2.48460504443907E-3</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.1925517311301699E-3</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>2.0210547846704601E-3</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>2.32727791187156E-3</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3527282363668498E-3</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.00939520752292E-3</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>2.9226176336739399E-3</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="17"/>
       <c r="G33" s="4">
         <v>2.3055594287943698E-3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4013,354 +4027,354 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="15">
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D12)</f>
         <v>2.8999263001501983E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="14"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>2.9086299843656201E-3</v>
       </c>
-      <c r="E3" s="14"/>
+      <c r="E3" s="17"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>2.8725109233065098E-3</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="14"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="14"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>2.9094927500167801E-3</v>
       </c>
-      <c r="E7" s="14"/>
+      <c r="E7" s="17"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>2.9300338678111201E-3</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="17"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>2.8954508177678399E-3</v>
       </c>
-      <c r="E9" s="14"/>
+      <c r="E9" s="17"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>2.8834394576333199E-3</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="14"/>
+      <c r="E12" s="17"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="15">
+      <c r="E13" s="18">
         <f>AVERAGE(D13:D23)</f>
         <v>2.6829958775808596E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="7">
         <v>2.6282434237133502E-3</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="17"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="7">
         <v>2.7524372879068298E-3</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="14"/>
+      <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="7">
         <v>2.5237854282296E-3</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="14"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="7">
         <v>2.6816447983030599E-3</v>
       </c>
-      <c r="E21" s="14"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="7">
         <v>2.7565596821078398E-3</v>
       </c>
-      <c r="E22" s="14"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="7">
         <v>2.7553046452244798E-3</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="15">
+      <c r="E24" s="18">
         <f>AVERAGE(D24:D33)</f>
         <v>2.1463692199712816E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="6">
         <v>2.0223762558382102E-3</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="17"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="14"/>
+      <c r="E26" s="17"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="6">
         <v>2.1925517311301699E-3</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="6">
         <v>2.0210547846704601E-3</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="17"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="6">
         <v>2.32727791187156E-3</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="17"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="14"/>
+      <c r="E30" s="17"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="6">
         <v>2.00939520752292E-3</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="17"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="14"/>
+      <c r="E32" s="17"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="17"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D22560-9A40-4BF3-8B11-9D380A38383A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB1C815-F837-4ABA-A03A-44BA2D3578A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,13 +824,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="9">
-        <v>15</v>
-      </c>
-      <c r="D4" s="11">
-        <v>5</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -859,8 +853,9 @@
         <v>17</v>
       </c>
       <c r="C7" s="9">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E7" s="11"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
@@ -870,14 +865,9 @@
         <v>15</v>
       </c>
       <c r="C8" s="9">
-        <v>18</v>
-      </c>
-      <c r="D8" s="11">
-        <v>2</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>28</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="15"/>
@@ -897,6 +887,12 @@
       <c r="C10" s="9">
         <v>10</v>
       </c>
+      <c r="D10" s="11">
+        <v>10</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
@@ -928,6 +924,12 @@
       </c>
       <c r="C13" s="9">
         <v>10</v>
+      </c>
+      <c r="D13" s="11">
+        <v>10</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1842,18 +1844,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
     <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB1C815-F837-4ABA-A03A-44BA2D3578A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA501FD5-6487-41DC-A5EF-DBAA15EB0194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capa" sheetId="19" r:id="rId1"/>
-    <sheet name="Activity (3)" sheetId="20" r:id="rId2"/>
+    <sheet name="Activity-16-08" sheetId="20" r:id="rId2"/>
     <sheet name="Activity" sheetId="12" r:id="rId3"/>
     <sheet name="Activity (2)" sheetId="16" r:id="rId4"/>
     <sheet name="Age" sheetId="13" r:id="rId5"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
   <si>
     <t>Estratégia</t>
   </si>
@@ -240,12 +240,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>Dell</t>
-  </si>
-  <si>
-    <t>Acer</t>
   </si>
 </sst>
 </file>
@@ -885,14 +879,9 @@
         <v>17</v>
       </c>
       <c r="C10" s="9">
-        <v>10</v>
-      </c>
-      <c r="D10" s="11">
-        <v>10</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>27</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
@@ -923,14 +912,9 @@
         <v>17</v>
       </c>
       <c r="C13" s="9">
-        <v>10</v>
-      </c>
-      <c r="D13" s="11">
-        <v>10</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>28</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
@@ -1104,10 +1088,12 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="18" t="e">
+      <c r="D2" s="3">
+        <v>1.22740707443255E-3</v>
+      </c>
+      <c r="E2" s="18">
         <f>AVERAGE(D2:D21)</f>
-        <v>#DIV/0!</v>
+        <v>1.297143749129491E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1116,7 +1102,9 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="3">
+        <v>1.5217850441141701E-3</v>
+      </c>
       <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1125,7 +1113,9 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3">
+        <v>1.4187702239963399E-3</v>
+      </c>
       <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1134,7 +1124,9 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>1.21923057588587E-3</v>
+      </c>
       <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1143,7 +1135,9 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>1.2107251197056299E-3</v>
+      </c>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1152,7 +1146,9 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3">
+        <v>1.5994412310248701E-3</v>
+      </c>
       <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1161,7 +1157,9 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3">
+        <v>1.3964272541872899E-3</v>
+      </c>
       <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -1170,7 +1168,9 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3">
+        <v>1.5234914987065399E-3</v>
+      </c>
       <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1179,7 +1179,9 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>1.14432918115938E-3</v>
+      </c>
       <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1188,7 +1190,9 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>1.29480134619695E-3</v>
+      </c>
       <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1197,7 +1201,9 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <v>1.1901786885313401E-3</v>
+      </c>
       <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1206,7 +1212,9 @@
       <c r="C13" s="1">
         <v>12</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>1.21455597518885E-3</v>
+      </c>
       <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,7 +1223,9 @@
       <c r="C14" s="1">
         <v>13</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>1.0349880227689299E-3</v>
+      </c>
       <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1224,7 +1234,9 @@
       <c r="C15" s="1">
         <v>14</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>1.5204181152668999E-3</v>
+      </c>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1233,7 +1245,9 @@
       <c r="C16" s="1">
         <v>15</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>1.19990421209504E-3</v>
+      </c>
       <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1242,7 +1256,9 @@
       <c r="C17" s="1">
         <v>16</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>1.2246906354182901E-3</v>
+      </c>
       <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1251,7 +1267,9 @@
       <c r="C18" s="1">
         <v>17</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>1.52117829921756E-3</v>
+      </c>
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1260,7 +1278,9 @@
       <c r="C19" s="1">
         <v>18</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>1.52878814352704E-3</v>
+      </c>
       <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1269,7 +1289,9 @@
       <c r="C20" s="1">
         <v>19</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>1.0795270986069399E-3</v>
+      </c>
       <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1278,7 +1300,9 @@
       <c r="C21" s="1">
         <v>20</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>8.7223724255934196E-4</v>
+      </c>
       <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1291,10 +1315,12 @@
       <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="18" t="e">
+      <c r="D22" s="3">
+        <v>1.76494351019696E-4</v>
+      </c>
+      <c r="E22" s="18">
         <f>AVERAGE(D22:D41)</f>
-        <v>#DIV/0!</v>
+        <v>4.034168271948948E-4</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1303,7 +1329,9 @@
       <c r="C23" s="1">
         <v>2</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>5.46025356640438E-4</v>
+      </c>
       <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1312,7 +1340,9 @@
       <c r="C24" s="1">
         <v>3</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3">
+        <v>1.7489087688418899E-4</v>
+      </c>
       <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,7 +1351,9 @@
       <c r="C25" s="1">
         <v>4</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>4.5331415788522699E-4</v>
+      </c>
       <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1330,7 +1362,9 @@
       <c r="C26" s="1">
         <v>5</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>4.5224030226177498E-4</v>
+      </c>
       <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1339,7 +1373,9 @@
       <c r="C27" s="1">
         <v>6</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>3.25042909349475E-4</v>
+      </c>
       <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1348,7 +1384,9 @@
       <c r="C28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>5.4759582523591596E-4</v>
+      </c>
       <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1357,7 +1395,9 @@
       <c r="C29" s="1">
         <v>8</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>4.0296420303591798E-5</v>
+      </c>
       <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1366,7 +1406,9 @@
       <c r="C30" s="1">
         <v>9</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>8.9001901515576199E-4</v>
+      </c>
       <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1375,7 +1417,9 @@
       <c r="C31" s="1">
         <v>10</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>8.6876944325313898E-4</v>
+      </c>
       <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1384,7 +1428,9 @@
       <c r="C32" s="1">
         <v>11</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>5.9022203911008697E-4</v>
+      </c>
       <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1393,7 +1439,9 @@
       <c r="C33" s="1">
         <v>12</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>3.02335649703622E-4</v>
+      </c>
       <c r="E33" s="18"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1402,7 +1450,9 @@
       <c r="C34" s="1">
         <v>13</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3">
+        <v>2.5819234845117001E-4</v>
+      </c>
       <c r="E34" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1411,7 +1461,9 @@
       <c r="C35" s="1">
         <v>14</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3">
+        <v>4.24572970254118E-4</v>
+      </c>
       <c r="E35" s="18"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1420,7 +1472,9 @@
       <c r="C36" s="1">
         <v>15</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3">
+        <v>1.46589791995469E-6</v>
+      </c>
       <c r="E36" s="18"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1429,7 +1483,9 @@
       <c r="C37" s="1">
         <v>16</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3">
+        <v>3.9779324614368499E-4</v>
+      </c>
       <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1438,7 +1494,9 @@
       <c r="C38" s="1">
         <v>17</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3">
+        <v>6.1650864017884503E-4</v>
+      </c>
       <c r="E38" s="18"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1447,7 +1505,9 @@
       <c r="C39" s="1">
         <v>18</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3">
+        <v>2.20078163303027E-5</v>
+      </c>
       <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1456,7 +1516,9 @@
       <c r="C40" s="1">
         <v>19</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3">
+        <v>5.0701389861864603E-4</v>
+      </c>
       <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1465,7 +1527,9 @@
       <c r="C41" s="1">
         <v>20</v>
       </c>
-      <c r="D41" s="3"/>
+      <c r="D41" s="3">
+        <v>4.7353537919825702E-4</v>
+      </c>
       <c r="E41" s="18"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1478,10 +1542,12 @@
       <c r="C42" s="1">
         <v>1</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="18" t="e">
+      <c r="D42" s="3">
+        <v>1.73793482370665E-4</v>
+      </c>
+      <c r="E42" s="18">
         <f>AVERAGE(D42:D61)</f>
-        <v>#DIV/0!</v>
+        <v>2.2989102089417284E-4</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1490,7 +1556,9 @@
       <c r="C43" s="1">
         <v>2</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3">
+        <v>4.4079621496062001E-5</v>
+      </c>
       <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1499,7 +1567,9 @@
       <c r="C44" s="1">
         <v>3</v>
       </c>
-      <c r="D44" s="3"/>
+      <c r="D44" s="3">
+        <v>1.9820721733818201E-4</v>
+      </c>
       <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1508,7 +1578,9 @@
       <c r="C45" s="1">
         <v>4</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="3">
+        <v>2.6898882604876098E-4</v>
+      </c>
       <c r="E45" s="18"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1517,7 +1589,9 @@
       <c r="C46" s="1">
         <v>5</v>
       </c>
-      <c r="D46" s="3"/>
+      <c r="D46" s="3">
+        <v>9.9347684117131399E-6</v>
+      </c>
       <c r="E46" s="18"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1526,7 +1600,9 @@
       <c r="C47" s="1">
         <v>6</v>
       </c>
-      <c r="D47" s="3"/>
+      <c r="D47" s="3">
+        <v>1.70899292234211E-4</v>
+      </c>
       <c r="E47" s="18"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1535,7 +1611,9 @@
       <c r="C48" s="1">
         <v>7</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3">
+        <v>3.7644454634369102E-4</v>
+      </c>
       <c r="E48" s="18"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1544,7 +1622,9 @@
       <c r="C49" s="1">
         <v>8</v>
       </c>
-      <c r="D49" s="3"/>
+      <c r="D49" s="3">
+        <v>7.5758852866904895E-5</v>
+      </c>
       <c r="E49" s="18"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1553,7 +1633,9 @@
       <c r="C50" s="1">
         <v>9</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="3">
+        <v>4.9271851899704603E-4</v>
+      </c>
       <c r="E50" s="18"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1562,7 +1644,9 @@
       <c r="C51" s="1">
         <v>10</v>
       </c>
-      <c r="D51" s="3"/>
+      <c r="D51" s="3">
+        <v>1.9241252143063401E-4</v>
+      </c>
       <c r="E51" s="18"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1571,7 +1655,9 @@
       <c r="C52" s="1">
         <v>11</v>
       </c>
-      <c r="D52" s="3"/>
+      <c r="D52" s="3">
+        <v>3.3565148161274601E-4</v>
+      </c>
       <c r="E52" s="18"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1580,7 +1666,9 @@
       <c r="C53" s="1">
         <v>12</v>
       </c>
-      <c r="D53" s="3"/>
+      <c r="D53" s="3">
+        <v>1.2738871373007399E-4</v>
+      </c>
       <c r="E53" s="18"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1589,7 +1677,9 @@
       <c r="C54" s="1">
         <v>13</v>
       </c>
-      <c r="D54" s="3"/>
+      <c r="D54" s="3">
+        <v>3.4164426510307702E-4</v>
+      </c>
       <c r="E54" s="18"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1598,7 +1688,9 @@
       <c r="C55" s="1">
         <v>14</v>
       </c>
-      <c r="D55" s="3"/>
+      <c r="D55" s="3">
+        <v>1.78335406733681E-4</v>
+      </c>
       <c r="E55" s="18"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1607,7 +1699,9 @@
       <c r="C56" s="1">
         <v>15</v>
       </c>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3">
+        <v>5.6072231141028302E-4</v>
+      </c>
       <c r="E56" s="18"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1616,7 +1710,9 @@
       <c r="C57" s="1">
         <v>16</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3">
+        <v>1.25699260356949E-4</v>
+      </c>
       <c r="E57" s="18"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1625,7 +1721,9 @@
       <c r="C58" s="1">
         <v>17</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3">
+        <v>2.9871229144554201E-5</v>
+      </c>
       <c r="E58" s="18"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1634,7 +1732,9 @@
       <c r="C59" s="1">
         <v>18</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3">
+        <v>8.7146915612245604E-5</v>
+      </c>
       <c r="E59" s="18"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1643,7 +1743,9 @@
       <c r="C60" s="1">
         <v>19</v>
       </c>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3">
+        <v>3.6070190177676801E-4</v>
+      </c>
       <c r="E60" s="18"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1652,7 +1754,9 @@
       <c r="C61" s="1">
         <v>20</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="3">
+        <v>4.4742128486520899E-4</v>
+      </c>
       <c r="E61" s="18"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1665,10 +1769,12 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="18" t="e">
+      <c r="D62" s="3">
+        <v>4.48989923826619E-4</v>
+      </c>
+      <c r="E62" s="18">
         <f>AVERAGE(D62:D81)</f>
-        <v>#DIV/0!</v>
+        <v>2.6670853227371365E-4</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1677,7 +1783,9 @@
       <c r="C63" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3">
+        <v>1.5055522887011001E-4</v>
+      </c>
       <c r="E63" s="18"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1686,7 +1794,9 @@
       <c r="C64" s="1">
         <v>3</v>
       </c>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3">
+        <v>1.2001671465039301E-4</v>
+      </c>
       <c r="E64" s="18"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1695,7 +1805,9 @@
       <c r="C65" s="1">
         <v>4</v>
       </c>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3">
+        <v>1.99045734909399E-4</v>
+      </c>
       <c r="E65" s="18"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1704,7 +1816,9 @@
       <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3">
+        <v>3.1517033052413397E-4</v>
+      </c>
       <c r="E66" s="18"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1713,7 +1827,9 @@
       <c r="C67" s="1">
         <v>6</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3">
+        <v>3.5873259491317602E-4</v>
+      </c>
       <c r="E67" s="18"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1722,7 +1838,9 @@
       <c r="C68" s="1">
         <v>7</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>5.6793071768028501E-4</v>
+      </c>
       <c r="E68" s="18"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1731,7 +1849,9 @@
       <c r="C69" s="1">
         <v>8</v>
       </c>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3">
+        <v>4.0939064919241801E-4</v>
+      </c>
       <c r="E69" s="18"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1740,7 +1860,9 @@
       <c r="C70" s="1">
         <v>9</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="3">
+        <v>9.6317454533480103E-7</v>
+      </c>
       <c r="E70" s="18"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1749,7 +1871,9 @@
       <c r="C71" s="1">
         <v>10</v>
       </c>
-      <c r="D71" s="3"/>
+      <c r="D71" s="3">
+        <v>3.5605812198087302E-4</v>
+      </c>
       <c r="E71" s="18"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1758,7 +1882,9 @@
       <c r="C72" s="1">
         <v>11</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="3">
+        <v>9.6845900817349302E-5</v>
+      </c>
       <c r="E72" s="18"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1767,7 +1893,9 @@
       <c r="C73" s="1">
         <v>12</v>
       </c>
-      <c r="D73" s="3"/>
+      <c r="D73" s="3">
+        <v>3.4802240911229203E-4</v>
+      </c>
       <c r="E73" s="18"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1776,7 +1904,9 @@
       <c r="C74" s="1">
         <v>13</v>
       </c>
-      <c r="D74" s="3"/>
+      <c r="D74" s="3">
+        <v>3.7985374558741899E-4</v>
+      </c>
       <c r="E74" s="18"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1785,7 +1915,9 @@
       <c r="C75" s="1">
         <v>14</v>
       </c>
-      <c r="D75" s="3"/>
+      <c r="D75" s="3">
+        <v>2.78945000054973E-5</v>
+      </c>
       <c r="E75" s="18"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -1794,7 +1926,9 @@
       <c r="C76" s="1">
         <v>15</v>
       </c>
-      <c r="D76" s="3"/>
+      <c r="D76" s="3">
+        <v>1.03419433171377E-4</v>
+      </c>
       <c r="E76" s="18"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -1803,7 +1937,9 @@
       <c r="C77" s="1">
         <v>16</v>
       </c>
-      <c r="D77" s="3"/>
+      <c r="D77" s="3">
+        <v>3.8444733659274201E-4</v>
+      </c>
       <c r="E77" s="18"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -1844,18 +1980,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A2:A21"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A2:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA501FD5-6487-41DC-A5EF-DBAA15EB0194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092AAEDC-2463-446E-9919-A7C077F5DDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="31">
   <si>
     <t>Estratégia</t>
   </si>
@@ -240,6 +240,18 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>6 ao 12</t>
+  </si>
+  <si>
+    <t>Dell</t>
+  </si>
+  <si>
+    <t>3 ao 20</t>
+  </si>
+  <si>
+    <t>Acer</t>
   </si>
 </sst>
 </file>
@@ -422,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -479,6 +491,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -947,8 +962,14 @@
       <c r="C16" s="9">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>18</v>
       </c>
@@ -959,7 +980,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="10" t="s">
         <v>16</v>
@@ -968,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="10" t="s">
         <v>17</v>
@@ -977,7 +998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>19</v>
       </c>
@@ -986,14 +1007,14 @@
       </c>
       <c r="C20" s="9"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
       <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="9"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="16"/>
       <c r="B22" s="10" t="s">
         <v>17</v>
@@ -1001,8 +1022,14 @@
       <c r="C22" s="9">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>20</v>
       </c>
@@ -1011,14 +1038,14 @@
       </c>
       <c r="C23" s="9"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="9"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="10" t="s">
         <v>17</v>
@@ -1980,18 +2007,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
     <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092AAEDC-2463-446E-9919-A7C077F5DDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4938C55-9C78-411B-A58C-92F6AEC19EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capa" sheetId="19" r:id="rId1"/>
     <sheet name="Activity-16-08" sheetId="20" r:id="rId2"/>
-    <sheet name="Activity" sheetId="12" r:id="rId3"/>
-    <sheet name="Activity (2)" sheetId="16" r:id="rId4"/>
-    <sheet name="Age" sheetId="13" r:id="rId5"/>
-    <sheet name="Age (2)" sheetId="17" r:id="rId6"/>
-    <sheet name="Gender" sheetId="15" r:id="rId7"/>
-    <sheet name="Gender (2)" sheetId="18" r:id="rId8"/>
+    <sheet name="Activity-32-16" sheetId="21" r:id="rId3"/>
+    <sheet name="Activity-64-08" sheetId="22" r:id="rId4"/>
+    <sheet name="Activity" sheetId="12" r:id="rId5"/>
+    <sheet name="Activity (2)" sheetId="16" r:id="rId6"/>
+    <sheet name="Age" sheetId="13" r:id="rId7"/>
+    <sheet name="Age (2)" sheetId="17" r:id="rId8"/>
+    <sheet name="Gender" sheetId="15" r:id="rId9"/>
+    <sheet name="Gender (2)" sheetId="18" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -99,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="29">
   <si>
     <t>Estratégia</t>
   </si>
@@ -242,16 +244,10 @@
     <t>OK</t>
   </si>
   <si>
-    <t>6 ao 12</t>
+    <t>Acer</t>
   </si>
   <si>
-    <t>Dell</t>
-  </si>
-  <si>
-    <t>3 ao 20</t>
-  </si>
-  <si>
-    <t>Acer</t>
+    <t>12 ao 20</t>
   </si>
 </sst>
 </file>
@@ -465,6 +461,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -491,9 +490,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -808,7 +804,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -819,16 +815,16 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="9">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="10" t="s">
         <v>17</v>
       </c>
@@ -837,7 +833,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -848,16 +844,16 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="9">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="10" t="s">
         <v>17</v>
       </c>
@@ -867,7 +863,7 @@
       <c r="E7" s="11"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="10" t="s">
@@ -879,17 +875,17 @@
       <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="10" t="s">
         <v>17</v>
       </c>
@@ -899,7 +895,7 @@
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -910,7 +906,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="10" t="s">
         <v>16</v>
       </c>
@@ -922,7 +918,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="10" t="s">
         <v>17</v>
       </c>
@@ -932,7 +928,7 @@
       <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="15" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="10" t="s">
@@ -943,7 +939,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="10" t="s">
         <v>16</v>
       </c>
@@ -955,22 +951,18 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="9">
-        <v>5</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>28</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="10" t="s">
@@ -981,7 +973,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="10" t="s">
         <v>16</v>
       </c>
@@ -990,7 +982,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="10" t="s">
         <v>17</v>
       </c>
@@ -999,7 +991,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
@@ -1008,29 +1000,24 @@
       <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="15"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="9"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="16"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="9">
-        <v>2</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>30</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -1039,19 +1026,25 @@
       <c r="C23" s="9"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C25" s="9">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1076,6 +1069,400 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905FDE81-1C1B-4B15-90FD-7441C7029F15}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D12)</f>
+        <v>2.8999263001501983E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2.9086299843656201E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2.8725109233065098E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2.9094927500167801E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7">
+        <v>2.9300338678111201E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2.8954508177678399E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2.8834394576333199E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="19">
+        <f>AVERAGE(D13:D23)</f>
+        <v>2.6829958775808596E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2.6282434237133502E-3</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2.7524372879068298E-3</v>
+      </c>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2.5237854282296E-3</v>
+      </c>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.6816447983030599E-3</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7">
+        <v>2.7565596821078398E-3</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="7">
+        <v>2.7553046452244798E-3</v>
+      </c>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="19">
+        <f>AVERAGE(D24:D33)</f>
+        <v>2.1463692199712816E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.0223762558382102E-3</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2.1925517311301699E-3</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2.0210547846704601E-3</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6">
+        <v>2.32727791187156E-3</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.00939520752292E-3</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6">
+        <v>2.3055594287943698E-3</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6F5848-5D8E-43A8-AD08-E2A6A8019A0A}">
   <dimension ref="A1:G81"/>
@@ -1106,10 +1493,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1">
@@ -1118,225 +1505,225 @@
       <c r="D2" s="3">
         <v>1.22740707443255E-3</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>AVERAGE(D2:D21)</f>
         <v>1.297143749129491E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="18"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="18"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.21923057588587E-3</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.2107251197056299E-3</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>1.14432918115938E-3</v>
       </c>
-      <c r="E10" s="18"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="18"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>1.1901786885313401E-3</v>
       </c>
-      <c r="E12" s="18"/>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="1">
         <v>12</v>
       </c>
       <c r="D13" s="3">
         <v>1.21455597518885E-3</v>
       </c>
-      <c r="E13" s="18"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="1">
         <v>13</v>
       </c>
       <c r="D14" s="3">
         <v>1.0349880227689299E-3</v>
       </c>
-      <c r="E14" s="18"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="1">
         <v>14</v>
       </c>
       <c r="D15" s="3">
         <v>1.5204181152668999E-3</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="1">
         <v>15</v>
       </c>
       <c r="D16" s="3">
         <v>1.19990421209504E-3</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1">
         <v>16</v>
       </c>
       <c r="D17" s="3">
         <v>1.2246906354182901E-3</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="1">
         <v>17</v>
       </c>
       <c r="D18" s="3">
         <v>1.52117829921756E-3</v>
       </c>
-      <c r="E18" s="18"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="1">
         <v>18</v>
       </c>
       <c r="D19" s="3">
         <v>1.52878814352704E-3</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1">
         <v>19</v>
       </c>
       <c r="D20" s="3">
         <v>1.0795270986069399E-3</v>
       </c>
-      <c r="E20" s="18"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="1">
         <v>20</v>
       </c>
       <c r="D21" s="3">
         <v>8.7223724255934196E-4</v>
       </c>
-      <c r="E21" s="18"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>14</v>
       </c>
       <c r="C22" s="1">
@@ -1345,225 +1732,225 @@
       <c r="D22" s="3">
         <v>1.76494351019696E-4</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <f>AVERAGE(D22:D41)</f>
         <v>4.034168271948948E-4</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1">
         <v>2</v>
       </c>
       <c r="D23" s="3">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E23" s="18"/>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
       <c r="C24" s="1">
         <v>3</v>
       </c>
       <c r="D24" s="3">
         <v>1.7489087688418899E-4</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="1">
         <v>4</v>
       </c>
       <c r="D25" s="3">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E25" s="18"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1">
         <v>5</v>
       </c>
       <c r="D26" s="3">
         <v>4.5224030226177498E-4</v>
       </c>
-      <c r="E26" s="18"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="1">
         <v>6</v>
       </c>
       <c r="D27" s="3">
         <v>3.25042909349475E-4</v>
       </c>
-      <c r="E27" s="18"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="1">
         <v>7</v>
       </c>
       <c r="D28" s="3">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E28" s="18"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="1">
         <v>8</v>
       </c>
       <c r="D29" s="3">
         <v>4.0296420303591798E-5</v>
       </c>
-      <c r="E29" s="18"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="1">
         <v>9</v>
       </c>
       <c r="D30" s="3">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E30" s="18"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="1">
         <v>10</v>
       </c>
       <c r="D31" s="3">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E31" s="18"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="1">
         <v>11</v>
       </c>
       <c r="D32" s="3">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E32" s="18"/>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="1">
         <v>12</v>
       </c>
       <c r="D33" s="3">
         <v>3.02335649703622E-4</v>
       </c>
-      <c r="E33" s="18"/>
+      <c r="E33" s="19"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
       <c r="C34" s="1">
         <v>13</v>
       </c>
       <c r="D34" s="3">
         <v>2.5819234845117001E-4</v>
       </c>
-      <c r="E34" s="18"/>
+      <c r="E34" s="19"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
       <c r="C35" s="1">
         <v>14</v>
       </c>
       <c r="D35" s="3">
         <v>4.24572970254118E-4</v>
       </c>
-      <c r="E35" s="18"/>
+      <c r="E35" s="19"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
       <c r="C36" s="1">
         <v>15</v>
       </c>
       <c r="D36" s="3">
         <v>1.46589791995469E-6</v>
       </c>
-      <c r="E36" s="18"/>
+      <c r="E36" s="19"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
       <c r="C37" s="1">
         <v>16</v>
       </c>
       <c r="D37" s="3">
         <v>3.9779324614368499E-4</v>
       </c>
-      <c r="E37" s="18"/>
+      <c r="E37" s="19"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
       <c r="C38" s="1">
         <v>17</v>
       </c>
       <c r="D38" s="3">
         <v>6.1650864017884503E-4</v>
       </c>
-      <c r="E38" s="18"/>
+      <c r="E38" s="19"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
       <c r="C39" s="1">
         <v>18</v>
       </c>
       <c r="D39" s="3">
         <v>2.20078163303027E-5</v>
       </c>
-      <c r="E39" s="18"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
       <c r="C40" s="1">
         <v>19</v>
       </c>
       <c r="D40" s="3">
         <v>5.0701389861864603E-4</v>
       </c>
-      <c r="E40" s="18"/>
+      <c r="E40" s="19"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
       <c r="C41" s="1">
         <v>20</v>
       </c>
       <c r="D41" s="3">
         <v>4.7353537919825702E-4</v>
       </c>
-      <c r="E41" s="18"/>
+      <c r="E41" s="19"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="1">
@@ -1572,225 +1959,225 @@
       <c r="D42" s="3">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="19">
         <f>AVERAGE(D42:D61)</f>
         <v>2.2989102089417284E-4</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
       <c r="C43" s="1">
         <v>2</v>
       </c>
       <c r="D43" s="3">
         <v>4.4079621496062001E-5</v>
       </c>
-      <c r="E43" s="18"/>
+      <c r="E43" s="19"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
       <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="D44" s="3">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E44" s="18"/>
+      <c r="E44" s="19"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
       <c r="C45" s="1">
         <v>4</v>
       </c>
       <c r="D45" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E45" s="18"/>
+      <c r="E45" s="19"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
       <c r="C46" s="1">
         <v>5</v>
       </c>
       <c r="D46" s="3">
         <v>9.9347684117131399E-6</v>
       </c>
-      <c r="E46" s="18"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
       <c r="C47" s="1">
         <v>6</v>
       </c>
       <c r="D47" s="3">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E47" s="18"/>
+      <c r="E47" s="19"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
       <c r="C48" s="1">
         <v>7</v>
       </c>
       <c r="D48" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E48" s="18"/>
+      <c r="E48" s="19"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
       <c r="C49" s="1">
         <v>8</v>
       </c>
       <c r="D49" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E49" s="18"/>
+      <c r="E49" s="19"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
       <c r="C50" s="1">
         <v>9</v>
       </c>
       <c r="D50" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E50" s="18"/>
+      <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
       <c r="C51" s="1">
         <v>10</v>
       </c>
       <c r="D51" s="3">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E51" s="18"/>
+      <c r="E51" s="19"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
       <c r="C52" s="1">
         <v>11</v>
       </c>
       <c r="D52" s="3">
         <v>3.3565148161274601E-4</v>
       </c>
-      <c r="E52" s="18"/>
+      <c r="E52" s="19"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
       <c r="C53" s="1">
         <v>12</v>
       </c>
       <c r="D53" s="3">
         <v>1.2738871373007399E-4</v>
       </c>
-      <c r="E53" s="18"/>
+      <c r="E53" s="19"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
       <c r="C54" s="1">
         <v>13</v>
       </c>
       <c r="D54" s="3">
         <v>3.4164426510307702E-4</v>
       </c>
-      <c r="E54" s="18"/>
+      <c r="E54" s="19"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
       <c r="C55" s="1">
         <v>14</v>
       </c>
       <c r="D55" s="3">
         <v>1.78335406733681E-4</v>
       </c>
-      <c r="E55" s="18"/>
+      <c r="E55" s="19"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
       <c r="C56" s="1">
         <v>15</v>
       </c>
       <c r="D56" s="3">
         <v>5.6072231141028302E-4</v>
       </c>
-      <c r="E56" s="18"/>
+      <c r="E56" s="19"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
       <c r="C57" s="1">
         <v>16</v>
       </c>
       <c r="D57" s="3">
         <v>1.25699260356949E-4</v>
       </c>
-      <c r="E57" s="18"/>
+      <c r="E57" s="19"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
       <c r="C58" s="1">
         <v>17</v>
       </c>
       <c r="D58" s="3">
         <v>2.9871229144554201E-5</v>
       </c>
-      <c r="E58" s="18"/>
+      <c r="E58" s="19"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
       <c r="C59" s="1">
         <v>18</v>
       </c>
       <c r="D59" s="3">
         <v>8.7146915612245604E-5</v>
       </c>
-      <c r="E59" s="18"/>
+      <c r="E59" s="19"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
       <c r="C60" s="1">
         <v>19</v>
       </c>
       <c r="D60" s="3">
         <v>3.6070190177676801E-4</v>
       </c>
-      <c r="E60" s="18"/>
+      <c r="E60" s="19"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
       <c r="C61" s="1">
         <v>20</v>
       </c>
       <c r="D61" s="3">
         <v>4.4742128486520899E-4</v>
       </c>
-      <c r="E61" s="18"/>
+      <c r="E61" s="19"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="18" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="1">
@@ -1799,211 +2186,211 @@
       <c r="D62" s="3">
         <v>4.48989923826619E-4</v>
       </c>
-      <c r="E62" s="18">
+      <c r="E62" s="19">
         <f>AVERAGE(D62:D81)</f>
         <v>2.6670853227371365E-4</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
       <c r="C63" s="1">
         <v>2</v>
       </c>
       <c r="D63" s="3">
         <v>1.5055522887011001E-4</v>
       </c>
-      <c r="E63" s="18"/>
+      <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
       <c r="C64" s="1">
         <v>3</v>
       </c>
       <c r="D64" s="3">
         <v>1.2001671465039301E-4</v>
       </c>
-      <c r="E64" s="18"/>
+      <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
       <c r="C65" s="1">
         <v>4</v>
       </c>
       <c r="D65" s="3">
         <v>1.99045734909399E-4</v>
       </c>
-      <c r="E65" s="18"/>
+      <c r="E65" s="19"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
       <c r="C66" s="1">
         <v>5</v>
       </c>
       <c r="D66" s="3">
         <v>3.1517033052413397E-4</v>
       </c>
-      <c r="E66" s="18"/>
+      <c r="E66" s="19"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
       <c r="C67" s="1">
         <v>6</v>
       </c>
       <c r="D67" s="3">
         <v>3.5873259491317602E-4</v>
       </c>
-      <c r="E67" s="18"/>
+      <c r="E67" s="19"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
       <c r="C68" s="1">
         <v>7</v>
       </c>
       <c r="D68" s="3">
         <v>5.6793071768028501E-4</v>
       </c>
-      <c r="E68" s="18"/>
+      <c r="E68" s="19"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="17"/>
-      <c r="B69" s="17"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
       <c r="C69" s="1">
         <v>8</v>
       </c>
       <c r="D69" s="3">
         <v>4.0939064919241801E-4</v>
       </c>
-      <c r="E69" s="18"/>
+      <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="17"/>
-      <c r="B70" s="17"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
       <c r="C70" s="1">
         <v>9</v>
       </c>
       <c r="D70" s="3">
         <v>9.6317454533480103E-7</v>
       </c>
-      <c r="E70" s="18"/>
+      <c r="E70" s="19"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="17"/>
-      <c r="B71" s="17"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
       <c r="C71" s="1">
         <v>10</v>
       </c>
       <c r="D71" s="3">
         <v>3.5605812198087302E-4</v>
       </c>
-      <c r="E71" s="18"/>
+      <c r="E71" s="19"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="17"/>
-      <c r="B72" s="17"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
       <c r="C72" s="1">
         <v>11</v>
       </c>
       <c r="D72" s="3">
         <v>9.6845900817349302E-5</v>
       </c>
-      <c r="E72" s="18"/>
+      <c r="E72" s="19"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="17"/>
-      <c r="B73" s="17"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
       <c r="C73" s="1">
         <v>12</v>
       </c>
       <c r="D73" s="3">
         <v>3.4802240911229203E-4</v>
       </c>
-      <c r="E73" s="18"/>
+      <c r="E73" s="19"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="17"/>
-      <c r="B74" s="17"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
       <c r="C74" s="1">
         <v>13</v>
       </c>
       <c r="D74" s="3">
         <v>3.7985374558741899E-4</v>
       </c>
-      <c r="E74" s="18"/>
+      <c r="E74" s="19"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="17"/>
-      <c r="B75" s="17"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
       <c r="C75" s="1">
         <v>14</v>
       </c>
       <c r="D75" s="3">
         <v>2.78945000054973E-5</v>
       </c>
-      <c r="E75" s="18"/>
+      <c r="E75" s="19"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="17"/>
-      <c r="B76" s="17"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
       <c r="C76" s="1">
         <v>15</v>
       </c>
       <c r="D76" s="3">
         <v>1.03419433171377E-4</v>
       </c>
-      <c r="E76" s="18"/>
+      <c r="E76" s="19"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="17"/>
-      <c r="B77" s="17"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
       <c r="C77" s="1">
         <v>16</v>
       </c>
       <c r="D77" s="3">
         <v>3.8444733659274201E-4</v>
       </c>
-      <c r="E77" s="18"/>
+      <c r="E77" s="19"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="17"/>
-      <c r="B78" s="17"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
       <c r="C78" s="1">
         <v>17</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="18"/>
+      <c r="E78" s="19"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="17"/>
-      <c r="B79" s="17"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
       <c r="C79" s="1">
         <v>18</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="18"/>
+      <c r="E79" s="19"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
       <c r="C80" s="1">
         <v>19</v>
       </c>
       <c r="D80" s="3"/>
-      <c r="E80" s="18"/>
+      <c r="E80" s="19"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
       <c r="C81" s="1">
         <v>20</v>
       </c>
       <c r="D81" s="3"/>
-      <c r="E81" s="18"/>
+      <c r="E81" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2026,6 +2413,1772 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956C174B-C471-4A8E-A569-E674A0845CB0}">
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1.81177350386232E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D21)</f>
+        <v>1.7959470008830347E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.8148006812720001E-3</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.9192099019838601E-3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.79743309038328E-3</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1.81473244825032E-3</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.7655544363974901E-3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.8292592457589301E-3</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.8682265640655E-3</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.87493088160664E-3</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.79981277503543E-3</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.6285214462332901E-3</v>
+      </c>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.72431917895846E-3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.7444806162926099E-3</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.76178039008014E-3</v>
+      </c>
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.78436985306525E-3</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1.22745404238443E-3</v>
+      </c>
+      <c r="E22" s="19">
+        <f>AVERAGE(D22:D41)</f>
+        <v>1.0396084713082136E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1.2128989821674999E-3</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.2072314178239499E-3</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1.2932873130527701E-3</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1.22977847712741E-3</v>
+      </c>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1.3025872216186299E-3</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1.31460119291109E-3</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3">
+        <v>6.5370694203719098E-4</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3">
+        <v>9.4895394338624303E-4</v>
+      </c>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.3742461215116502E-4</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3">
+        <v>7.6866612718044195E-4</v>
+      </c>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>8.8623270175297597E-4</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1.1282395797383501E-3</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3">
+        <v>7.9655840881736998E-4</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3">
+        <v>8.86506107473686E-4</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>7.2837430705559596E-4</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>9.3942836160821241E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8.4607791428294903E-4</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>8.6882802551990898E-4</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>8.6728801473186397E-4</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>7.7904478042610005E-4</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>9.2900543855691799E-4</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1.2615741751790201E-3</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1.06939764152111E-3</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>9.7021590959237101E-4</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3">
+        <v>9.2769582628270304E-4</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3">
+        <v>9.4669778345507895E-4</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1.00990100961522E-3</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3">
+        <v>9.9005436558675204E-4</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>1.07585808806672E-3</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <v>1.13767442655503E-3</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1.03747697438056E-3</v>
+      </c>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3">
+        <v>1.14830186220033E-3</v>
+      </c>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3">
+        <v>6.8235983672783101E-4</v>
+      </c>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3">
+        <v>9.4821347887384102E-4</v>
+      </c>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3">
+        <v>5.6452737355434501E-4</v>
+      </c>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3">
+        <v>9.1128680440702296E-4</v>
+      </c>
+      <c r="E62" s="19">
+        <f>AVERAGE(D62:D81)</f>
+        <v>9.4846276299504156E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1.4683539980228999E-3</v>
+      </c>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1.6343507071946001E-3</v>
+      </c>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1.20977681426497E-3</v>
+      </c>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3">
+        <v>5.8142701679629399E-4</v>
+      </c>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1.60321717730762E-4</v>
+      </c>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>7.4779050881008296E-4</v>
+      </c>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3">
+        <v>1.52770895491985E-3</v>
+      </c>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3">
+        <v>8.6027219762045592E-6</v>
+      </c>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3">
+        <v>8.8286393758491098E-4</v>
+      </c>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3">
+        <v>6.4453391140332301E-4</v>
+      </c>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3">
+        <v>4.3678505857632399E-4</v>
+      </c>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3">
+        <v>1.9099989509070399E-3</v>
+      </c>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3">
+        <v>1.00141512844318E-3</v>
+      </c>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3">
+        <v>2.0372532554325802E-3</v>
+      </c>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1.2934721450619E-5</v>
+      </c>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA2EE0D-5FCF-4410-B029-D5CEFA04EE6D}">
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3.0978240498613701E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D21)</f>
+        <v>3.1563454979149051E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.2009432953445998E-3</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.1579264804642302E-3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.21297026733342E-3</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.11623672818373E-3</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.1017103904343898E-3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.1680537066117501E-3</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.1231260670666499E-3</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.0871044892398E-3</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.1837766954712298E-3</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.1490137271207299E-3</v>
+      </c>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.0895495975651402E-3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.0828146980759301E-3</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.1749190655984499E-3</v>
+      </c>
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.1629792886528102E-3</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.1931833688853802E-3</v>
+      </c>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.1783585315260398E-3</v>
+      </c>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.2214171091285199E-3</v>
+      </c>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.2610083682040902E-3</v>
+      </c>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3.1639940335298402E-3</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="19" t="e">
+        <f>AVERAGE(D22:D41)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="19" t="e">
+        <f>AVERAGE(D42:D61)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="19" t="e">
+        <f>AVERAGE(D62:D81)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2054,10 +4207,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -2066,124 +4219,124 @@
       <c r="D2" s="3">
         <v>1.22740707443255E-3</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>AVERAGE(D2:D12)</f>
         <v>1.3405988398128117E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.21923057588587E-3</v>
       </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.2107251197056299E-3</v>
       </c>
-      <c r="E6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="17"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>1.14432918115938E-3</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>1.1901786885313401E-3</v>
       </c>
-      <c r="E12" s="17"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -2192,124 +4345,124 @@
       <c r="D13" s="3">
         <v>1.76494351019696E-4</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>AVERAGE(D13:D23)</f>
         <v>4.6044642516324585E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="15"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E14" s="21"/>
+      <c r="E14" s="22"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="15"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>1.7489087688418899E-4</v>
       </c>
-      <c r="E15" s="21"/>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="15"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E16" s="21"/>
+      <c r="E16" s="22"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="15"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>4.5224030226177498E-4</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>3.25042909349475E-4</v>
       </c>
-      <c r="E18" s="21"/>
+      <c r="E18" s="22"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="15"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="22"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>4.0296400000000003E-5</v>
       </c>
-      <c r="E20" s="21"/>
+      <c r="E20" s="22"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="15"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="15"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="16"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="17"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E23" s="22"/>
+      <c r="E23" s="23"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -2318,118 +4471,118 @@
       <c r="D24" s="3">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <f>AVERAGE(D24:D33)</f>
         <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E25" s="17"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E26" s="17"/>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E27" s="17"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E28" s="17"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E29" s="17"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E30" s="17"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E32" s="17"/>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E33" s="17"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2447,7 +4600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C042F672-E41D-468F-9A40-AB573A878B0F}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2476,263 +4629,263 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>AVERAGE(D2:D15)</f>
         <v>1.4591194330376932E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
         <v>1.5217850441141701E-3</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>1.4187702239963399E-3</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
         <v>1.5994412310248701E-3</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
         <v>1.3964272541872899E-3</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
         <v>1.5234914987065399E-3</v>
       </c>
-      <c r="E9" s="17"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="17"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
         <v>1.29480134619695E-3</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="17"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="1"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="17"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="1"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="17"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="1">
         <v>11</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>AVERAGE(D16:D26)</f>
         <v>6.4932430621342815E-4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="15"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="1">
         <v>2</v>
       </c>
       <c r="D17" s="7">
         <v>5.46025356640438E-4</v>
       </c>
-      <c r="E17" s="21"/>
+      <c r="E17" s="22"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="15"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="21"/>
+      <c r="E18" s="22"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="15"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="1">
         <v>4</v>
       </c>
       <c r="D19" s="7">
         <v>4.5331415788522699E-4</v>
       </c>
-      <c r="E19" s="21"/>
+      <c r="E19" s="22"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="15"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="1">
         <v>5</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="21"/>
+      <c r="E20" s="22"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="15"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="1">
         <v>6</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="15"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="1">
         <v>7</v>
       </c>
       <c r="D22" s="7">
         <v>5.4759582523591596E-4</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="15"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="1">
         <v>8</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="21"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="15"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="1">
         <v>9</v>
       </c>
       <c r="D24" s="7">
         <v>8.9001901515576199E-4</v>
       </c>
-      <c r="E24" s="21"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="15"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="1">
         <v>10</v>
       </c>
       <c r="D25" s="7">
         <v>8.6876944325313898E-4</v>
       </c>
-      <c r="E25" s="21"/>
+      <c r="E25" s="22"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="16"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="17"/>
       <c r="C26" s="1">
         <v>11</v>
       </c>
       <c r="D26" s="7">
         <v>5.9022203911008697E-4</v>
       </c>
-      <c r="E26" s="22"/>
+      <c r="E26" s="23"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="1">
@@ -2741,162 +4894,162 @@
       <c r="D27" s="6">
         <v>1.73793482370665E-4</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <f>AVERAGE(D27:D40)</f>
         <v>2.1330410891497666E-4</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="1">
         <v>2</v>
       </c>
       <c r="D28" s="3">
         <v>4.4079599999999997E-5</v>
       </c>
-      <c r="E28" s="17"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="1">
         <v>3</v>
       </c>
       <c r="D29" s="6">
         <v>1.9820721733818201E-4</v>
       </c>
-      <c r="E29" s="17"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="1">
         <v>4</v>
       </c>
       <c r="D30" s="3">
         <v>2.6898882604876098E-4</v>
       </c>
-      <c r="E30" s="17"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="1">
         <v>5</v>
       </c>
       <c r="D31" s="3">
         <v>9.9348000000000002E-6</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="1">
         <v>6</v>
       </c>
       <c r="D32" s="6">
         <v>1.70899292234211E-4</v>
       </c>
-      <c r="E32" s="17"/>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="1">
         <v>7</v>
       </c>
       <c r="D33" s="3">
         <v>3.7644454634369102E-4</v>
       </c>
-      <c r="E33" s="17"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
       <c r="C34" s="1">
         <v>8</v>
       </c>
       <c r="D34" s="3">
         <v>7.5758852866904895E-5</v>
       </c>
-      <c r="E34" s="17"/>
+      <c r="E34" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
       <c r="C35" s="1">
         <v>9</v>
       </c>
       <c r="D35" s="3">
         <v>4.9271851899704603E-4</v>
       </c>
-      <c r="E35" s="17"/>
+      <c r="E35" s="18"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
       <c r="C36" s="1">
         <v>10</v>
       </c>
       <c r="D36" s="6">
         <v>1.9241252143063401E-4</v>
       </c>
-      <c r="E36" s="17"/>
+      <c r="E36" s="18"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
       <c r="C37" s="1">
         <v>11</v>
       </c>
       <c r="D37" s="3">
         <v>3.3565148161274601E-4</v>
       </c>
-      <c r="E37" s="17"/>
+      <c r="E37" s="18"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
       <c r="C38" s="1">
         <v>12</v>
       </c>
       <c r="D38" s="6">
         <v>1.2738871373007399E-4</v>
       </c>
-      <c r="E38" s="17"/>
+      <c r="E38" s="18"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
       <c r="C39" s="1">
         <v>13</v>
       </c>
       <c r="D39" s="3">
         <v>3.4164426510307702E-4</v>
       </c>
-      <c r="E39" s="17"/>
+      <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
       <c r="C40" s="1">
         <v>14</v>
       </c>
       <c r="D40" s="6">
         <v>1.78335406733681E-4</v>
       </c>
-      <c r="E40" s="17"/>
+      <c r="E40" s="18"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2914,7 +5067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2943,10 +5096,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -2955,124 +5108,124 @@
       <c r="D2" s="3">
         <v>6.8494550335423199E-3</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>AVERAGE(D2:D12)</f>
         <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>7.7222014481316001E-3</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>7.4276032951078701E-3</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>6.9163642363323698E-3</v>
       </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>7.1247468487415202E-3</v>
       </c>
-      <c r="E6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <v>7.9683523176790998E-3</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="3">
         <v>7.1325304703669396E-3</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>7.6723666731501597E-3</v>
       </c>
-      <c r="E9" s="17"/>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>6.44864466466859E-3</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="3">
         <v>7.1998086663083299E-3</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3">
         <v>6.8408648336931201E-3</v>
       </c>
-      <c r="E12" s="17"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
@@ -3081,124 +5234,124 @@
       <c r="D13" s="3">
         <v>4.4059430113216501E-3</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>AVERAGE(D13:D23)</f>
         <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="3">
         <v>6.0285373262784596E-3</v>
       </c>
-      <c r="E14" s="17"/>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3">
         <v>4.6542086132795998E-3</v>
       </c>
-      <c r="E15" s="17"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="3">
         <v>5.4842343524997596E-3</v>
       </c>
-      <c r="E16" s="17"/>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>5.2386490268761304E-3</v>
       </c>
-      <c r="E17" s="17"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
       <c r="D18" s="3">
         <v>4.5414210107642796E-3</v>
       </c>
-      <c r="E18" s="17"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
       <c r="D19" s="3">
         <v>6.4272965329950603E-3</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>3.38376634582825E-3</v>
       </c>
-      <c r="E20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>7.5523987537550697E-3</v>
       </c>
-      <c r="E21" s="17"/>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="3">
         <v>7.6800340233492996E-3</v>
       </c>
-      <c r="E22" s="17"/>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="3">
         <v>6.3918233917569199E-3</v>
       </c>
-      <c r="E23" s="17"/>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -3207,945 +5360,118 @@
       <c r="D24" s="3">
         <v>6.8834568210915997E-3</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <f>AVERAGE(D24:D33)</f>
         <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>5.9727451086721804E-3</v>
       </c>
-      <c r="E25" s="17"/>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>3.2861956035523401E-3</v>
       </c>
-      <c r="E26" s="17"/>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="3">
         <v>4.1621944755989501E-3</v>
       </c>
-      <c r="E27" s="17"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
       <c r="D28" s="3">
         <v>6.0968354981954303E-3</v>
       </c>
-      <c r="E28" s="17"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
       <c r="D29" s="3">
         <v>6.8318852941438796E-3</v>
       </c>
-      <c r="E29" s="17"/>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
       <c r="D30" s="3">
         <v>3.3675964367588002E-3</v>
       </c>
-      <c r="E30" s="17"/>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>2.7372032922601602E-3</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>4.0609534836609498E-3</v>
       </c>
-      <c r="E32" s="17"/>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="3">
         <v>3.6197936532585901E-3</v>
       </c>
-      <c r="E33" s="17"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="E13:E23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="18">
-        <f>AVERAGE(D2:D12)</f>
-        <v>7.5204771451239999E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="7">
-        <v>7.7222014481316001E-3</v>
-      </c>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="7">
-        <v>7.4276032951078701E-3</v>
-      </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="17"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7">
-        <v>7.9683523176790998E-3</v>
-      </c>
-      <c r="E7" s="17"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="7">
-        <v>7.1325304703669396E-3</v>
-      </c>
-      <c r="E8" s="17"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="7">
-        <v>7.6723666731501597E-3</v>
-      </c>
-      <c r="E9" s="17"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7">
-        <v>7.1998086663083299E-3</v>
-      </c>
-      <c r="E11" s="17"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="1">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="18">
-        <f>AVERAGE(D13:D23)</f>
-        <v>6.5940540634390936E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="7">
-        <v>6.0285373262784596E-3</v>
-      </c>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5.4842343524997596E-3</v>
-      </c>
-      <c r="E16" s="17"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="1">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="17"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="1">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="1">
-        <v>7</v>
-      </c>
-      <c r="D19" s="7">
-        <v>6.4272965329950603E-3</v>
-      </c>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="1">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="17"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="1">
-        <v>9</v>
-      </c>
-      <c r="D21" s="7">
-        <v>7.5523987537550697E-3</v>
-      </c>
-      <c r="E21" s="17"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="1">
-        <v>10</v>
-      </c>
-      <c r="D22" s="7">
-        <v>7.6800340233492996E-3</v>
-      </c>
-      <c r="E22" s="17"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="1">
-        <v>11</v>
-      </c>
-      <c r="D23" s="7">
-        <v>6.3918233917569199E-3</v>
-      </c>
-      <c r="E23" s="17"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>6.8834568210915997E-3</v>
-      </c>
-      <c r="E24" s="18">
-        <f>AVERAGE(D24:D33)</f>
-        <v>4.7018859667192891E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="1">
-        <v>2</v>
-      </c>
-      <c r="D25" s="3">
-        <v>5.9727451086721804E-3</v>
-      </c>
-      <c r="E25" s="17"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="6">
-        <v>3.2861956035523401E-3</v>
-      </c>
-      <c r="E26" s="17"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="1">
-        <v>4</v>
-      </c>
-      <c r="D27" s="6">
-        <v>4.1621944755989501E-3</v>
-      </c>
-      <c r="E27" s="17"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="1">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
-        <v>6.0968354981954303E-3</v>
-      </c>
-      <c r="E28" s="17"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="1">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>6.8318852941438796E-3</v>
-      </c>
-      <c r="E29" s="17"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="1">
-        <v>7</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3.3675964367588002E-3</v>
-      </c>
-      <c r="E30" s="17"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="1">
-        <v>8</v>
-      </c>
-      <c r="D31" s="6">
-        <v>2.7372032922601602E-3</v>
-      </c>
-      <c r="E31" s="17"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="1">
-        <v>9</v>
-      </c>
-      <c r="D32" s="6">
-        <v>4.0609534836609498E-3</v>
-      </c>
-      <c r="E32" s="17"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="1">
-        <v>10</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.6197936532585901E-3</v>
-      </c>
-      <c r="E33" s="17"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="E13:E23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2.81366470929909E-3</v>
-      </c>
-      <c r="E2" s="18">
-        <f>AVERAGE(D2:D12)</f>
-        <v>2.8589718670011272E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2.9086299843656201E-3</v>
-      </c>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2.8725109233065098E-3</v>
-      </c>
-      <c r="E4" s="17"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2.7472220866062401E-3</v>
-      </c>
-      <c r="E5" s="17"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2.8395079487722498E-3</v>
-      </c>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2.9094927500167801E-3</v>
-      </c>
-      <c r="E7" s="17"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2.9300338678111201E-3</v>
-      </c>
-      <c r="E8" s="17"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2.8954508177678399E-3</v>
-      </c>
-      <c r="E9" s="17"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2.86130290885414E-3</v>
-      </c>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2.8834394576333199E-3</v>
-      </c>
-      <c r="E11" s="17"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="1">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2.7874350825794901E-3</v>
-      </c>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2.4381599990933901E-3</v>
-      </c>
-      <c r="E13" s="18">
-        <f>AVERAGE(D13:D23)</f>
-        <v>2.6530523100631071E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2.6282434237133502E-3</v>
-      </c>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3">
-        <v>2.3461147455381701E-3</v>
-      </c>
-      <c r="E15" s="17"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2.7524372879068298E-3</v>
-      </c>
-      <c r="E16" s="17"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="1">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>3.2472745789499402E-3</v>
-      </c>
-      <c r="E17" s="17"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="1">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3">
-        <v>2.5237854282296E-3</v>
-      </c>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="1">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2.9887873260404599E-3</v>
-      </c>
-      <c r="E19" s="17"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="1">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2.06526349558706E-3</v>
-      </c>
-      <c r="E20" s="17"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="1">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2.6816447983030599E-3</v>
-      </c>
-      <c r="E21" s="17"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="1">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2.7565596821078398E-3</v>
-      </c>
-      <c r="E22" s="17"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="1">
-        <v>11</v>
-      </c>
-      <c r="D23" s="3">
-        <v>2.7553046452244798E-3</v>
-      </c>
-      <c r="E23" s="17"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3.3099004965032601E-3</v>
-      </c>
-      <c r="E24" s="18">
-        <f>AVERAGE(D24:D33)</f>
-        <v>2.4948066730810809E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="1">
-        <v>2</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2.0223762558382102E-3</v>
-      </c>
-      <c r="E25" s="17"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2.48460504443907E-3</v>
-      </c>
-      <c r="E26" s="17"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="1">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3">
-        <v>2.1925517311301699E-3</v>
-      </c>
-      <c r="E27" s="17"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="1">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
-        <v>2.0210547846704601E-3</v>
-      </c>
-      <c r="E28" s="17"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="1">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>2.32727791187156E-3</v>
-      </c>
-      <c r="E29" s="17"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="1">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3.3527282363668498E-3</v>
-      </c>
-      <c r="E30" s="17"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="1">
-        <v>8</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2.00939520752292E-3</v>
-      </c>
-      <c r="E31" s="17"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="1">
-        <v>9</v>
-      </c>
-      <c r="D32" s="3">
-        <v>2.9226176336739399E-3</v>
-      </c>
-      <c r="E32" s="17"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="1">
-        <v>10</v>
-      </c>
-      <c r="D33" s="3">
-        <v>2.3055594287943698E-3</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="G33" s="4">
-        <v>2.3055594287943698E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4164,7 +5490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905FDE81-1C1B-4B15-90FD-7441C7029F15}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4192,354 +5518,787 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>AVERAGE(D2:D12)</f>
-        <v>2.8999263001501983E-3</v>
+        <v>7.5204771451239999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="7">
-        <v>2.9086299843656201E-3</v>
-      </c>
-      <c r="E3" s="17"/>
+        <v>7.7222014481316001E-3</v>
+      </c>
+      <c r="E3" s="18"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="7">
-        <v>2.8725109233065098E-3</v>
-      </c>
-      <c r="E4" s="17"/>
+        <v>7.4276032951078701E-3</v>
+      </c>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="17"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="17"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1">
         <v>6</v>
       </c>
       <c r="D7" s="7">
-        <v>2.9094927500167801E-3</v>
-      </c>
-      <c r="E7" s="17"/>
+        <v>7.9683523176790998E-3</v>
+      </c>
+      <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="1">
         <v>7</v>
       </c>
       <c r="D8" s="7">
-        <v>2.9300338678111201E-3</v>
-      </c>
-      <c r="E8" s="17"/>
+        <v>7.1325304703669396E-3</v>
+      </c>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="1">
         <v>8</v>
       </c>
       <c r="D9" s="7">
-        <v>2.8954508177678399E-3</v>
-      </c>
-      <c r="E9" s="17"/>
+        <v>7.6723666731501597E-3</v>
+      </c>
+      <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="17"/>
+      <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="1">
         <v>10</v>
       </c>
       <c r="D11" s="7">
-        <v>2.8834394576333199E-3</v>
-      </c>
-      <c r="E11" s="17"/>
+        <v>7.1998086663083299E-3</v>
+      </c>
+      <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="17"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>AVERAGE(D13:D23)</f>
-        <v>2.6829958775808596E-3</v>
+        <v>6.5940540634390936E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="7">
-        <v>2.6282434237133502E-3</v>
-      </c>
-      <c r="E14" s="17"/>
+        <v>6.0285373262784596E-3</v>
+      </c>
+      <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="17"/>
+      <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
       <c r="D16" s="7">
-        <v>2.7524372879068298E-3</v>
-      </c>
-      <c r="E16" s="17"/>
+        <v>5.4842343524997596E-3</v>
+      </c>
+      <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1">
         <v>5</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="17"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="7">
-        <v>2.5237854282296E-3</v>
-      </c>
-      <c r="E18" s="17"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="17"/>
+      <c r="D19" s="7">
+        <v>6.4272965329950603E-3</v>
+      </c>
+      <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1">
         <v>8</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="1">
         <v>9</v>
       </c>
       <c r="D21" s="7">
-        <v>2.6816447983030599E-3</v>
-      </c>
-      <c r="E21" s="17"/>
+        <v>7.5523987537550697E-3</v>
+      </c>
+      <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="1">
         <v>10</v>
       </c>
       <c r="D22" s="7">
-        <v>2.7565596821078398E-3</v>
-      </c>
-      <c r="E22" s="17"/>
+        <v>7.6800340233492996E-3</v>
+      </c>
+      <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1">
         <v>11</v>
       </c>
       <c r="D23" s="7">
-        <v>2.7553046452244798E-3</v>
-      </c>
-      <c r="E23" s="17"/>
+        <v>6.3918233917569199E-3</v>
+      </c>
+      <c r="E23" s="18"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17" t="s">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="18">
+      <c r="D24" s="3">
+        <v>6.8834568210915997E-3</v>
+      </c>
+      <c r="E24" s="19">
         <f>AVERAGE(D24:D33)</f>
-        <v>2.1463692199712816E-3</v>
+        <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="6">
-        <v>2.0223762558382102E-3</v>
-      </c>
-      <c r="E25" s="17"/>
+      <c r="D25" s="3">
+        <v>5.9727451086721804E-3</v>
+      </c>
+      <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="6">
+        <v>3.2861956035523401E-3</v>
+      </c>
+      <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
       <c r="C27" s="1">
         <v>4</v>
       </c>
       <c r="D27" s="6">
-        <v>2.1925517311301699E-3</v>
-      </c>
-      <c r="E27" s="17"/>
+        <v>4.1621944755989501E-3</v>
+      </c>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="6">
-        <v>2.0210547846704601E-3</v>
-      </c>
-      <c r="E28" s="17"/>
+      <c r="D28" s="3">
+        <v>6.0968354981954303E-3</v>
+      </c>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="6">
-        <v>2.32727791187156E-3</v>
-      </c>
-      <c r="E29" s="17"/>
+      <c r="D29" s="3">
+        <v>6.8318852941438796E-3</v>
+      </c>
+      <c r="E29" s="18"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="17"/>
+      <c r="D30" s="6">
+        <v>3.3675964367588002E-3</v>
+      </c>
+      <c r="E30" s="18"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
       <c r="C31" s="1">
         <v>8</v>
       </c>
       <c r="D31" s="6">
-        <v>2.00939520752292E-3</v>
-      </c>
-      <c r="E31" s="17"/>
+        <v>2.7372032922601602E-3</v>
+      </c>
+      <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="17"/>
+      <c r="D32" s="6">
+        <v>4.0609534836609498E-3</v>
+      </c>
+      <c r="E32" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
       <c r="D33" s="6">
+        <v>3.6197936532585901E-3</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.81366470929909E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D12)</f>
+        <v>2.8589718670011272E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.9086299843656201E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.8725109233065098E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.7472220866062401E-3</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.8395079487722498E-3</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.9094927500167801E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.9300338678111201E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.8954508177678399E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.86130290885414E-3</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.8834394576333199E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.7874350825794901E-3</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.4381599990933901E-3</v>
+      </c>
+      <c r="E13" s="19">
+        <f>AVERAGE(D13:D23)</f>
+        <v>2.6530523100631071E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.6282434237133502E-3</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.3461147455381701E-3</v>
+      </c>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.7524372879068298E-3</v>
+      </c>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.2472745789499402E-3</v>
+      </c>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.5237854282296E-3</v>
+      </c>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2.9887873260404599E-3</v>
+      </c>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.06526349558706E-3</v>
+      </c>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.6816447983030599E-3</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.7565596821078398E-3</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.7553046452244798E-3</v>
+      </c>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.3099004965032601E-3</v>
+      </c>
+      <c r="E24" s="19">
+        <f>AVERAGE(D24:D33)</f>
+        <v>2.4948066730810809E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.0223762558382102E-3</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.48460504443907E-3</v>
+      </c>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.1925517311301699E-3</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.0210547846704601E-3</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2.32727791187156E-3</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3.3527282363668498E-3</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.00939520752292E-3</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2.9226176336739399E-3</v>
+      </c>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
         <v>2.3055594287943698E-3</v>
       </c>
-      <c r="E33" s="17"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
+      <c r="E33" s="18"/>
+      <c r="G33" s="4">
+        <v>2.3055594287943698E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4938C55-9C78-411B-A58C-92F6AEC19EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA73B652-8649-42BE-A27D-2FD276BF02FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="28">
   <si>
     <t>Estratégia</t>
   </si>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>Acer</t>
-  </si>
-  <si>
-    <t>12 ao 20</t>
   </si>
 </sst>
 </file>
@@ -1005,6 +1002,12 @@
         <v>16</v>
       </c>
       <c r="C21" s="9"/>
+      <c r="D21" s="11">
+        <v>5</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
@@ -1024,6 +1027,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="9"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
@@ -1031,6 +1035,12 @@
         <v>16</v>
       </c>
       <c r="C24" s="9"/>
+      <c r="D24" s="11">
+        <v>5</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
@@ -1038,14 +1048,9 @@
         <v>17</v>
       </c>
       <c r="C25" s="9">
-        <v>12</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>27</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E25" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2394,18 +2399,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A2:A21"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A2:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3323,18 +3328,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="A2:A21"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4160,18 +4165,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA73B652-8649-42BE-A27D-2FD276BF02FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B402450-C692-4441-A19A-D700982E4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="40">
   <si>
     <t>Estratégia</t>
   </si>
@@ -245,6 +245,42 @@
   </si>
   <si>
     <t>Acer</t>
+  </si>
+  <si>
+    <t>0.00008426125272287793</t>
+  </si>
+  <si>
+    <t>0.00028513611841457607</t>
+  </si>
+  <si>
+    <t>0.000050230047639008845</t>
+  </si>
+  <si>
+    <t>0.000020788333344080723</t>
+  </si>
+  <si>
+    <t>0.000018828346608490786</t>
+  </si>
+  <si>
+    <t>0.00019055804285282577</t>
+  </si>
+  <si>
+    <t>0.00000011082249822523104</t>
+  </si>
+  <si>
+    <t>0.0011675693782395708</t>
+  </si>
+  <si>
+    <t>0.00011459477836536617</t>
+  </si>
+  <si>
+    <t>0.00026680757261041794</t>
+  </si>
+  <si>
+    <t>0.00002832089405266678</t>
+  </si>
+  <si>
+    <t>0.00063205634573782</t>
   </si>
 </sst>
 </file>
@@ -994,14 +1030,19 @@
       <c r="B20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="9"/>
+      <c r="C20" s="9">
+        <v>2</v>
+      </c>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="16"/>
       <c r="B21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="9">
+        <v>5</v>
+      </c>
       <c r="D21" s="11">
         <v>5</v>
       </c>
@@ -1034,7 +1075,9 @@
       <c r="B24" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="9"/>
+      <c r="C24" s="9">
+        <v>5</v>
+      </c>
       <c r="D24" s="11">
         <v>5</v>
       </c>
@@ -2399,18 +2442,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
     <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3328,18 +3371,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3612,10 +3655,12 @@
       <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="19" t="e">
+      <c r="D22" s="3">
+        <v>5.3620058092532696E-4</v>
+      </c>
+      <c r="E22" s="19">
         <f>AVERAGE(D22:D41)</f>
-        <v>#DIV/0!</v>
+        <v>4.9034341319012184E-4</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -3624,7 +3669,9 @@
       <c r="C23" s="1">
         <v>2</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>4.9067443495337396E-4</v>
+      </c>
       <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -3633,7 +3680,9 @@
       <c r="C24" s="1">
         <v>3</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3">
+        <v>4.8274026235112602E-4</v>
+      </c>
       <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -3642,7 +3691,9 @@
       <c r="C25" s="1">
         <v>4</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>4.4905621092078499E-4</v>
+      </c>
       <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -3651,7 +3702,9 @@
       <c r="C26" s="1">
         <v>5</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>5.1592484645380599E-4</v>
+      </c>
       <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -3660,7 +3713,9 @@
       <c r="C27" s="1">
         <v>6</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>4.73706253041544E-4</v>
+      </c>
       <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -3669,7 +3724,9 @@
       <c r="C28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>4.8693322669276303E-4</v>
+      </c>
       <c r="E28" s="19"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -3678,7 +3735,9 @@
       <c r="C29" s="1">
         <v>8</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>4.7942464368844499E-4</v>
+      </c>
       <c r="E29" s="19"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -3687,7 +3746,9 @@
       <c r="C30" s="1">
         <v>9</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>4.7979506413700699E-4</v>
+      </c>
       <c r="E30" s="19"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -3696,7 +3757,9 @@
       <c r="C31" s="1">
         <v>10</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>5.1296010715081396E-4</v>
+      </c>
       <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -3705,7 +3768,9 @@
       <c r="C32" s="1">
         <v>11</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>4.9216958449097698E-4</v>
+      </c>
       <c r="E32" s="19"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -3714,7 +3779,9 @@
       <c r="C33" s="1">
         <v>12</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>4.7693767900378899E-4</v>
+      </c>
       <c r="E33" s="19"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -3723,7 +3790,9 @@
       <c r="C34" s="1">
         <v>13</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3">
+        <v>4.8081431395237298E-4</v>
+      </c>
       <c r="E34" s="19"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -3732,7 +3801,9 @@
       <c r="C35" s="1">
         <v>14</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3">
+        <v>4.6625232922799898E-4</v>
+      </c>
       <c r="E35" s="19"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -3741,7 +3812,9 @@
       <c r="C36" s="1">
         <v>15</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3">
+        <v>4.9613894416534099E-4</v>
+      </c>
       <c r="E36" s="19"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -3750,7 +3823,9 @@
       <c r="C37" s="1">
         <v>16</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3">
+        <v>5.0908324423255802E-4</v>
+      </c>
       <c r="E37" s="19"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -3759,7 +3834,9 @@
       <c r="C38" s="1">
         <v>17</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3">
+        <v>4.7948194577032699E-4</v>
+      </c>
       <c r="E38" s="19"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -3768,7 +3845,9 @@
       <c r="C39" s="1">
         <v>18</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3">
+        <v>4.9708175920040298E-4</v>
+      </c>
       <c r="E39" s="19"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -3777,7 +3856,9 @@
       <c r="C40" s="1">
         <v>19</v>
       </c>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3">
+        <v>4.8796962016209902E-4</v>
+      </c>
       <c r="E40" s="19"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -3786,7 +3867,9 @@
       <c r="C41" s="1">
         <v>20</v>
       </c>
-      <c r="D41" s="3"/>
+      <c r="D41" s="3">
+        <v>5.1352321328158098E-4</v>
+      </c>
       <c r="E41" s="19"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -3799,10 +3882,12 @@
       <c r="C42" s="1">
         <v>1</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="19" t="e">
+      <c r="D42" s="3">
+        <v>4.7450533056738598E-4</v>
+      </c>
+      <c r="E42" s="19">
         <f>AVERAGE(D42:D61)</f>
-        <v>#DIV/0!</v>
+        <v>4.9518087121661102E-4</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -3811,7 +3896,9 @@
       <c r="C43" s="1">
         <v>2</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3">
+        <v>4.48898127203229E-4</v>
+      </c>
       <c r="E43" s="19"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -3820,7 +3907,9 @@
       <c r="C44" s="1">
         <v>3</v>
       </c>
-      <c r="D44" s="3"/>
+      <c r="D44" s="3">
+        <v>4.8975663088243802E-4</v>
+      </c>
       <c r="E44" s="19"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -3829,7 +3918,9 @@
       <c r="C45" s="1">
         <v>4</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="3">
+        <v>5.1409628584040399E-4</v>
+      </c>
       <c r="E45" s="19"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -3838,7 +3929,9 @@
       <c r="C46" s="1">
         <v>5</v>
       </c>
-      <c r="D46" s="3"/>
+      <c r="D46" s="3">
+        <v>5.0419697243202298E-4</v>
+      </c>
       <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -3847,7 +3940,9 @@
       <c r="C47" s="1">
         <v>6</v>
       </c>
-      <c r="D47" s="3"/>
+      <c r="D47" s="3">
+        <v>5.1302186162947697E-4</v>
+      </c>
       <c r="E47" s="19"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -3856,7 +3951,9 @@
       <c r="C48" s="1">
         <v>7</v>
       </c>
-      <c r="D48" s="3"/>
+      <c r="D48" s="3">
+        <v>5.15007109778121E-4</v>
+      </c>
       <c r="E48" s="19"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -3865,7 +3962,9 @@
       <c r="C49" s="1">
         <v>8</v>
       </c>
-      <c r="D49" s="3"/>
+      <c r="D49" s="3">
+        <v>4.9144822252606497E-4</v>
+      </c>
       <c r="E49" s="19"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -3874,7 +3973,9 @@
       <c r="C50" s="1">
         <v>9</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="3">
+        <v>5.2696605308688799E-4</v>
+      </c>
       <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -3883,7 +3984,9 @@
       <c r="C51" s="1">
         <v>10</v>
       </c>
-      <c r="D51" s="3"/>
+      <c r="D51" s="3">
+        <v>5.3197903006485102E-4</v>
+      </c>
       <c r="E51" s="19"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -3892,7 +3995,9 @@
       <c r="C52" s="1">
         <v>11</v>
       </c>
-      <c r="D52" s="3"/>
+      <c r="D52" s="3">
+        <v>4.9968828335491297E-4</v>
+      </c>
       <c r="E52" s="19"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -3901,7 +4006,9 @@
       <c r="C53" s="1">
         <v>12</v>
       </c>
-      <c r="D53" s="3"/>
+      <c r="D53" s="3">
+        <v>4.7063199623675699E-4</v>
+      </c>
       <c r="E53" s="19"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -3910,7 +4017,9 @@
       <c r="C54" s="1">
         <v>13</v>
       </c>
-      <c r="D54" s="3"/>
+      <c r="D54" s="3">
+        <v>5.11065730498944E-4</v>
+      </c>
       <c r="E54" s="19"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -3919,7 +4028,9 @@
       <c r="C55" s="1">
         <v>14</v>
       </c>
-      <c r="D55" s="3"/>
+      <c r="D55" s="3">
+        <v>4.8510444527276802E-4</v>
+      </c>
       <c r="E55" s="19"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -3928,7 +4039,9 @@
       <c r="C56" s="1">
         <v>15</v>
       </c>
-      <c r="D56" s="3"/>
+      <c r="D56" s="3">
+        <v>5.1222185484092004E-4</v>
+      </c>
       <c r="E56" s="19"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -3937,7 +4050,9 @@
       <c r="C57" s="1">
         <v>16</v>
       </c>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3">
+        <v>4.73755015797482E-4</v>
+      </c>
       <c r="E57" s="19"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -3946,7 +4061,9 @@
       <c r="C58" s="1">
         <v>17</v>
       </c>
-      <c r="D58" s="3"/>
+      <c r="D58" s="3">
+        <v>4.2321035980401198E-4</v>
+      </c>
       <c r="E58" s="19"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -3955,7 +4072,9 @@
       <c r="C59" s="1">
         <v>18</v>
       </c>
-      <c r="D59" s="3"/>
+      <c r="D59" s="3">
+        <v>5.1827376578583804E-4</v>
+      </c>
       <c r="E59" s="19"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -3964,7 +4083,9 @@
       <c r="C60" s="1">
         <v>19</v>
       </c>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3">
+        <v>4.9801579214465302E-4</v>
+      </c>
       <c r="E60" s="19"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -3973,7 +4094,9 @@
       <c r="C61" s="1">
         <v>20</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="3">
+        <v>5.0177455658505102E-4</v>
+      </c>
       <c r="E61" s="19"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -3986,7 +4109,9 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="E62" s="19" t="e">
         <f>AVERAGE(D62:D81)</f>
         <v>#DIV/0!</v>
@@ -3998,7 +4123,9 @@
       <c r="C63" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -4007,7 +4134,9 @@
       <c r="C64" s="1">
         <v>3</v>
       </c>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -4016,7 +4145,9 @@
       <c r="C65" s="1">
         <v>4</v>
       </c>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="E65" s="19"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -4025,7 +4156,9 @@
       <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="E66" s="19"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -4034,7 +4167,9 @@
       <c r="C67" s="1">
         <v>6</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="E67" s="19"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -4043,7 +4178,9 @@
       <c r="C68" s="1">
         <v>7</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="E68" s="19"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -4052,7 +4189,9 @@
       <c r="C69" s="1">
         <v>8</v>
       </c>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -4061,7 +4200,9 @@
       <c r="C70" s="1">
         <v>9</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="E70" s="19"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -4070,7 +4211,9 @@
       <c r="C71" s="1">
         <v>10</v>
       </c>
-      <c r="D71" s="3"/>
+      <c r="D71" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="E71" s="19"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -4079,7 +4222,9 @@
       <c r="C72" s="1">
         <v>11</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E72" s="19"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -4088,7 +4233,9 @@
       <c r="C73" s="1">
         <v>12</v>
       </c>
-      <c r="D73" s="3"/>
+      <c r="D73" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E73" s="19"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -4165,18 +4312,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="A2:A21"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B402450-C692-4441-A19A-D700982E4DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91663962-28B9-4AA6-9328-0190CC44291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capa" sheetId="19" r:id="rId1"/>
     <sheet name="Activity-16-08" sheetId="20" r:id="rId2"/>
     <sheet name="Activity-32-16" sheetId="21" r:id="rId3"/>
     <sheet name="Activity-64-08" sheetId="22" r:id="rId4"/>
-    <sheet name="Activity" sheetId="12" r:id="rId5"/>
-    <sheet name="Activity (2)" sheetId="16" r:id="rId6"/>
-    <sheet name="Age" sheetId="13" r:id="rId7"/>
-    <sheet name="Age (2)" sheetId="17" r:id="rId8"/>
-    <sheet name="Gender" sheetId="15" r:id="rId9"/>
-    <sheet name="Gender (2)" sheetId="18" r:id="rId10"/>
+    <sheet name="Age-16-08" sheetId="23" r:id="rId5"/>
+    <sheet name="Age-32-16" sheetId="24" r:id="rId6"/>
+    <sheet name="Activity" sheetId="12" r:id="rId7"/>
+    <sheet name="Activity (2)" sheetId="16" r:id="rId8"/>
+    <sheet name="Age" sheetId="13" r:id="rId9"/>
+    <sheet name="Age (2)" sheetId="17" r:id="rId10"/>
+    <sheet name="Gender" sheetId="15" r:id="rId11"/>
+    <sheet name="Gender (2)" sheetId="18" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -101,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="66">
   <si>
     <t>Estratégia</t>
   </si>
@@ -281,6 +283,84 @@
   </si>
   <si>
     <t>0.00063205634573782</t>
+  </si>
+  <si>
+    <t>0.00009644672571143702</t>
+  </si>
+  <si>
+    <t>0.0004641752089120271</t>
+  </si>
+  <si>
+    <t>0.000022112568939252295</t>
+  </si>
+  <si>
+    <t>0.00031302763264424874</t>
+  </si>
+  <si>
+    <t>0.00015868389007219052</t>
+  </si>
+  <si>
+    <t>0.0001787146627812362</t>
+  </si>
+  <si>
+    <t>0.00003507727378722661</t>
+  </si>
+  <si>
+    <t>0.00019027668158216087</t>
+  </si>
+  <si>
+    <t>0.00003155995639270873</t>
+  </si>
+  <si>
+    <t>0.000010776308118814108</t>
+  </si>
+  <si>
+    <t>0.0001930182772226571</t>
+  </si>
+  <si>
+    <t>0.008443821545302503</t>
+  </si>
+  <si>
+    <t>0.008070676710282543</t>
+  </si>
+  <si>
+    <t>0.008522991666268442</t>
+  </si>
+  <si>
+    <t>0.008634708847753853</t>
+  </si>
+  <si>
+    <t>0.008175585403801599</t>
+  </si>
+  <si>
+    <t>0.008667483608796909</t>
+  </si>
+  <si>
+    <t>0.008103717141672313</t>
+  </si>
+  <si>
+    <t>0.00611422684128972</t>
+  </si>
+  <si>
+    <t>0.007267212046696717</t>
+  </si>
+  <si>
+    <t>0.0007374246121511659</t>
+  </si>
+  <si>
+    <t>0.0007686661271804426</t>
+  </si>
+  <si>
+    <t>0.006555385749806815</t>
+  </si>
+  <si>
+    <t>0.008095271064024735</t>
+  </si>
+  <si>
+    <t>0.006792237065817606</t>
+  </si>
+  <si>
+    <t>0.006794999836867685</t>
   </si>
 </sst>
 </file>
@@ -1043,9 +1123,6 @@
       <c r="C21" s="9">
         <v>5</v>
       </c>
-      <c r="D21" s="11">
-        <v>5</v>
-      </c>
       <c r="E21" s="11" t="s">
         <v>27</v>
       </c>
@@ -1076,9 +1153,6 @@
         <v>16</v>
       </c>
       <c r="C24" s="9">
-        <v>5</v>
-      </c>
-      <c r="D24" s="11">
         <v>5</v>
       </c>
       <c r="E24" s="11" t="s">
@@ -1118,6 +1192,833 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D12)</f>
+        <v>7.5204771451239999E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>7.7222014481316001E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7">
+        <v>7.4276032951078701E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7">
+        <v>7.9683523176790998E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7">
+        <v>7.1325304703669396E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7">
+        <v>7.6723666731501597E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7">
+        <v>7.1998086663083299E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="19">
+        <f>AVERAGE(D13:D23)</f>
+        <v>6.5940540634390936E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7">
+        <v>6.0285373262784596E-3</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.4842343524997596E-3</v>
+      </c>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="7">
+        <v>6.4272965329950603E-3</v>
+      </c>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="7">
+        <v>7.5523987537550697E-3</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7">
+        <v>7.6800340233492996E-3</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="7">
+        <v>6.3918233917569199E-3</v>
+      </c>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>6.8834568210915997E-3</v>
+      </c>
+      <c r="E24" s="19">
+        <f>AVERAGE(D24:D33)</f>
+        <v>4.7018859667192891E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>5.9727451086721804E-3</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6">
+        <v>3.2861956035523401E-3</v>
+      </c>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4.1621944755989501E-3</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>6.0968354981954303E-3</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>6.8318852941438796E-3</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="6">
+        <v>3.3675964367588002E-3</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="6">
+        <v>2.7372032922601602E-3</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="6">
+        <v>4.0609534836609498E-3</v>
+      </c>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.6197936532585901E-3</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.81366470929909E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D12)</f>
+        <v>2.8589718670011272E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.9086299843656201E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.8725109233065098E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.7472220866062401E-3</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.8395079487722498E-3</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.9094927500167801E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.9300338678111201E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.8954508177678399E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.86130290885414E-3</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.8834394576333199E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.7874350825794901E-3</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.4381599990933901E-3</v>
+      </c>
+      <c r="E13" s="19">
+        <f>AVERAGE(D13:D23)</f>
+        <v>2.6530523100631071E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.6282434237133502E-3</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.3461147455381701E-3</v>
+      </c>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.7524372879068298E-3</v>
+      </c>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.2472745789499402E-3</v>
+      </c>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.5237854282296E-3</v>
+      </c>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2.9887873260404599E-3</v>
+      </c>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.06526349558706E-3</v>
+      </c>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.6816447983030599E-3</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.7565596821078398E-3</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.7553046452244798E-3</v>
+      </c>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.3099004965032601E-3</v>
+      </c>
+      <c r="E24" s="19">
+        <f>AVERAGE(D24:D33)</f>
+        <v>2.4948066730810809E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.0223762558382102E-3</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.48460504443907E-3</v>
+      </c>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.1925517311301699E-3</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.0210547846704601E-3</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2.32727791187156E-3</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3.3527282363668498E-3</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.00939520752292E-3</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2.9226176336739399E-3</v>
+      </c>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.3055594287943698E-3</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="G33" s="4">
+        <v>2.3055594287943698E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905FDE81-1C1B-4B15-90FD-7441C7029F15}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2442,18 +3343,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A2:A21"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A2:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3371,6 +4272,996 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA2EE0D-5FCF-4410-B029-D5CEFA04EE6D}">
+  <dimension ref="A1:G84"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3.0978240498613701E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D21)</f>
+        <v>3.1563454979149051E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.2009432953445998E-3</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.1579264804642302E-3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.21297026733342E-3</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.11623672818373E-3</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.1017103904343898E-3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.1680537066117501E-3</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.1231260670666499E-3</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.0871044892398E-3</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.1837766954712298E-3</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.1490137271207299E-3</v>
+      </c>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.0895495975651402E-3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.0828146980759301E-3</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.1749190655984499E-3</v>
+      </c>
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.1629792886528102E-3</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.1931833688853802E-3</v>
+      </c>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.1783585315260398E-3</v>
+      </c>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.2214171091285199E-3</v>
+      </c>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.2610083682040902E-3</v>
+      </c>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3.1639940335298402E-3</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>5.3620058092532696E-4</v>
+      </c>
+      <c r="E22" s="19">
+        <f>AVERAGE(D22:D41)</f>
+        <v>4.9034341319012184E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4.9067443495337396E-4</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4.8274026235112602E-4</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4.4905621092078499E-4</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3">
+        <v>5.1592484645380599E-4</v>
+      </c>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3">
+        <v>4.73706253041544E-4</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>4.8693322669276303E-4</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3">
+        <v>4.7942464368844499E-4</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3">
+        <v>4.7979506413700699E-4</v>
+      </c>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3">
+        <v>5.1296010715081396E-4</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3">
+        <v>4.9216958449097698E-4</v>
+      </c>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>4.7693767900378899E-4</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3">
+        <v>4.8081431395237298E-4</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3">
+        <v>4.6625232922799898E-4</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3">
+        <v>4.9613894416534099E-4</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3">
+        <v>5.0908324423255802E-4</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3">
+        <v>4.7948194577032699E-4</v>
+      </c>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3">
+        <v>4.9708175920040298E-4</v>
+      </c>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3">
+        <v>4.8796962016209902E-4</v>
+      </c>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3">
+        <v>5.1352321328158098E-4</v>
+      </c>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>4.7450533056738598E-4</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>4.9518087121661102E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>4.48898127203229E-4</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>4.8975663088243802E-4</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>5.1409628584040399E-4</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>5.0419697243202298E-4</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>5.1302186162947697E-4</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>5.15007109778121E-4</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>4.9144822252606497E-4</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>5.2696605308688799E-4</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3">
+        <v>5.3197903006485102E-4</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3">
+        <v>4.9968828335491297E-4</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3">
+        <v>4.7063199623675699E-4</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3">
+        <v>5.11065730498944E-4</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>4.8510444527276802E-4</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <v>5.1222185484092004E-4</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3">
+        <v>4.73755015797482E-4</v>
+      </c>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3">
+        <v>4.2321035980401198E-4</v>
+      </c>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3">
+        <v>5.1827376578583804E-4</v>
+      </c>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3">
+        <v>4.9801579214465302E-4</v>
+      </c>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3">
+        <v>5.0177455658505102E-4</v>
+      </c>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E62" s="19" t="e">
+        <f>AVERAGE(D62:D84)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" s="19"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="1">
+        <v>21</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E82" s="19"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="1">
+        <v>22</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E83" s="19"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="1">
+        <v>23</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
     <mergeCell ref="A2:A21"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
@@ -3380,17 +5271,17 @@
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A62:A84"/>
+    <mergeCell ref="B62:B84"/>
+    <mergeCell ref="E62:E84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA2EE0D-5FCF-4410-B029-D5CEFA04EE6D}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{633554F0-CDCC-4625-B331-2BAE43124203}">
   <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3420,7 +5311,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>13</v>
@@ -3429,11 +5320,11 @@
         <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>3.0978240498613701E-3</v>
+        <v>6.8494550335423199E-3</v>
       </c>
       <c r="E2" s="19">
         <f>AVERAGE(D2:D21)</f>
-        <v>3.1563454979149051E-3</v>
+        <v>7.0918391765205065E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -3443,7 +5334,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3">
-        <v>3.2009432953445998E-3</v>
+        <v>7.7222014481316001E-3</v>
       </c>
       <c r="E3" s="19"/>
     </row>
@@ -3454,7 +5345,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="3">
-        <v>3.1579264804642302E-3</v>
+        <v>7.4276032951078701E-3</v>
       </c>
       <c r="E4" s="19"/>
     </row>
@@ -3465,7 +5356,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="3">
-        <v>3.21297026733342E-3</v>
+        <v>6.9163642363323698E-3</v>
       </c>
       <c r="E5" s="19"/>
     </row>
@@ -3476,7 +5367,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3">
-        <v>3.11623672818373E-3</v>
+        <v>7.1247468487415202E-3</v>
       </c>
       <c r="E6" s="19"/>
     </row>
@@ -3487,7 +5378,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>3.1017103904343898E-3</v>
+        <v>7.9683523176790998E-3</v>
       </c>
       <c r="E7" s="19"/>
     </row>
@@ -3498,7 +5389,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>3.1680537066117501E-3</v>
+        <v>7.1325304703669396E-3</v>
       </c>
       <c r="E8" s="19"/>
     </row>
@@ -3509,7 +5400,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="3">
-        <v>3.1231260670666499E-3</v>
+        <v>7.6723666731501597E-3</v>
       </c>
       <c r="E9" s="19"/>
     </row>
@@ -3520,7 +5411,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="3">
-        <v>3.0871044892398E-3</v>
+        <v>6.44864466466859E-3</v>
       </c>
       <c r="E10" s="19"/>
     </row>
@@ -3531,7 +5422,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="3">
-        <v>3.1837766954712298E-3</v>
+        <v>7.1998086663083299E-3</v>
       </c>
       <c r="E11" s="19"/>
     </row>
@@ -3542,7 +5433,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="3">
-        <v>3.1490137271207299E-3</v>
+        <v>6.8408648336931201E-3</v>
       </c>
       <c r="E12" s="19"/>
     </row>
@@ -3553,7 +5444,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="3">
-        <v>3.0895495975651402E-3</v>
+        <v>6.8814324682569903E-3</v>
       </c>
       <c r="E13" s="19"/>
     </row>
@@ -3564,7 +5455,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="3">
-        <v>3.0828146980759301E-3</v>
+        <v>6.3697274436861897E-3</v>
       </c>
       <c r="E14" s="19"/>
     </row>
@@ -3575,7 +5466,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="3">
-        <v>3.1749190655984499E-3</v>
+        <v>7.61589698193122E-3</v>
       </c>
       <c r="E15" s="19"/>
     </row>
@@ -3586,7 +5477,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="3">
-        <v>3.1629792886528102E-3</v>
+        <v>7.0268300176353302E-3</v>
       </c>
       <c r="E16" s="19"/>
     </row>
@@ -3597,7 +5488,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="3">
-        <v>3.1931833688853802E-3</v>
+        <v>6.8828583810696398E-3</v>
       </c>
       <c r="E17" s="19"/>
     </row>
@@ -3608,7 +5499,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="3">
-        <v>3.1783585315260398E-3</v>
+        <v>7.5946920303030597E-3</v>
       </c>
       <c r="E18" s="19"/>
     </row>
@@ -3619,7 +5510,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="3">
-        <v>3.2214171091285199E-3</v>
+        <v>7.8174824988819398E-3</v>
       </c>
       <c r="E19" s="19"/>
     </row>
@@ -3630,7 +5521,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3">
-        <v>3.2610083682040902E-3</v>
+        <v>6.5736147010191396E-3</v>
       </c>
       <c r="E20" s="19"/>
     </row>
@@ -3641,13 +5532,13 @@
         <v>20</v>
       </c>
       <c r="D21" s="3">
-        <v>3.1639940335298402E-3</v>
+        <v>5.7713105199046896E-3</v>
       </c>
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>14</v>
@@ -3656,11 +5547,11 @@
         <v>1</v>
       </c>
       <c r="D22" s="3">
-        <v>5.3620058092532696E-4</v>
+        <v>4.4059430113216501E-3</v>
       </c>
       <c r="E22" s="19">
         <f>AVERAGE(D22:D41)</f>
-        <v>4.9034341319012184E-4</v>
+        <v>5.3183658635870337E-3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -3670,7 +5561,7 @@
         <v>2</v>
       </c>
       <c r="D23" s="3">
-        <v>4.9067443495337396E-4</v>
+        <v>6.0285373262784596E-3</v>
       </c>
       <c r="E23" s="19"/>
     </row>
@@ -3681,7 +5572,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="3">
-        <v>4.8274026235112602E-4</v>
+        <v>4.6542086132795998E-3</v>
       </c>
       <c r="E24" s="19"/>
     </row>
@@ -3692,7 +5583,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="3">
-        <v>4.4905621092078499E-4</v>
+        <v>5.4842343524997596E-3</v>
       </c>
       <c r="E25" s="19"/>
     </row>
@@ -3703,7 +5594,7 @@
         <v>5</v>
       </c>
       <c r="D26" s="3">
-        <v>5.1592484645380599E-4</v>
+        <v>5.2386490268761304E-3</v>
       </c>
       <c r="E26" s="19"/>
     </row>
@@ -3714,7 +5605,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="3">
-        <v>4.73706253041544E-4</v>
+        <v>4.5414210107642796E-3</v>
       </c>
       <c r="E27" s="19"/>
     </row>
@@ -3725,7 +5616,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>4.8693322669276303E-4</v>
+        <v>6.4272965329950603E-3</v>
       </c>
       <c r="E28" s="19"/>
     </row>
@@ -3736,7 +5627,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="3">
-        <v>4.7942464368844499E-4</v>
+        <v>3.38376634582825E-3</v>
       </c>
       <c r="E29" s="19"/>
     </row>
@@ -3747,7 +5638,7 @@
         <v>9</v>
       </c>
       <c r="D30" s="3">
-        <v>4.7979506413700699E-4</v>
+        <v>7.5523987537550697E-3</v>
       </c>
       <c r="E30" s="19"/>
     </row>
@@ -3758,7 +5649,7 @@
         <v>10</v>
       </c>
       <c r="D31" s="3">
-        <v>5.1296010715081396E-4</v>
+        <v>7.6800340233492996E-3</v>
       </c>
       <c r="E31" s="19"/>
     </row>
@@ -3769,7 +5660,7 @@
         <v>11</v>
       </c>
       <c r="D32" s="3">
-        <v>4.9216958449097698E-4</v>
+        <v>6.3918233917569199E-3</v>
       </c>
       <c r="E32" s="19"/>
     </row>
@@ -3780,7 +5671,7 @@
         <v>12</v>
       </c>
       <c r="D33" s="3">
-        <v>4.7693767900378899E-4</v>
+        <v>4.2373542282834803E-3</v>
       </c>
       <c r="E33" s="19"/>
     </row>
@@ -3791,7 +5682,7 @@
         <v>13</v>
       </c>
       <c r="D34" s="3">
-        <v>4.8081431395237298E-4</v>
+        <v>4.915635919904E-3</v>
       </c>
       <c r="E34" s="19"/>
     </row>
@@ -3802,7 +5693,7 @@
         <v>14</v>
       </c>
       <c r="D35" s="3">
-        <v>4.6625232922799898E-4</v>
+        <v>5.4657145165723396E-3</v>
       </c>
       <c r="E35" s="19"/>
     </row>
@@ -3813,7 +5704,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="3">
-        <v>4.9613894416534099E-4</v>
+        <v>2.4761238010971602E-3</v>
       </c>
       <c r="E36" s="19"/>
     </row>
@@ -3824,7 +5715,7 @@
         <v>16</v>
       </c>
       <c r="D37" s="3">
-        <v>5.0908324423255802E-4</v>
+        <v>5.6164777642944402E-3</v>
       </c>
       <c r="E37" s="19"/>
     </row>
@@ -3835,7 +5726,7 @@
         <v>17</v>
       </c>
       <c r="D38" s="3">
-        <v>4.7948194577032699E-4</v>
+        <v>7.1929511615365102E-3</v>
       </c>
       <c r="E38" s="19"/>
     </row>
@@ -3846,7 +5737,7 @@
         <v>18</v>
       </c>
       <c r="D39" s="3">
-        <v>4.9708175920040298E-4</v>
+        <v>2.8599226141712798E-3</v>
       </c>
       <c r="E39" s="19"/>
     </row>
@@ -3857,7 +5748,7 @@
         <v>19</v>
       </c>
       <c r="D40" s="3">
-        <v>4.8796962016209902E-4</v>
+        <v>6.4138915677315004E-3</v>
       </c>
       <c r="E40" s="19"/>
     </row>
@@ -3868,13 +5759,13 @@
         <v>20</v>
       </c>
       <c r="D41" s="3">
-        <v>5.1352321328158098E-4</v>
+        <v>5.4009333094454997E-3</v>
       </c>
       <c r="E41" s="19"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>24</v>
@@ -3883,11 +5774,11 @@
         <v>1</v>
       </c>
       <c r="D42" s="3">
-        <v>4.7450533056738598E-4</v>
+        <v>6.8834568210915997E-3</v>
       </c>
       <c r="E42" s="19">
         <f>AVERAGE(D42:D61)</f>
-        <v>4.9518087121661102E-4</v>
+        <v>4.576013434961077E-3</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -3897,7 +5788,7 @@
         <v>2</v>
       </c>
       <c r="D43" s="3">
-        <v>4.48898127203229E-4</v>
+        <v>5.9727451086721804E-3</v>
       </c>
       <c r="E43" s="19"/>
     </row>
@@ -3908,7 +5799,7 @@
         <v>3</v>
       </c>
       <c r="D44" s="3">
-        <v>4.8975663088243802E-4</v>
+        <v>3.2861956035523401E-3</v>
       </c>
       <c r="E44" s="19"/>
     </row>
@@ -3919,7 +5810,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="3">
-        <v>5.1409628584040399E-4</v>
+        <v>4.1621944755989501E-3</v>
       </c>
       <c r="E45" s="19"/>
     </row>
@@ -3930,7 +5821,7 @@
         <v>5</v>
       </c>
       <c r="D46" s="3">
-        <v>5.0419697243202298E-4</v>
+        <v>6.0968354981954303E-3</v>
       </c>
       <c r="E46" s="19"/>
     </row>
@@ -3941,7 +5832,7 @@
         <v>6</v>
       </c>
       <c r="D47" s="3">
-        <v>5.1302186162947697E-4</v>
+        <v>6.8318852941438796E-3</v>
       </c>
       <c r="E47" s="19"/>
     </row>
@@ -3952,7 +5843,7 @@
         <v>7</v>
       </c>
       <c r="D48" s="3">
-        <v>5.15007109778121E-4</v>
+        <v>3.3675964367588002E-3</v>
       </c>
       <c r="E48" s="19"/>
     </row>
@@ -3963,7 +5854,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="3">
-        <v>4.9144822252606497E-4</v>
+        <v>2.7372032922601602E-3</v>
       </c>
       <c r="E49" s="19"/>
     </row>
@@ -3974,7 +5865,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="3">
-        <v>5.2696605308688799E-4</v>
+        <v>4.0609534836609498E-3</v>
       </c>
       <c r="E50" s="19"/>
     </row>
@@ -3985,7 +5876,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="3">
-        <v>5.3197903006485102E-4</v>
+        <v>3.6197936532585901E-3</v>
       </c>
       <c r="E51" s="19"/>
     </row>
@@ -3996,7 +5887,7 @@
         <v>11</v>
       </c>
       <c r="D52" s="3">
-        <v>4.9968828335491297E-4</v>
+        <v>3.6673222957590902E-3</v>
       </c>
       <c r="E52" s="19"/>
     </row>
@@ -4007,7 +5898,7 @@
         <v>12</v>
       </c>
       <c r="D53" s="3">
-        <v>4.7063199623675699E-4</v>
+        <v>2.90451377202124E-3</v>
       </c>
       <c r="E53" s="19"/>
     </row>
@@ -4018,7 +5909,7 @@
         <v>13</v>
       </c>
       <c r="D54" s="3">
-        <v>5.11065730498944E-4</v>
+        <v>7.0540871245019796E-3</v>
       </c>
       <c r="E54" s="19"/>
     </row>
@@ -4029,7 +5920,7 @@
         <v>14</v>
       </c>
       <c r="D55" s="3">
-        <v>4.8510444527276802E-4</v>
+        <v>3.7965863896698201E-3</v>
       </c>
       <c r="E55" s="19"/>
     </row>
@@ -4040,7 +5931,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="3">
-        <v>5.1222185484092004E-4</v>
+        <v>5.4131272615231298E-3</v>
       </c>
       <c r="E56" s="19"/>
     </row>
@@ -4051,7 +5942,7 @@
         <v>16</v>
       </c>
       <c r="D57" s="3">
-        <v>4.73755015797482E-4</v>
+        <v>5.8200351814192202E-3</v>
       </c>
       <c r="E57" s="19"/>
     </row>
@@ -4062,7 +5953,7 @@
         <v>17</v>
       </c>
       <c r="D58" s="3">
-        <v>4.2321035980401198E-4</v>
+        <v>3.1635792867456898E-3</v>
       </c>
       <c r="E58" s="19"/>
     </row>
@@ -4073,7 +5964,7 @@
         <v>18</v>
       </c>
       <c r="D59" s="3">
-        <v>5.1827376578583804E-4</v>
+        <v>3.3820933092763698E-3</v>
       </c>
       <c r="E59" s="19"/>
     </row>
@@ -4084,7 +5975,7 @@
         <v>19</v>
       </c>
       <c r="D60" s="3">
-        <v>4.9801579214465302E-4</v>
+        <v>4.2017418724428698E-3</v>
       </c>
       <c r="E60" s="19"/>
     </row>
@@ -4095,13 +5986,13 @@
         <v>20</v>
       </c>
       <c r="D61" s="3">
-        <v>5.0177455658505102E-4</v>
+        <v>5.0983225386692496E-3</v>
       </c>
       <c r="E61" s="19"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>25</v>
@@ -4109,12 +6000,12 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="19" t="e">
+      <c r="D62" s="3">
+        <v>6.2818931418228401E-3</v>
+      </c>
+      <c r="E62" s="19">
         <f>AVERAGE(D62:D81)</f>
-        <v>#DIV/0!</v>
+        <v>6.5500486795894604E-3</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -4123,8 +6014,8 @@
       <c r="C63" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>29</v>
+      <c r="D63" s="3">
+        <v>6.8182042173560798E-3</v>
       </c>
       <c r="E63" s="19"/>
     </row>
@@ -4134,9 +6025,7 @@
       <c r="C64" s="1">
         <v>3</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="D64" s="3"/>
       <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -4145,9 +6034,7 @@
       <c r="C65" s="1">
         <v>4</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="D65" s="3"/>
       <c r="E65" s="19"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -4156,9 +6043,7 @@
       <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="D66" s="3"/>
       <c r="E66" s="19"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -4167,9 +6052,7 @@
       <c r="C67" s="1">
         <v>6</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="D67" s="3"/>
       <c r="E67" s="19"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -4178,9 +6061,7 @@
       <c r="C68" s="1">
         <v>7</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="D68" s="3"/>
       <c r="E68" s="19"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -4189,9 +6070,7 @@
       <c r="C69" s="1">
         <v>8</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="D69" s="3"/>
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -4200,9 +6079,7 @@
       <c r="C70" s="1">
         <v>9</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="D70" s="3"/>
       <c r="E70" s="19"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -4211,9 +6088,7 @@
       <c r="C71" s="1">
         <v>10</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>37</v>
-      </c>
+      <c r="D71" s="3"/>
       <c r="E71" s="19"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -4222,9 +6097,7 @@
       <c r="C72" s="1">
         <v>11</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="D72" s="3"/>
       <c r="E72" s="19"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -4233,9 +6106,7 @@
       <c r="C73" s="1">
         <v>12</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="D73" s="3"/>
       <c r="E73" s="19"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -4330,7 +6201,884 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A187A79-2F9C-4481-8EBD-08EEDD2231C1}">
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>8.8432581244842993E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D21)</f>
+        <v>8.7675163804370772E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.9353771851844298E-3</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9.0998611554805892E-3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.7575297490641597E-3</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.7434515023467104E-3</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.7263566291275602E-3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.9138666514094102E-3</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>9.0047530343961499E-3</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.0233626371162608E-3</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8.8549492408121905E-3</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.2547618993638692E-3</v>
+      </c>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8.4273010266179994E-3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.5966886811637503E-3</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.6313316596500593E-3</v>
+      </c>
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.6998965303387195E-3</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="19" t="e">
+        <f>AVERAGE(D22:D41)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>6.2969138289247001E-3</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>6.1136459708670248E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>6.4076776396648598E-3</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>6.2667263273711001E-3</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>6.2939902848690703E-3</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>6.1958847109314704E-3</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>5.8309748107789102E-3</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>5.5695092562729398E-3</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>6.4782136600685398E-3</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>5.5695092562729398E-3</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3">
+        <v>6.2270599335157101E-3</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="19" t="e">
+        <f>AVERAGE(D62:D81)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4752,7 +7500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C042F672-E41D-468F-9A40-AB573A878B0F}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5219,7 +7967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5617,833 +8365,6 @@
       <c r="E33" s="18"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="E13:E23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="19">
-        <f>AVERAGE(D2:D12)</f>
-        <v>7.5204771451239999E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="7">
-        <v>7.7222014481316001E-3</v>
-      </c>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="7">
-        <v>7.4276032951078701E-3</v>
-      </c>
-      <c r="E4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7">
-        <v>7.9683523176790998E-3</v>
-      </c>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="7">
-        <v>7.1325304703669396E-3</v>
-      </c>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="7">
-        <v>7.6723666731501597E-3</v>
-      </c>
-      <c r="E9" s="18"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7">
-        <v>7.1998086663083299E-3</v>
-      </c>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="1">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="19">
-        <f>AVERAGE(D13:D23)</f>
-        <v>6.5940540634390936E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="7">
-        <v>6.0285373262784596E-3</v>
-      </c>
-      <c r="E14" s="18"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="18"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5.4842343524997596E-3</v>
-      </c>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="1">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="1">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="18"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="1">
-        <v>7</v>
-      </c>
-      <c r="D19" s="7">
-        <v>6.4272965329950603E-3</v>
-      </c>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="1">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="1">
-        <v>9</v>
-      </c>
-      <c r="D21" s="7">
-        <v>7.5523987537550697E-3</v>
-      </c>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="1">
-        <v>10</v>
-      </c>
-      <c r="D22" s="7">
-        <v>7.6800340233492996E-3</v>
-      </c>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="1">
-        <v>11</v>
-      </c>
-      <c r="D23" s="7">
-        <v>6.3918233917569199E-3</v>
-      </c>
-      <c r="E23" s="18"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>6.8834568210915997E-3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>AVERAGE(D24:D33)</f>
-        <v>4.7018859667192891E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="1">
-        <v>2</v>
-      </c>
-      <c r="D25" s="3">
-        <v>5.9727451086721804E-3</v>
-      </c>
-      <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="6">
-        <v>3.2861956035523401E-3</v>
-      </c>
-      <c r="E26" s="18"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="1">
-        <v>4</v>
-      </c>
-      <c r="D27" s="6">
-        <v>4.1621944755989501E-3</v>
-      </c>
-      <c r="E27" s="18"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="1">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
-        <v>6.0968354981954303E-3</v>
-      </c>
-      <c r="E28" s="18"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="1">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>6.8318852941438796E-3</v>
-      </c>
-      <c r="E29" s="18"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="1">
-        <v>7</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3.3675964367588002E-3</v>
-      </c>
-      <c r="E30" s="18"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="1">
-        <v>8</v>
-      </c>
-      <c r="D31" s="6">
-        <v>2.7372032922601602E-3</v>
-      </c>
-      <c r="E31" s="18"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="1">
-        <v>9</v>
-      </c>
-      <c r="D32" s="6">
-        <v>4.0609534836609498E-3</v>
-      </c>
-      <c r="E32" s="18"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="1">
-        <v>10</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.6197936532585901E-3</v>
-      </c>
-      <c r="E33" s="18"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="E13:E23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2.81366470929909E-3</v>
-      </c>
-      <c r="E2" s="19">
-        <f>AVERAGE(D2:D12)</f>
-        <v>2.8589718670011272E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2.9086299843656201E-3</v>
-      </c>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2.8725109233065098E-3</v>
-      </c>
-      <c r="E4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>2.7472220866062401E-3</v>
-      </c>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2.8395079487722498E-3</v>
-      </c>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2.9094927500167801E-3</v>
-      </c>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2.9300338678111201E-3</v>
-      </c>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2.8954508177678399E-3</v>
-      </c>
-      <c r="E9" s="18"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2.86130290885414E-3</v>
-      </c>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2.8834394576333199E-3</v>
-      </c>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="1">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2.7874350825794901E-3</v>
-      </c>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2.4381599990933901E-3</v>
-      </c>
-      <c r="E13" s="19">
-        <f>AVERAGE(D13:D23)</f>
-        <v>2.6530523100631071E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2.6282434237133502E-3</v>
-      </c>
-      <c r="E14" s="18"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="1">
-        <v>3</v>
-      </c>
-      <c r="D15" s="3">
-        <v>2.3461147455381701E-3</v>
-      </c>
-      <c r="E15" s="18"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2.7524372879068298E-3</v>
-      </c>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="1">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>3.2472745789499402E-3</v>
-      </c>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="1">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3">
-        <v>2.5237854282296E-3</v>
-      </c>
-      <c r="E18" s="18"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="1">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3">
-        <v>2.9887873260404599E-3</v>
-      </c>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="1">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>2.06526349558706E-3</v>
-      </c>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="1">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3">
-        <v>2.6816447983030599E-3</v>
-      </c>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="1">
-        <v>10</v>
-      </c>
-      <c r="D22" s="3">
-        <v>2.7565596821078398E-3</v>
-      </c>
-      <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="1">
-        <v>11</v>
-      </c>
-      <c r="D23" s="3">
-        <v>2.7553046452244798E-3</v>
-      </c>
-      <c r="E23" s="18"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3.3099004965032601E-3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>AVERAGE(D24:D33)</f>
-        <v>2.4948066730810809E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="1">
-        <v>2</v>
-      </c>
-      <c r="D25" s="3">
-        <v>2.0223762558382102E-3</v>
-      </c>
-      <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="1">
-        <v>3</v>
-      </c>
-      <c r="D26" s="3">
-        <v>2.48460504443907E-3</v>
-      </c>
-      <c r="E26" s="18"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="1">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3">
-        <v>2.1925517311301699E-3</v>
-      </c>
-      <c r="E27" s="18"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="1">
-        <v>5</v>
-      </c>
-      <c r="D28" s="3">
-        <v>2.0210547846704601E-3</v>
-      </c>
-      <c r="E28" s="18"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="1">
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>2.32727791187156E-3</v>
-      </c>
-      <c r="E29" s="18"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="1">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3.3527282363668498E-3</v>
-      </c>
-      <c r="E30" s="18"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="1">
-        <v>8</v>
-      </c>
-      <c r="D31" s="3">
-        <v>2.00939520752292E-3</v>
-      </c>
-      <c r="E31" s="18"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="1">
-        <v>9</v>
-      </c>
-      <c r="D32" s="3">
-        <v>2.9226176336739399E-3</v>
-      </c>
-      <c r="E32" s="18"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="1">
-        <v>10</v>
-      </c>
-      <c r="D33" s="3">
-        <v>2.3055594287943698E-3</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="G33" s="4">
-        <v>2.3055594287943698E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>5</v>
       </c>

--- a/_resultados.xlsx
+++ b/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91663962-28B9-4AA6-9328-0190CC44291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F4646A-49DC-4A60-BF09-1E955C7E40F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="752" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capa" sheetId="19" r:id="rId1"/>
@@ -19,12 +19,16 @@
     <sheet name="Activity-64-08" sheetId="22" r:id="rId4"/>
     <sheet name="Age-16-08" sheetId="23" r:id="rId5"/>
     <sheet name="Age-32-16" sheetId="24" r:id="rId6"/>
-    <sheet name="Activity" sheetId="12" r:id="rId7"/>
-    <sheet name="Activity (2)" sheetId="16" r:id="rId8"/>
-    <sheet name="Age" sheetId="13" r:id="rId9"/>
-    <sheet name="Age (2)" sheetId="17" r:id="rId10"/>
-    <sheet name="Gender" sheetId="15" r:id="rId11"/>
-    <sheet name="Gender (2)" sheetId="18" r:id="rId12"/>
+    <sheet name="Age-64-08" sheetId="25" r:id="rId7"/>
+    <sheet name="Gender-16-08" sheetId="26" r:id="rId8"/>
+    <sheet name="Gender-32-16" sheetId="27" r:id="rId9"/>
+    <sheet name="Gender-64-08" sheetId="28" r:id="rId10"/>
+    <sheet name="Activity" sheetId="12" r:id="rId11"/>
+    <sheet name="Activity (2)" sheetId="16" r:id="rId12"/>
+    <sheet name="Age" sheetId="13" r:id="rId13"/>
+    <sheet name="Age (2)" sheetId="17" r:id="rId14"/>
+    <sheet name="Gender" sheetId="15" r:id="rId15"/>
+    <sheet name="Gender (2)" sheetId="18" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -103,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="32">
   <si>
     <t>Estratégia</t>
   </si>
@@ -246,121 +250,19 @@
     <t>OK</t>
   </si>
   <si>
-    <t>Acer</t>
+    <t>0.002666330037271747</t>
   </si>
   <si>
-    <t>0.00008426125272287793</t>
+    <t>0.0025990501236971605</t>
   </si>
   <si>
-    <t>0.00028513611841457607</t>
+    <t>0.003462425292078889</t>
   </si>
   <si>
-    <t>0.000050230047639008845</t>
+    <t>0.002509717874034078</t>
   </si>
   <si>
-    <t>0.000020788333344080723</t>
-  </si>
-  <si>
-    <t>0.000018828346608490786</t>
-  </si>
-  <si>
-    <t>0.00019055804285282577</t>
-  </si>
-  <si>
-    <t>0.00000011082249822523104</t>
-  </si>
-  <si>
-    <t>0.0011675693782395708</t>
-  </si>
-  <si>
-    <t>0.00011459477836536617</t>
-  </si>
-  <si>
-    <t>0.00026680757261041794</t>
-  </si>
-  <si>
-    <t>0.00002832089405266678</t>
-  </si>
-  <si>
-    <t>0.00063205634573782</t>
-  </si>
-  <si>
-    <t>0.00009644672571143702</t>
-  </si>
-  <si>
-    <t>0.0004641752089120271</t>
-  </si>
-  <si>
-    <t>0.000022112568939252295</t>
-  </si>
-  <si>
-    <t>0.00031302763264424874</t>
-  </si>
-  <si>
-    <t>0.00015868389007219052</t>
-  </si>
-  <si>
-    <t>0.0001787146627812362</t>
-  </si>
-  <si>
-    <t>0.00003507727378722661</t>
-  </si>
-  <si>
-    <t>0.00019027668158216087</t>
-  </si>
-  <si>
-    <t>0.00003155995639270873</t>
-  </si>
-  <si>
-    <t>0.000010776308118814108</t>
-  </si>
-  <si>
-    <t>0.0001930182772226571</t>
-  </si>
-  <si>
-    <t>0.008443821545302503</t>
-  </si>
-  <si>
-    <t>0.008070676710282543</t>
-  </si>
-  <si>
-    <t>0.008522991666268442</t>
-  </si>
-  <si>
-    <t>0.008634708847753853</t>
-  </si>
-  <si>
-    <t>0.008175585403801599</t>
-  </si>
-  <si>
-    <t>0.008667483608796909</t>
-  </si>
-  <si>
-    <t>0.008103717141672313</t>
-  </si>
-  <si>
-    <t>0.00611422684128972</t>
-  </si>
-  <si>
-    <t>0.007267212046696717</t>
-  </si>
-  <si>
-    <t>0.0007374246121511659</t>
-  </si>
-  <si>
-    <t>0.0007686661271804426</t>
-  </si>
-  <si>
-    <t>0.006555385749806815</t>
-  </si>
-  <si>
-    <t>0.008095271064024735</t>
-  </si>
-  <si>
-    <t>0.006792237065817606</t>
-  </si>
-  <si>
-    <t>0.006794999836867685</t>
+    <t>0.0030225800040082212</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1013,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="11"/>
     </row>
@@ -1121,11 +1023,9 @@
         <v>16</v>
       </c>
       <c r="C21" s="9">
-        <v>5</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>27</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
@@ -1144,7 +1044,9 @@
       <c r="B23" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="9">
+        <v>1</v>
+      </c>
       <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1153,11 +1055,9 @@
         <v>16</v>
       </c>
       <c r="C24" s="9">
-        <v>5</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>27</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
@@ -1192,7 +1092,1823 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20BD1F9-62CA-44DC-A5CE-8C5DA9DAF053}">
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>3.0920022508217999E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D21)</f>
+        <v>3.1256884455689421E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.13315433431677E-3</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.1411312925742102E-3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.1573542739626601E-3</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.11461066896262E-3</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3.0755827580487001E-3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.1378100547576099E-3</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.1360280163418002E-3</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.0985918500267499E-3</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3.11555145173975E-3</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.1007001009200601E-3</v>
+      </c>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.0922012907448199E-3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3.0977706333334002E-3</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <v>3.1153368952903599E-3</v>
+      </c>
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3.16554777312934E-3</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.1022443794083499E-3</v>
+      </c>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.1451697098806202E-3</v>
+      </c>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3.1900381402986898E-3</v>
+      </c>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3.18892839528421E-3</v>
+      </c>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3.1140146415363202E-3</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.9792748738964201E-3</v>
+      </c>
+      <c r="E22" s="19">
+        <f>AVERAGE(D22:D41)</f>
+        <v>2.9680677649702742E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.9679755243615701E-3</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2.9504060931560801E-3</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.9215257255345499E-3</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.98513418775701E-3</v>
+      </c>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.9503345790937502E-3</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.98048783775874E-3</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3">
+        <v>3.0004543275332801E-3</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2.99082732798791E-3</v>
+      </c>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.9956675897422598E-3</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2.9310222701132102E-3</v>
+      </c>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.95895775653532E-3</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2.9080186123031601E-3</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2.9976445820983802E-3</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2.99135301031846E-3</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2.93944217966751E-3</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2.9805237852297598E-3</v>
+      </c>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2.9734151550055402E-3</v>
+      </c>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.9515519908248598E-3</v>
+      </c>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3">
+        <v>3.0073378904877201E-3</v>
+      </c>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2.9645603213727602E-3</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>2.9732065291103301E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>2.98719720091428E-3</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>2.95059546374061E-3</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2.95332224000644E-3</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2.9326702319878999E-3</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2.9413346206857501E-3</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>3.0173528517228399E-3</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.94944032255649E-3</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2.9929636587451899E-3</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3">
+        <v>2.9677695656245302E-3</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3">
+        <v>2.9917128136115099E-3</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3">
+        <v>3.0124680132109002E-3</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3">
+        <v>2.9856750520879001E-3</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2.97057733204853E-3</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2.9823883275159999E-3</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3">
+        <v>2.9804566382339499E-3</v>
+      </c>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3">
+        <v>2.93516884069206E-3</v>
+      </c>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3">
+        <v>3.00060505017753E-3</v>
+      </c>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3">
+        <v>2.9465445724206401E-3</v>
+      </c>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3">
+        <v>3.0013274648507901E-3</v>
+      </c>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" s="19" t="e">
+        <f>AVERAGE(D62:D81)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1.22740707443255E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D12)</f>
+        <v>1.3405988398128117E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.5217850441141701E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.4187702239963399E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.21923057588587E-3</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1.2107251197056299E-3</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.5994412310248701E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1.3964272541872899E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.5234914987065399E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.14432918115938E-3</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.29480134619695E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.1901786885313401E-3</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.76494351019696E-4</v>
+      </c>
+      <c r="E13" s="21">
+        <f>AVERAGE(D13:D23)</f>
+        <v>4.6044642516324585E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5.46025356640438E-4</v>
+      </c>
+      <c r="E14" s="22"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.7489087688418899E-4</v>
+      </c>
+      <c r="E15" s="22"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>4.5331415788522699E-4</v>
+      </c>
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>4.5224030226177498E-4</v>
+      </c>
+      <c r="E17" s="22"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3.25042909349475E-4</v>
+      </c>
+      <c r="E18" s="22"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5.4759582523591596E-4</v>
+      </c>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3">
+        <v>4.0296400000000003E-5</v>
+      </c>
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8.9001901515576199E-4</v>
+      </c>
+      <c r="E21" s="22"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8.6876944325313898E-4</v>
+      </c>
+      <c r="E22" s="22"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5.9022203911008697E-4</v>
+      </c>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.73793482370665E-4</v>
+      </c>
+      <c r="E24" s="19">
+        <f>AVERAGE(D24:D33)</f>
+        <v>2.0032376576300951E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4.4079599999999997E-5</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1.9820721733818201E-4</v>
+      </c>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.6898882604876098E-4</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>9.9348000000000002E-6</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1.70899292234211E-4</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3.7644454634369102E-4</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.5758852866904895E-5</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3">
+        <v>4.9271851899704603E-4</v>
+      </c>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1.9241252143063401E-4</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C042F672-E41D-468F-9A40-AB573A878B0F}">
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D15)</f>
+        <v>1.4591194330376932E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1.5217850441141701E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1.4187702239963399E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.5994412310248701E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.3964272541872899E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.5234914987065399E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.29480134619695E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="21">
+        <f>AVERAGE(D16:D26)</f>
+        <v>6.4932430621342815E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7">
+        <v>5.46025356640438E-4</v>
+      </c>
+      <c r="E17" s="22"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="1">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="22"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4.5331415788522699E-4</v>
+      </c>
+      <c r="E19" s="22"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="1">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="1">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="22"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="1">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7">
+        <v>5.4759582523591596E-4</v>
+      </c>
+      <c r="E22" s="22"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="1">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="22"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="1">
+        <v>9</v>
+      </c>
+      <c r="D24" s="7">
+        <v>8.9001901515576199E-4</v>
+      </c>
+      <c r="E24" s="22"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="1">
+        <v>10</v>
+      </c>
+      <c r="D25" s="7">
+        <v>8.6876944325313898E-4</v>
+      </c>
+      <c r="E25" s="22"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="1">
+        <v>11</v>
+      </c>
+      <c r="D26" s="7">
+        <v>5.9022203911008697E-4</v>
+      </c>
+      <c r="E26" s="23"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1.73793482370665E-4</v>
+      </c>
+      <c r="E27" s="19">
+        <f>AVERAGE(D27:D40)</f>
+        <v>2.1330410891497666E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3">
+        <v>4.4079599999999997E-5</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1.9820721733818201E-4</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>4</v>
+      </c>
+      <c r="D30" s="3">
+        <v>2.6898882604876098E-4</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3">
+        <v>9.9348000000000002E-6</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>6</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1.70899292234211E-4</v>
+      </c>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3">
+        <v>3.7644454634369102E-4</v>
+      </c>
+      <c r="E33" s="18"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>8</v>
+      </c>
+      <c r="D34" s="3">
+        <v>7.5758852866904895E-5</v>
+      </c>
+      <c r="E34" s="18"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>9</v>
+      </c>
+      <c r="D35" s="3">
+        <v>4.9271851899704603E-4</v>
+      </c>
+      <c r="E35" s="18"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>10</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1.9241252143063401E-4</v>
+      </c>
+      <c r="E36" s="18"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3">
+        <v>3.3565148161274601E-4</v>
+      </c>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>12</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1.2738871373007399E-4</v>
+      </c>
+      <c r="E38" s="18"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>13</v>
+      </c>
+      <c r="D39" s="3">
+        <v>3.4164426510307702E-4</v>
+      </c>
+      <c r="E39" s="18"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>14</v>
+      </c>
+      <c r="D40" s="6">
+        <v>1.78335406733681E-4</v>
+      </c>
+      <c r="E40" s="18"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A2:A40"/>
+    <mergeCell ref="B2:B15"/>
+    <mergeCell ref="E2:E15"/>
+    <mergeCell ref="B16:B26"/>
+    <mergeCell ref="E16:E26"/>
+    <mergeCell ref="B27:B40"/>
+    <mergeCell ref="E27:E40"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1212,7 +2928,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1229,10 +2945,12 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3">
+        <v>6.8494550335423199E-3</v>
+      </c>
       <c r="E2" s="19">
         <f>AVERAGE(D2:D12)</f>
-        <v>7.5204771451239999E-3</v>
+        <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1241,7 +2959,7 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="3">
         <v>7.7222014481316001E-3</v>
       </c>
       <c r="E3" s="18"/>
@@ -1252,7 +2970,7 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="3">
         <v>7.4276032951078701E-3</v>
       </c>
       <c r="E4" s="18"/>
@@ -1263,7 +2981,9 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>6.9163642363323698E-3</v>
+      </c>
       <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1272,7 +2992,9 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>7.1247468487415202E-3</v>
+      </c>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1281,7 +3003,7 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>7.9683523176790998E-3</v>
       </c>
       <c r="E7" s="18"/>
@@ -1292,7 +3014,7 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>7.1325304703669396E-3</v>
       </c>
       <c r="E8" s="18"/>
@@ -1303,7 +3025,7 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="3">
         <v>7.6723666731501597E-3</v>
       </c>
       <c r="E9" s="18"/>
@@ -1314,7 +3036,9 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3">
+        <v>6.44864466466859E-3</v>
+      </c>
       <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1323,7 +3047,7 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="3">
         <v>7.1998086663083299E-3</v>
       </c>
       <c r="E11" s="18"/>
@@ -1334,7 +3058,9 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <v>6.8408648336931201E-3</v>
+      </c>
       <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1345,10 +3071,12 @@
       <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>4.4059430113216501E-3</v>
+      </c>
       <c r="E13" s="19">
         <f>AVERAGE(D13:D23)</f>
-        <v>6.5940540634390936E-3</v>
+        <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1357,7 +3085,7 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>6.0285373262784596E-3</v>
       </c>
       <c r="E14" s="18"/>
@@ -1368,7 +3096,9 @@
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>4.6542086132795998E-3</v>
+      </c>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1377,7 +3107,7 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="3">
         <v>5.4842343524997596E-3</v>
       </c>
       <c r="E16" s="18"/>
@@ -1388,7 +3118,9 @@
       <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>5.2386490268761304E-3</v>
+      </c>
       <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1397,7 +3129,9 @@
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>4.5414210107642796E-3</v>
+      </c>
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1406,7 +3140,7 @@
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="3">
         <v>6.4272965329950603E-3</v>
       </c>
       <c r="E19" s="18"/>
@@ -1417,7 +3151,9 @@
       <c r="C20" s="1">
         <v>8</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>3.38376634582825E-3</v>
+      </c>
       <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1426,7 +3162,7 @@
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="3">
         <v>7.5523987537550697E-3</v>
       </c>
       <c r="E21" s="18"/>
@@ -1437,7 +3173,7 @@
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="3">
         <v>7.6800340233492996E-3</v>
       </c>
       <c r="E22" s="18"/>
@@ -1448,7 +3184,7 @@
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="3">
         <v>6.3918233917569199E-3</v>
       </c>
       <c r="E23" s="18"/>
@@ -1486,7 +3222,7 @@
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="3">
         <v>3.2861956035523401E-3</v>
       </c>
       <c r="E26" s="18"/>
@@ -1497,7 +3233,7 @@
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="3">
         <v>4.1621944755989501E-3</v>
       </c>
       <c r="E27" s="18"/>
@@ -1530,7 +3266,7 @@
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="3">
         <v>3.3675964367588002E-3</v>
       </c>
       <c r="E30" s="18"/>
@@ -1541,7 +3277,7 @@
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="3">
         <v>2.7372032922601602E-3</v>
       </c>
       <c r="E31" s="18"/>
@@ -1552,7 +3288,7 @@
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="3">
         <v>4.0609534836609498E-3</v>
       </c>
       <c r="E32" s="18"/>
@@ -1563,7 +3299,7 @@
       <c r="C33" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="3">
         <v>3.6197936532585901E-3</v>
       </c>
       <c r="E33" s="18"/>
@@ -1593,8 +3329,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B8560C-6760-4F2C-BEB3-D4C8A79DCAAF}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1623,7 +3359,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>6</v>
@@ -1631,12 +3367,10 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
-        <v>2.81366470929909E-3</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="19">
         <f>AVERAGE(D2:D12)</f>
-        <v>2.8589718670011272E-3</v>
+        <v>7.5204771451239999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1645,8 +3379,8 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
-        <v>2.9086299843656201E-3</v>
+      <c r="D3" s="7">
+        <v>7.7222014481316001E-3</v>
       </c>
       <c r="E3" s="18"/>
     </row>
@@ -1656,8 +3390,8 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
-        <v>2.8725109233065098E-3</v>
+      <c r="D4" s="7">
+        <v>7.4276032951078701E-3</v>
       </c>
       <c r="E4" s="18"/>
     </row>
@@ -1667,9 +3401,7 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
-        <v>2.7472220866062401E-3</v>
-      </c>
+      <c r="D5" s="3"/>
       <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1678,9 +3410,7 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3">
-        <v>2.8395079487722498E-3</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1689,8 +3419,8 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="3">
-        <v>2.9094927500167801E-3</v>
+      <c r="D7" s="7">
+        <v>7.9683523176790998E-3</v>
       </c>
       <c r="E7" s="18"/>
     </row>
@@ -1700,8 +3430,8 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
-        <v>2.9300338678111201E-3</v>
+      <c r="D8" s="7">
+        <v>7.1325304703669396E-3</v>
       </c>
       <c r="E8" s="18"/>
     </row>
@@ -1711,8 +3441,8 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="3">
-        <v>2.8954508177678399E-3</v>
+      <c r="D9" s="7">
+        <v>7.6723666731501597E-3</v>
       </c>
       <c r="E9" s="18"/>
     </row>
@@ -1722,9 +3452,7 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3">
-        <v>2.86130290885414E-3</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1733,8 +3461,8 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="3">
-        <v>2.8834394576333199E-3</v>
+      <c r="D11" s="7">
+        <v>7.1998086663083299E-3</v>
       </c>
       <c r="E11" s="18"/>
     </row>
@@ -1744,9 +3472,7 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3">
-        <v>2.7874350825794901E-3</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1757,12 +3483,10 @@
       <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="D13" s="3">
-        <v>2.4381599990933901E-3</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="19">
         <f>AVERAGE(D13:D23)</f>
-        <v>2.6530523100631071E-3</v>
+        <v>6.5940540634390936E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1771,8 +3495,8 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="3">
-        <v>2.6282434237133502E-3</v>
+      <c r="D14" s="7">
+        <v>6.0285373262784596E-3</v>
       </c>
       <c r="E14" s="18"/>
     </row>
@@ -1782,9 +3506,7 @@
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="3">
-        <v>2.3461147455381701E-3</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1793,8 +3515,8 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="3">
-        <v>2.7524372879068298E-3</v>
+      <c r="D16" s="7">
+        <v>5.4842343524997596E-3</v>
       </c>
       <c r="E16" s="18"/>
     </row>
@@ -1804,9 +3526,7 @@
       <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="3">
-        <v>3.2472745789499402E-3</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1815,9 +3535,7 @@
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="3">
-        <v>2.5237854282296E-3</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1826,8 +3544,8 @@
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="3">
-        <v>2.9887873260404599E-3</v>
+      <c r="D19" s="7">
+        <v>6.4272965329950603E-3</v>
       </c>
       <c r="E19" s="18"/>
     </row>
@@ -1837,9 +3555,7 @@
       <c r="C20" s="1">
         <v>8</v>
       </c>
-      <c r="D20" s="3">
-        <v>2.06526349558706E-3</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1848,8 +3564,8 @@
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="3">
-        <v>2.6816447983030599E-3</v>
+      <c r="D21" s="7">
+        <v>7.5523987537550697E-3</v>
       </c>
       <c r="E21" s="18"/>
     </row>
@@ -1859,8 +3575,8 @@
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="3">
-        <v>2.7565596821078398E-3</v>
+      <c r="D22" s="7">
+        <v>7.6800340233492996E-3</v>
       </c>
       <c r="E22" s="18"/>
     </row>
@@ -1870,8 +3586,8 @@
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="3">
-        <v>2.7553046452244798E-3</v>
+      <c r="D23" s="7">
+        <v>6.3918233917569199E-3</v>
       </c>
       <c r="E23" s="18"/>
     </row>
@@ -1884,11 +3600,11 @@
         <v>1</v>
       </c>
       <c r="D24" s="3">
-        <v>3.3099004965032601E-3</v>
+        <v>6.8834568210915997E-3</v>
       </c>
       <c r="E24" s="19">
         <f>AVERAGE(D24:D33)</f>
-        <v>2.4948066730810809E-3</v>
+        <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1898,7 +3614,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="3">
-        <v>2.0223762558382102E-3</v>
+        <v>5.9727451086721804E-3</v>
       </c>
       <c r="E25" s="18"/>
     </row>
@@ -1908,8 +3624,8 @@
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="3">
-        <v>2.48460504443907E-3</v>
+      <c r="D26" s="6">
+        <v>3.2861956035523401E-3</v>
       </c>
       <c r="E26" s="18"/>
     </row>
@@ -1919,8 +3635,8 @@
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="3">
-        <v>2.1925517311301699E-3</v>
+      <c r="D27" s="6">
+        <v>4.1621944755989501E-3</v>
       </c>
       <c r="E27" s="18"/>
     </row>
@@ -1931,7 +3647,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="3">
-        <v>2.0210547846704601E-3</v>
+        <v>6.0968354981954303E-3</v>
       </c>
       <c r="E28" s="18"/>
     </row>
@@ -1942,7 +3658,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="3">
-        <v>2.32727791187156E-3</v>
+        <v>6.8318852941438796E-3</v>
       </c>
       <c r="E29" s="18"/>
     </row>
@@ -1952,8 +3668,8 @@
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="3">
-        <v>3.3527282363668498E-3</v>
+      <c r="D30" s="6">
+        <v>3.3675964367588002E-3</v>
       </c>
       <c r="E30" s="18"/>
     </row>
@@ -1963,8 +3679,8 @@
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="3">
-        <v>2.00939520752292E-3</v>
+      <c r="D31" s="6">
+        <v>2.7372032922601602E-3</v>
       </c>
       <c r="E31" s="18"/>
     </row>
@@ -1974,26 +3690,23 @@
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="3">
-        <v>2.9226176336739399E-3</v>
+      <c r="D32" s="6">
+        <v>4.0609534836609498E-3</v>
       </c>
       <c r="E32" s="18"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="3">
-        <v>2.3055594287943698E-3</v>
+      <c r="D33" s="6">
+        <v>3.6197936532585901E-3</v>
       </c>
       <c r="E33" s="18"/>
-      <c r="G33" s="4">
-        <v>2.3055594287943698E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>5</v>
       </c>
@@ -2018,7 +3731,432 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.81366470929909E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D12)</f>
+        <v>2.8589718670011272E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.9086299843656201E-3</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.8725109233065098E-3</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.7472220866062401E-3</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.8395079487722498E-3</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.9094927500167801E-3</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.9300338678111201E-3</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.8954508177678399E-3</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.86130290885414E-3</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.8834394576333199E-3</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.7874350825794901E-3</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.4381599990933901E-3</v>
+      </c>
+      <c r="E13" s="19">
+        <f>AVERAGE(D13:D23)</f>
+        <v>2.6530523100631071E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2.6282434237133502E-3</v>
+      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2.3461147455381701E-3</v>
+      </c>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.7524372879068298E-3</v>
+      </c>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3.2472745789499402E-3</v>
+      </c>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2.5237854282296E-3</v>
+      </c>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2.9887873260404599E-3</v>
+      </c>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.06526349558706E-3</v>
+      </c>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.6816447983030599E-3</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="1">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.7565596821078398E-3</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.7553046452244798E-3</v>
+      </c>
+      <c r="E23" s="18"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3.3099004965032601E-3</v>
+      </c>
+      <c r="E24" s="19">
+        <f>AVERAGE(D24:D33)</f>
+        <v>2.4948066730810809E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.0223762558382102E-3</v>
+      </c>
+      <c r="E25" s="18"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2.48460504443907E-3</v>
+      </c>
+      <c r="E26" s="18"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>4</v>
+      </c>
+      <c r="D27" s="3">
+        <v>2.1925517311301699E-3</v>
+      </c>
+      <c r="E27" s="18"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3">
+        <v>2.0210547846704601E-3</v>
+      </c>
+      <c r="E28" s="18"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>2.32727791187156E-3</v>
+      </c>
+      <c r="E29" s="18"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
+        <v>3.3527282363668498E-3</v>
+      </c>
+      <c r="E30" s="18"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.00939520752292E-3</v>
+      </c>
+      <c r="E31" s="18"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2.9226176336739399E-3</v>
+      </c>
+      <c r="E32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>10</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.3055594287943698E-3</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="G33" s="4">
+        <v>2.3055594287943698E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="E2:E12"/>
+    <mergeCell ref="B13:B23"/>
+    <mergeCell ref="E13:E23"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="E24:E33"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{905FDE81-1C1B-4B15-90FD-7441C7029F15}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3343,18 +5481,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
     <mergeCell ref="A2:A21"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A81"/>
-    <mergeCell ref="B62:B81"/>
-    <mergeCell ref="E62:E81"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4272,18 +6410,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5010,12 +7148,12 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E62" s="19" t="e">
+      <c r="D62" s="3">
+        <v>8.4261252722877902E-5</v>
+      </c>
+      <c r="E62" s="19">
         <f>AVERAGE(D62:D84)</f>
-        <v>#DIV/0!</v>
+        <v>1.9796222257608179E-4</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -5024,8 +7162,8 @@
       <c r="C63" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>29</v>
+      <c r="D63" s="3">
+        <v>2.8513611841457601E-4</v>
       </c>
       <c r="E63" s="19"/>
     </row>
@@ -5035,8 +7173,8 @@
       <c r="C64" s="1">
         <v>3</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>30</v>
+      <c r="D64" s="3">
+        <v>5.0230047639008798E-5</v>
       </c>
       <c r="E64" s="19"/>
     </row>
@@ -5046,8 +7184,8 @@
       <c r="C65" s="1">
         <v>4</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>31</v>
+      <c r="D65" s="3">
+        <v>2.07883333440807E-5</v>
       </c>
       <c r="E65" s="19"/>
     </row>
@@ -5057,8 +7195,8 @@
       <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>32</v>
+      <c r="D66" s="3">
+        <v>1.8828346608490698E-5</v>
       </c>
       <c r="E66" s="19"/>
     </row>
@@ -5068,8 +7206,8 @@
       <c r="C67" s="1">
         <v>6</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>33</v>
+      <c r="D67" s="3">
+        <v>1.9055804285282501E-4</v>
       </c>
       <c r="E67" s="19"/>
     </row>
@@ -5079,8 +7217,8 @@
       <c r="C68" s="1">
         <v>7</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>34</v>
+      <c r="D68" s="3">
+        <v>1.10822498225231E-7</v>
       </c>
       <c r="E68" s="19"/>
     </row>
@@ -5090,8 +7228,8 @@
       <c r="C69" s="1">
         <v>8</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>35</v>
+      <c r="D69" s="3">
+        <v>1.1675693782395699E-3</v>
       </c>
       <c r="E69" s="19"/>
     </row>
@@ -5101,8 +7239,8 @@
       <c r="C70" s="1">
         <v>9</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>36</v>
+      <c r="D70" s="3">
+        <v>1.14594778365366E-4</v>
       </c>
       <c r="E70" s="19"/>
     </row>
@@ -5112,8 +7250,8 @@
       <c r="C71" s="1">
         <v>10</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>37</v>
+      <c r="D71" s="3">
+        <v>2.6680757261041702E-4</v>
       </c>
       <c r="E71" s="19"/>
     </row>
@@ -5123,8 +7261,8 @@
       <c r="C72" s="1">
         <v>11</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>38</v>
+      <c r="D72" s="3">
+        <v>2.8320894052666702E-5</v>
       </c>
       <c r="E72" s="19"/>
     </row>
@@ -5134,8 +7272,8 @@
       <c r="C73" s="1">
         <v>12</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>39</v>
+      <c r="D73" s="3">
+        <v>6.3205634573781997E-4</v>
       </c>
       <c r="E73" s="19"/>
     </row>
@@ -5145,8 +7283,8 @@
       <c r="C74" s="1">
         <v>13</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>40</v>
+      <c r="D74" s="3">
+        <v>9.6446725711436994E-5</v>
       </c>
       <c r="E74" s="19"/>
     </row>
@@ -5156,8 +7294,8 @@
       <c r="C75" s="1">
         <v>14</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>41</v>
+      <c r="D75" s="3">
+        <v>4.6417520891202699E-4</v>
       </c>
       <c r="E75" s="19"/>
     </row>
@@ -5167,8 +7305,8 @@
       <c r="C76" s="1">
         <v>15</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>42</v>
+      <c r="D76" s="3">
+        <v>2.2112568939252201E-5</v>
       </c>
       <c r="E76" s="19"/>
     </row>
@@ -5178,8 +7316,8 @@
       <c r="C77" s="1">
         <v>16</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>43</v>
+      <c r="D77" s="3">
+        <v>3.1302763264424798E-4</v>
       </c>
       <c r="E77" s="19"/>
     </row>
@@ -5189,8 +7327,8 @@
       <c r="C78" s="1">
         <v>17</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>44</v>
+      <c r="D78" s="3">
+        <v>1.5868389007219001E-4</v>
       </c>
       <c r="E78" s="19"/>
     </row>
@@ -5200,8 +7338,8 @@
       <c r="C79" s="1">
         <v>18</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>45</v>
+      <c r="D79" s="3">
+        <v>1.7871466278123599E-4</v>
       </c>
       <c r="E79" s="19"/>
     </row>
@@ -5211,8 +7349,8 @@
       <c r="C80" s="1">
         <v>19</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>46</v>
+      <c r="D80" s="3">
+        <v>3.5077273787226597E-5</v>
       </c>
       <c r="E80" s="19"/>
     </row>
@@ -5222,8 +7360,8 @@
       <c r="C81" s="1">
         <v>20</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>47</v>
+      <c r="D81" s="3">
+        <v>1.9027668158216001E-4</v>
       </c>
       <c r="E81" s="19"/>
     </row>
@@ -5233,8 +7371,8 @@
       <c r="C82" s="1">
         <v>21</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>48</v>
+      <c r="D82" s="3">
+        <v>3.1559956392708702E-5</v>
       </c>
       <c r="E82" s="19"/>
     </row>
@@ -5244,8 +7382,8 @@
       <c r="C83" s="1">
         <v>22</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>49</v>
+      <c r="D83" s="3">
+        <v>1.07763081188141E-5</v>
       </c>
       <c r="E83" s="19"/>
     </row>
@@ -5255,25 +7393,25 @@
       <c r="C84" s="1">
         <v>23</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>50</v>
+      <c r="D84" s="3">
+        <v>1.9301827722265701E-4</v>
       </c>
       <c r="E84" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A84"/>
+    <mergeCell ref="B62:B84"/>
+    <mergeCell ref="E62:E84"/>
     <mergeCell ref="A2:A21"/>
     <mergeCell ref="B2:B21"/>
     <mergeCell ref="E2:E21"/>
     <mergeCell ref="A22:A41"/>
     <mergeCell ref="B22:B41"/>
     <mergeCell ref="E22:E41"/>
-    <mergeCell ref="A42:A61"/>
-    <mergeCell ref="B42:B61"/>
-    <mergeCell ref="E42:E61"/>
-    <mergeCell ref="A62:A84"/>
-    <mergeCell ref="B62:B84"/>
-    <mergeCell ref="E62:E84"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6005,7 +8143,7 @@
       </c>
       <c r="E62" s="19">
         <f>AVERAGE(D62:D81)</f>
-        <v>6.5500486795894604E-3</v>
+        <v>5.7762223120384768E-3</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -6025,7 +8163,9 @@
       <c r="C64" s="1">
         <v>3</v>
       </c>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3">
+        <v>4.2285695769365096E-3</v>
+      </c>
       <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -6183,18 +8323,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
     <mergeCell ref="A42:A61"/>
     <mergeCell ref="B42:B61"/>
     <mergeCell ref="E42:E61"/>
     <mergeCell ref="A62:A81"/>
     <mergeCell ref="B62:B81"/>
     <mergeCell ref="E62:E81"/>
-    <mergeCell ref="A2:A21"/>
-    <mergeCell ref="B2:B21"/>
-    <mergeCell ref="E2:E21"/>
-    <mergeCell ref="A22:A41"/>
-    <mergeCell ref="B22:B41"/>
-    <mergeCell ref="E22:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6457,12 +8597,12 @@
       <c r="C22" s="1">
         <v>1</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="19" t="e">
+      <c r="D22" s="3">
+        <v>8.4438215453025E-3</v>
+      </c>
+      <c r="E22" s="19">
         <f>AVERAGE(D22:D41)</f>
-        <v>#DIV/0!</v>
+        <v>6.7829605511808659E-3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -6471,8 +8611,8 @@
       <c r="C23" s="1">
         <v>2</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>52</v>
+      <c r="D23" s="3">
+        <v>8.07067671028254E-3</v>
       </c>
       <c r="E23" s="19"/>
     </row>
@@ -6482,8 +8622,8 @@
       <c r="C24" s="1">
         <v>3</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>53</v>
+      <c r="D24" s="3">
+        <v>8.5229916662684403E-3</v>
       </c>
       <c r="E24" s="19"/>
     </row>
@@ -6493,8 +8633,8 @@
       <c r="C25" s="1">
         <v>4</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>54</v>
+      <c r="D25" s="3">
+        <v>8.6347088477538494E-3</v>
       </c>
       <c r="E25" s="19"/>
     </row>
@@ -6504,8 +8644,8 @@
       <c r="C26" s="1">
         <v>5</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>55</v>
+      <c r="D26" s="3">
+        <v>8.1755854038015902E-3</v>
       </c>
       <c r="E26" s="19"/>
     </row>
@@ -6515,8 +8655,8 @@
       <c r="C27" s="1">
         <v>6</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>56</v>
+      <c r="D27" s="3">
+        <v>8.6674836087969002E-3</v>
       </c>
       <c r="E27" s="19"/>
     </row>
@@ -6526,8 +8666,8 @@
       <c r="C28" s="1">
         <v>7</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>57</v>
+      <c r="D28" s="3">
+        <v>8.1037171416723092E-3</v>
       </c>
       <c r="E28" s="19"/>
     </row>
@@ -6537,8 +8677,8 @@
       <c r="C29" s="1">
         <v>8</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>58</v>
+      <c r="D29" s="3">
+        <v>6.1142268412897197E-3</v>
       </c>
       <c r="E29" s="19"/>
     </row>
@@ -6548,8 +8688,8 @@
       <c r="C30" s="1">
         <v>9</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>59</v>
+      <c r="D30" s="3">
+        <v>7.2672120466967102E-3</v>
       </c>
       <c r="E30" s="19"/>
     </row>
@@ -6559,8 +8699,8 @@
       <c r="C31" s="1">
         <v>10</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>60</v>
+      <c r="D31" s="3">
+        <v>7.3742461215116502E-4</v>
       </c>
       <c r="E31" s="19"/>
     </row>
@@ -6570,8 +8710,8 @@
       <c r="C32" s="1">
         <v>11</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>61</v>
+      <c r="D32" s="3">
+        <v>7.6866612718044195E-4</v>
       </c>
       <c r="E32" s="19"/>
     </row>
@@ -6581,8 +8721,8 @@
       <c r="C33" s="1">
         <v>12</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>62</v>
+      <c r="D33" s="3">
+        <v>6.5553857498068099E-3</v>
       </c>
       <c r="E33" s="19"/>
     </row>
@@ -6592,8 +8732,8 @@
       <c r="C34" s="1">
         <v>13</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>63</v>
+      <c r="D34" s="3">
+        <v>8.0952710640247293E-3</v>
       </c>
       <c r="E34" s="19"/>
     </row>
@@ -6603,8 +8743,8 @@
       <c r="C35" s="1">
         <v>14</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>64</v>
+      <c r="D35" s="3">
+        <v>6.7922370658176001E-3</v>
       </c>
       <c r="E35" s="19"/>
     </row>
@@ -6614,8 +8754,8 @@
       <c r="C36" s="1">
         <v>15</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>65</v>
+      <c r="D36" s="3">
+        <v>6.7949998368676797E-3</v>
       </c>
       <c r="E36" s="19"/>
     </row>
@@ -6881,10 +9021,12 @@
       <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="19" t="e">
+      <c r="D62" s="3">
+        <v>6.2516390259418301E-3</v>
+      </c>
+      <c r="E62" s="19">
         <f>AVERAGE(D62:D81)</f>
-        <v>#DIV/0!</v>
+        <v>7.4809309692636288E-3</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -6893,7 +9035,9 @@
       <c r="C63" s="1">
         <v>2</v>
       </c>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3">
+        <v>3.7268189374924498E-3</v>
+      </c>
       <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -6902,7 +9046,9 @@
       <c r="C64" s="1">
         <v>3</v>
       </c>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3">
+        <v>8.0098641848510201E-3</v>
+      </c>
       <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -6911,7 +9057,9 @@
       <c r="C65" s="1">
         <v>4</v>
       </c>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3">
+        <v>9.7651583782437292E-3</v>
+      </c>
       <c r="E65" s="19"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -6920,7 +9068,9 @@
       <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3">
+        <v>3.9790135573412504E-3</v>
+      </c>
       <c r="E66" s="19"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -6929,7 +9079,9 @@
       <c r="C67" s="1">
         <v>6</v>
       </c>
-      <c r="D67" s="3"/>
+      <c r="D67" s="3">
+        <v>9.5050643919983892E-3</v>
+      </c>
       <c r="E67" s="19"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -6938,7 +9090,9 @@
       <c r="C68" s="1">
         <v>7</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>7.4540737367528196E-3</v>
+      </c>
       <c r="E68" s="19"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -6947,7 +9101,9 @@
       <c r="C69" s="1">
         <v>8</v>
       </c>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3">
+        <v>7.4762744869634502E-3</v>
+      </c>
       <c r="E69" s="19"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -6956,7 +9112,9 @@
       <c r="C70" s="1">
         <v>9</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="3">
+        <v>7.5092264043993603E-3</v>
+      </c>
       <c r="E70" s="19"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -6965,7 +9123,9 @@
       <c r="C71" s="1">
         <v>10</v>
       </c>
-      <c r="D71" s="3"/>
+      <c r="D71" s="3">
+        <v>1.1132176588651999E-2</v>
+      </c>
       <c r="E71" s="19"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -7056,6 +9216,963 @@
         <v>20</v>
       </c>
       <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62FAC7C-936D-40C4-8BC1-6B039D7C594B}">
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>8.4564763474451396E-3</v>
+      </c>
+      <c r="E2" s="19">
+        <f>AVERAGE(D2:D21)</f>
+        <v>8.3775689176081962E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>8.4579754470519193E-3</v>
+      </c>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8.2395338144664702E-3</v>
+      </c>
+      <c r="E4" s="19"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8.2188412939552796E-3</v>
+      </c>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.4149180211845996E-3</v>
+      </c>
+      <c r="E6" s="19"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8.5156105887332408E-3</v>
+      </c>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8.2049425739000297E-3</v>
+      </c>
+      <c r="E8" s="19"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.4925237344880104E-3</v>
+      </c>
+      <c r="E9" s="19"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8.3018782971462403E-3</v>
+      </c>
+      <c r="E10" s="19"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3">
+        <v>8.5906098929944604E-3</v>
+      </c>
+      <c r="E11" s="19"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.3444735584454997E-3</v>
+      </c>
+      <c r="E12" s="19"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>8.2143235738836896E-3</v>
+      </c>
+      <c r="E13" s="19"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3">
+        <v>8.4570310019296806E-3</v>
+      </c>
+      <c r="E14" s="19"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.6144552867900605E-3</v>
+      </c>
+      <c r="E15" s="19"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3">
+        <v>8.1257031553689692E-3</v>
+      </c>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.3711222187129002E-3</v>
+      </c>
+      <c r="E17" s="19"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3">
+        <v>8.2991354195743102E-3</v>
+      </c>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3">
+        <v>8.5307542196958203E-3</v>
+      </c>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3">
+        <v>8.3505798597183906E-3</v>
+      </c>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8.3504900466792199E-3</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>7.5577295247130499E-3</v>
+      </c>
+      <c r="E22" s="19">
+        <f>AVERAGE(D22:D41)</f>
+        <v>7.2749862265618567E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>7.2577074212052698E-3</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
+        <v>7.36107308984894E-3</v>
+      </c>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="1">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3">
+        <v>7.0616200009351896E-3</v>
+      </c>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3">
+        <v>7.3173761848583001E-3</v>
+      </c>
+      <c r="E26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="3">
+        <v>7.2040915620434302E-3</v>
+      </c>
+      <c r="E27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.2691903502957603E-3</v>
+      </c>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="1">
+        <v>8</v>
+      </c>
+      <c r="D29" s="3">
+        <v>7.1158290547289798E-3</v>
+      </c>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="1">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3">
+        <v>7.2111694726930799E-3</v>
+      </c>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="1">
+        <v>10</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.47534653336571E-3</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="1">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3">
+        <v>7.2273882477084496E-3</v>
+      </c>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>7.1861727246906098E-3</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3">
+        <v>7.1926703981644597E-3</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3">
+        <v>7.02880127151861E-3</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3">
+        <v>7.41151943693465E-3</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3">
+        <v>7.3458161012885104E-3</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3">
+        <v>7.1972223872907998E-3</v>
+      </c>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3">
+        <v>7.3754548326963399E-3</v>
+      </c>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3">
+        <v>7.3361744762232102E-3</v>
+      </c>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3">
+        <v>7.3673714600338003E-3</v>
+      </c>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>6.9231224715440498E-3</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>7.0685121903172844E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>7.23446699361255E-3</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>6.9362388729810199E-3</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>7.4215696528995801E-3</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>7.0191034033137397E-3</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>6.7454033353900999E-3</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>7.4228302311956304E-3</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>6.9226508285290204E-3</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>7.0504886813189498E-3</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3">
+        <v>6.8973468735956797E-3</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3">
+        <v>6.9566541651100598E-3</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3">
+        <v>7.15130851496473E-3</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3">
+        <v>7.0931487203595E-3</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>6.9406552265025697E-3</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <v>7.2824898978663304E-3</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3">
+        <v>7.2034735341288299E-3</v>
+      </c>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3">
+        <v>6.8882537285240696E-3</v>
+      </c>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3">
+        <v>7.2040469720153801E-3</v>
+      </c>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3">
+        <v>7.3114041802669798E-3</v>
+      </c>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3">
+        <v>6.7655875222269197E-3</v>
+      </c>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3">
+        <v>4.6178389035990003E-3</v>
+      </c>
+      <c r="E62" s="19">
+        <f>AVERAGE(D62:D81)</f>
+        <v>6.1911150001234217E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3">
+        <v>6.5921379343750397E-3</v>
+      </c>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3">
+        <v>5.6444414267353398E-3</v>
+      </c>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3">
+        <v>5.4431003440307303E-3</v>
+      </c>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
+        <v>5</v>
+      </c>
+      <c r="D66" s="3">
+        <v>6.5498013841910003E-3</v>
+      </c>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3">
+        <v>7.2166332889887401E-3</v>
+      </c>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>6.1355844037008101E-3</v>
+      </c>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3">
+        <v>5.6572368936161996E-3</v>
+      </c>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3">
+        <v>6.0954117814058899E-3</v>
+      </c>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3">
+        <v>6.0153326284015799E-3</v>
+      </c>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3">
+        <v>6.9219512248241003E-3</v>
+      </c>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3">
+        <v>6.11397285318934E-3</v>
+      </c>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3">
+        <v>6.6072704713531598E-3</v>
+      </c>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3">
+        <v>7.1785748195853302E-3</v>
+      </c>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3">
+        <v>4.5666761759366997E-3</v>
+      </c>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3">
+        <v>4.9971736087931103E-3</v>
+      </c>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3">
+        <v>7.51178563251142E-3</v>
+      </c>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3">
+        <v>8.8176016343343207E-3</v>
+      </c>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3">
+        <v>5.9805013115278999E-3</v>
+      </c>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3">
+        <v>5.1592732813687302E-3</v>
+      </c>
       <c r="E81" s="19"/>
     </row>
   </sheetData>
@@ -7078,12 +10195,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
-  <dimension ref="A1:G35"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE7E7F09-A486-43FA-AFEC-982A1305ADE3}">
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="4"/>
     <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
@@ -7108,20 +10226,20 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>1.22740707443255E-3</v>
+        <v>2.81366470929909E-3</v>
       </c>
       <c r="E2" s="19">
-        <f>AVERAGE(D2:D12)</f>
-        <v>1.3405988398128117E-3</v>
+        <f>AVERAGE(D2:D21)</f>
+        <v>2.8513275848922217E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7131,9 +10249,9 @@
         <v>2</v>
       </c>
       <c r="D3" s="3">
-        <v>1.5217850441141701E-3</v>
-      </c>
-      <c r="E3" s="18"/>
+        <v>2.9086299843656201E-3</v>
+      </c>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="18"/>
@@ -7142,9 +10260,9 @@
         <v>3</v>
       </c>
       <c r="D4" s="3">
-        <v>1.4187702239963399E-3</v>
-      </c>
-      <c r="E4" s="18"/>
+        <v>2.8725109233065098E-3</v>
+      </c>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="18"/>
@@ -7153,9 +10271,9 @@
         <v>4</v>
       </c>
       <c r="D5" s="3">
-        <v>1.21923057588587E-3</v>
-      </c>
-      <c r="E5" s="18"/>
+        <v>2.7472220866062401E-3</v>
+      </c>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="18"/>
@@ -7164,9 +10282,9 @@
         <v>5</v>
       </c>
       <c r="D6" s="3">
-        <v>1.2107251197056299E-3</v>
-      </c>
-      <c r="E6" s="18"/>
+        <v>2.8395079487722498E-3</v>
+      </c>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="18"/>
@@ -7175,9 +10293,9 @@
         <v>6</v>
       </c>
       <c r="D7" s="3">
-        <v>1.5994412310248701E-3</v>
-      </c>
-      <c r="E7" s="18"/>
+        <v>2.9094927500167801E-3</v>
+      </c>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="18"/>
@@ -7186,9 +10304,9 @@
         <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>1.3964272541872899E-3</v>
-      </c>
-      <c r="E8" s="18"/>
+        <v>2.9300338678111201E-3</v>
+      </c>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -7197,9 +10315,9 @@
         <v>8</v>
       </c>
       <c r="D9" s="3">
-        <v>1.5234914987065399E-3</v>
-      </c>
-      <c r="E9" s="18"/>
+        <v>2.8954508177678399E-3</v>
+      </c>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
@@ -7208,9 +10326,9 @@
         <v>9</v>
       </c>
       <c r="D10" s="3">
-        <v>1.14432918115938E-3</v>
-      </c>
-      <c r="E10" s="18"/>
+        <v>2.86130290885414E-3</v>
+      </c>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
@@ -7219,9 +10337,9 @@
         <v>10</v>
       </c>
       <c r="D11" s="3">
-        <v>1.29480134619695E-3</v>
-      </c>
-      <c r="E11" s="18"/>
+        <v>2.8834394576333199E-3</v>
+      </c>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
@@ -7230,282 +10348,779 @@
         <v>11</v>
       </c>
       <c r="D12" s="3">
-        <v>1.1901786885313401E-3</v>
-      </c>
-      <c r="E12" s="18"/>
+        <v>2.7874350825794901E-3</v>
+      </c>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
-      <c r="B13" s="15" t="s">
-        <v>7</v>
-      </c>
+      <c r="B13" s="18"/>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3">
-        <v>1.76494351019696E-4</v>
-      </c>
-      <c r="E13" s="21">
-        <f>AVERAGE(D13:D23)</f>
-        <v>4.6044642516324585E-4</v>
-      </c>
+        <v>2.7525051153243401E-3</v>
+      </c>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
-      <c r="B14" s="16"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D14" s="3">
-        <v>5.46025356640438E-4</v>
-      </c>
-      <c r="E14" s="22"/>
+        <v>2.7662257224752101E-3</v>
+      </c>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
-      <c r="B15" s="16"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3">
-        <v>1.7489087688418899E-4</v>
-      </c>
-      <c r="E15" s="22"/>
+        <v>2.9406589041873102E-3</v>
+      </c>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="18"/>
-      <c r="B16" s="16"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3">
-        <v>4.5331415788522699E-4</v>
-      </c>
-      <c r="E16" s="22"/>
+        <v>2.8370305583636998E-3</v>
+      </c>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
-      <c r="B17" s="16"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="1">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3">
-        <v>4.5224030226177498E-4</v>
-      </c>
-      <c r="E17" s="22"/>
+        <v>2.8178603662805399E-3</v>
+      </c>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="18"/>
-      <c r="B18" s="16"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="1">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D18" s="3">
-        <v>3.25042909349475E-4</v>
-      </c>
-      <c r="E18" s="22"/>
+        <v>2.9661436358707099E-3</v>
+      </c>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="18"/>
-      <c r="B19" s="16"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="1">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D19" s="3">
-        <v>5.4759582523591596E-4</v>
-      </c>
-      <c r="E19" s="22"/>
+        <v>2.8796542855546998E-3</v>
+      </c>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
-      <c r="B20" s="16"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="1">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D20" s="3">
-        <v>4.0296400000000003E-5</v>
-      </c>
-      <c r="E20" s="22"/>
+        <v>2.8219944771796799E-3</v>
+      </c>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="18"/>
-      <c r="B21" s="16"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D21" s="3">
-        <v>8.9001901515576199E-4</v>
-      </c>
-      <c r="E21" s="22"/>
+        <v>2.7957880955958498E-3</v>
+      </c>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="16"/>
+      <c r="A22" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
       <c r="C22" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3">
-        <v>8.6876944325313898E-4</v>
-      </c>
-      <c r="E22" s="22"/>
+        <v>2.4381599990933901E-3</v>
+      </c>
+      <c r="E22" s="19">
+        <f>AVERAGE(D22:D41)</f>
+        <v>2.6316297362044268E-3</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
-      <c r="B23" s="17"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D23" s="3">
-        <v>5.9022203911008697E-4</v>
-      </c>
-      <c r="E23" s="23"/>
+        <v>2.6282434237133502E-3</v>
+      </c>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="18"/>
-      <c r="B24" s="18" t="s">
-        <v>8</v>
-      </c>
+      <c r="B24" s="18"/>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="3">
-        <v>1.73793482370665E-4</v>
-      </c>
-      <c r="E24" s="19">
-        <f>AVERAGE(D24:D33)</f>
-        <v>2.0032376576300951E-4</v>
-      </c>
+        <v>2.3461147455381701E-3</v>
+      </c>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="3">
-        <v>4.4079599999999997E-5</v>
-      </c>
-      <c r="E25" s="18"/>
+        <v>2.7524372879068298E-3</v>
+      </c>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="18"/>
       <c r="B26" s="18"/>
       <c r="C26" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="3">
-        <v>1.9820721733818201E-4</v>
-      </c>
-      <c r="E26" s="18"/>
+        <v>3.2472745789499402E-3</v>
+      </c>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D27" s="3">
-        <v>2.6898882604876098E-4</v>
-      </c>
-      <c r="E27" s="18"/>
+        <v>2.5237854282296E-3</v>
+      </c>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>9.9348000000000002E-6</v>
-      </c>
-      <c r="E28" s="18"/>
+        <v>2.9887873260404599E-3</v>
+      </c>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3">
-        <v>1.70899292234211E-4</v>
-      </c>
-      <c r="E29" s="18"/>
+        <v>2.06526349558706E-3</v>
+      </c>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="18"/>
       <c r="B30" s="18"/>
       <c r="C30" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" s="3">
-        <v>3.7644454634369102E-4</v>
-      </c>
-      <c r="E30" s="18"/>
+        <v>2.6816447983030599E-3</v>
+      </c>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="18"/>
       <c r="B31" s="18"/>
       <c r="C31" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3">
-        <v>7.5758852866904895E-5</v>
-      </c>
-      <c r="E31" s="18"/>
+        <v>2.7565596821078398E-3</v>
+      </c>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3">
-        <v>4.9271851899704603E-4</v>
-      </c>
-      <c r="E32" s="18"/>
+        <v>2.7553046452244798E-3</v>
+      </c>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>3.1897007707068202E-3</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2.35548027007934E-3</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2.8436489535965501E-3</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1.70148443487083E-3</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2.7788672642603202E-3</v>
+      </c>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3">
+        <v>3.0725315266457E-3</v>
+      </c>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1.8539865245109999E-3</v>
+      </c>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.76319371832273E-3</v>
+      </c>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2.8901258504010598E-3</v>
+      </c>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>3.3099004965032601E-3</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>2.468410738941349E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>2.0223762558382102E-3</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>2.48460504443907E-3</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2.1925517311301699E-3</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2.0210547846704601E-3</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2.32727791187156E-3</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>3.3527282363668498E-3</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.00939520752292E-3</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2.9226176336739399E-3</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="3">
-        <v>1.9241252143063401E-4</v>
-      </c>
-      <c r="E33" s="18"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+      <c r="D51" s="3">
+        <v>2.3055594287943698E-3</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3">
+        <v>3.2286986322523502E-3</v>
+      </c>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3">
+        <v>2.0678913756985401E-3</v>
+      </c>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1.97292007963753E-3</v>
+      </c>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3">
+        <v>1.8995918992215899E-3</v>
+      </c>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2.29849091136575E-3</v>
+      </c>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3">
+        <v>2.1367533734444602E-3</v>
+      </c>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3">
+        <v>2.2416139375018599E-3</v>
+      </c>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3">
+        <v>3.14845189446259E-3</v>
+      </c>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3">
+        <v>2.4563851126431602E-3</v>
+      </c>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3">
+        <v>2.96935083178834E-3</v>
+      </c>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1.3327355283255899E-3</v>
+      </c>
+      <c r="E62" s="19">
+        <f>AVERAGE(D62:D81)</f>
+        <v>1.3327355283255899E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="E13:E23"/>
+  <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C042F672-E41D-468F-9A40-AB573A878B0F}">
-  <dimension ref="A1:G42"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6838073C-3256-4ACB-AEB2-32BAE33D808A}">
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="4"/>
     <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
@@ -7530,18 +11145,20 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3">
+        <v>3.0401932235441099E-3</v>
+      </c>
       <c r="E2" s="19">
-        <f>AVERAGE(D2:D15)</f>
-        <v>1.4591194330376932E-3</v>
+        <f>AVERAGE(D2:D21)</f>
+        <v>3.0380547293692235E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7550,10 +11167,10 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="7">
-        <v>1.5217850441141701E-3</v>
-      </c>
-      <c r="E3" s="18"/>
+      <c r="D3" s="3">
+        <v>3.0331384444736401E-3</v>
+      </c>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="18"/>
@@ -7561,10 +11178,10 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="7">
-        <v>1.4187702239963399E-3</v>
-      </c>
-      <c r="E4" s="18"/>
+      <c r="D4" s="3">
+        <v>3.1182764735492199E-3</v>
+      </c>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="18"/>
@@ -7572,8 +11189,10 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="18"/>
+      <c r="D5" s="3">
+        <v>3.0154031793589E-3</v>
+      </c>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="18"/>
@@ -7581,8 +11200,10 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="18"/>
+      <c r="D6" s="3">
+        <v>3.0645263646368699E-3</v>
+      </c>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="18"/>
@@ -7590,10 +11211,10 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="7">
-        <v>1.5994412310248701E-3</v>
-      </c>
-      <c r="E7" s="18"/>
+      <c r="D7" s="3">
+        <v>3.0189844430268402E-3</v>
+      </c>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="18"/>
@@ -7601,10 +11222,10 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="7">
-        <v>1.3964272541872899E-3</v>
-      </c>
-      <c r="E8" s="18"/>
+      <c r="D8" s="3">
+        <v>3.0527009145820002E-3</v>
+      </c>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -7612,10 +11233,10 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="7">
-        <v>1.5234914987065399E-3</v>
-      </c>
-      <c r="E9" s="18"/>
+      <c r="D9" s="3">
+        <v>3.0699752859798999E-3</v>
+      </c>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
@@ -7623,8 +11244,10 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="18"/>
+      <c r="D10" s="3">
+        <v>3.0743395526040499E-3</v>
+      </c>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="18"/>
@@ -7632,485 +11255,10 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="7">
-        <v>1.29480134619695E-3</v>
-      </c>
-      <c r="E11" s="18"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="18"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="18"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="18"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="1">
-        <v>11</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="18"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="21">
-        <f>AVERAGE(D16:D26)</f>
-        <v>6.4932430621342815E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="1">
-        <v>2</v>
-      </c>
-      <c r="D17" s="7">
-        <v>5.46025356640438E-4</v>
-      </c>
-      <c r="E17" s="22"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="1">
-        <v>3</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="22"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="1">
-        <v>4</v>
-      </c>
-      <c r="D19" s="7">
-        <v>4.5331415788522699E-4</v>
-      </c>
-      <c r="E19" s="22"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="1">
-        <v>5</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="22"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="1">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="22"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="1">
-        <v>7</v>
-      </c>
-      <c r="D22" s="7">
-        <v>5.4759582523591596E-4</v>
-      </c>
-      <c r="E22" s="22"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="1">
-        <v>8</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="22"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="1">
-        <v>9</v>
-      </c>
-      <c r="D24" s="7">
-        <v>8.9001901515576199E-4</v>
-      </c>
-      <c r="E24" s="22"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="18"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="1">
-        <v>10</v>
-      </c>
-      <c r="D25" s="7">
-        <v>8.6876944325313898E-4</v>
-      </c>
-      <c r="E25" s="22"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="18"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="1">
-        <v>11</v>
-      </c>
-      <c r="D26" s="7">
-        <v>5.9022203911008697E-4</v>
-      </c>
-      <c r="E26" s="23"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="6">
-        <v>1.73793482370665E-4</v>
-      </c>
-      <c r="E27" s="19">
-        <f>AVERAGE(D27:D40)</f>
-        <v>2.1330410891497666E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="1">
-        <v>2</v>
-      </c>
-      <c r="D28" s="3">
-        <v>4.4079599999999997E-5</v>
-      </c>
-      <c r="E28" s="18"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="1">
-        <v>3</v>
-      </c>
-      <c r="D29" s="6">
-        <v>1.9820721733818201E-4</v>
-      </c>
-      <c r="E29" s="18"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="1">
-        <v>4</v>
-      </c>
-      <c r="D30" s="3">
-        <v>2.6898882604876098E-4</v>
-      </c>
-      <c r="E30" s="18"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="1">
-        <v>5</v>
-      </c>
-      <c r="D31" s="3">
-        <v>9.9348000000000002E-6</v>
-      </c>
-      <c r="E31" s="18"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="1">
-        <v>6</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1.70899292234211E-4</v>
-      </c>
-      <c r="E32" s="18"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="1">
-        <v>7</v>
-      </c>
-      <c r="D33" s="3">
-        <v>3.7644454634369102E-4</v>
-      </c>
-      <c r="E33" s="18"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="1">
-        <v>8</v>
-      </c>
-      <c r="D34" s="3">
-        <v>7.5758852866904895E-5</v>
-      </c>
-      <c r="E34" s="18"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="1">
-        <v>9</v>
-      </c>
-      <c r="D35" s="3">
-        <v>4.9271851899704603E-4</v>
-      </c>
-      <c r="E35" s="18"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="1">
-        <v>10</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1.9241252143063401E-4</v>
-      </c>
-      <c r="E36" s="18"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="1">
-        <v>11</v>
-      </c>
-      <c r="D37" s="3">
-        <v>3.3565148161274601E-4</v>
-      </c>
-      <c r="E37" s="18"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="1">
-        <v>12</v>
-      </c>
-      <c r="D38" s="6">
-        <v>1.2738871373007399E-4</v>
-      </c>
-      <c r="E38" s="18"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="1">
-        <v>13</v>
-      </c>
-      <c r="D39" s="3">
-        <v>3.4164426510307702E-4</v>
-      </c>
-      <c r="E39" s="18"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="1">
-        <v>14</v>
-      </c>
-      <c r="D40" s="6">
-        <v>1.78335406733681E-4</v>
-      </c>
-      <c r="E40" s="18"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A2:A40"/>
-    <mergeCell ref="B2:B15"/>
-    <mergeCell ref="E2:E15"/>
-    <mergeCell ref="B16:B26"/>
-    <mergeCell ref="E16:E26"/>
-    <mergeCell ref="B27:B40"/>
-    <mergeCell ref="E27:E40"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>6.8494550335423199E-3</v>
-      </c>
-      <c r="E2" s="19">
-        <f>AVERAGE(D2:D12)</f>
-        <v>7.2093580443383567E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3">
-        <v>7.7222014481316001E-3</v>
-      </c>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>7.4276032951078701E-3</v>
-      </c>
-      <c r="E4" s="18"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6.9163642363323698E-3</v>
-      </c>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>7.1247468487415202E-3</v>
-      </c>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>7.9683523176790998E-3</v>
-      </c>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
-        <v>7.1325304703669396E-3</v>
-      </c>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="1">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>7.6723666731501597E-3</v>
-      </c>
-      <c r="E9" s="18"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6.44864466466859E-3</v>
-      </c>
-      <c r="E10" s="18"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="1">
-        <v>10</v>
-      </c>
       <c r="D11" s="3">
-        <v>7.1998086663083299E-3</v>
-      </c>
-      <c r="E11" s="18"/>
+        <v>3.0387621275461199E-3</v>
+      </c>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="18"/>
@@ -8119,270 +11267,744 @@
         <v>11</v>
       </c>
       <c r="D12" s="3">
-        <v>6.8408648336931201E-3</v>
-      </c>
-      <c r="E12" s="18"/>
+        <v>2.9463407000412901E-3</v>
+      </c>
+      <c r="E12" s="19"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="18"/>
-      <c r="B13" s="18" t="s">
-        <v>7</v>
-      </c>
+      <c r="B13" s="18"/>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D13" s="3">
-        <v>4.4059430113216501E-3</v>
-      </c>
-      <c r="E13" s="19">
-        <f>AVERAGE(D13:D23)</f>
-        <v>5.6171193080640424E-3</v>
-      </c>
+        <v>3.00094837317991E-3</v>
+      </c>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D14" s="3">
-        <v>6.0285373262784596E-3</v>
-      </c>
-      <c r="E14" s="18"/>
+        <v>3.0249392886697898E-3</v>
+      </c>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="1">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3">
-        <v>4.6542086132795998E-3</v>
-      </c>
-      <c r="E15" s="18"/>
+        <v>3.02556291647119E-3</v>
+      </c>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D16" s="3">
-        <v>5.4842343524997596E-3</v>
-      </c>
-      <c r="E16" s="18"/>
+        <v>3.0467296528745298E-3</v>
+      </c>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="1">
-        <v>5</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5.2386490268761304E-3</v>
-      </c>
-      <c r="E17" s="18"/>
+        <v>16</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="1">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3">
-        <v>4.5414210107642796E-3</v>
-      </c>
-      <c r="E18" s="18"/>
+        <v>17</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="18"/>
       <c r="B19" s="18"/>
       <c r="C19" s="1">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3">
-        <v>6.4272965329950603E-3</v>
-      </c>
-      <c r="E19" s="18"/>
+        <v>18</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
       <c r="B20" s="18"/>
       <c r="C20" s="1">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>3.38376634582825E-3</v>
-      </c>
-      <c r="E20" s="18"/>
+        <v>19</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="1">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3">
-        <v>7.5523987537550697E-3</v>
-      </c>
-      <c r="E21" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
+      <c r="A22" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>14</v>
+      </c>
       <c r="C22" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3">
-        <v>7.6800340233492996E-3</v>
-      </c>
-      <c r="E22" s="18"/>
+        <v>2.56045791222035E-3</v>
+      </c>
+      <c r="E22" s="19">
+        <f>AVERAGE(D22:D41)</f>
+        <v>2.5566700516496286E-3</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="1">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D23" s="3">
-        <v>6.3918233917569199E-3</v>
-      </c>
-      <c r="E23" s="18"/>
+        <v>2.4897869931685599E-3</v>
+      </c>
+      <c r="E23" s="19"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="18"/>
-      <c r="B24" s="18" t="s">
-        <v>8</v>
-      </c>
+      <c r="B24" s="18"/>
       <c r="C24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="3">
-        <v>6.8834568210915997E-3</v>
-      </c>
-      <c r="E24" s="19">
-        <f>AVERAGE(D24:D33)</f>
-        <v>4.7018859667192891E-3</v>
-      </c>
+        <v>2.56563837271321E-3</v>
+      </c>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="3">
-        <v>5.9727451086721804E-3</v>
-      </c>
-      <c r="E25" s="18"/>
+        <v>2.8058455741671001E-3</v>
+      </c>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="18"/>
       <c r="B26" s="18"/>
       <c r="C26" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="3">
-        <v>3.2861956035523401E-3</v>
-      </c>
-      <c r="E26" s="18"/>
+        <v>2.5955966653407E-3</v>
+      </c>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D27" s="3">
-        <v>4.1621944755989501E-3</v>
-      </c>
-      <c r="E27" s="18"/>
+        <v>2.6488434196267801E-3</v>
+      </c>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="18"/>
       <c r="C28" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" s="3">
-        <v>6.0968354981954303E-3</v>
-      </c>
-      <c r="E28" s="18"/>
+        <v>2.9603660335354798E-3</v>
+      </c>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="18"/>
       <c r="B29" s="18"/>
       <c r="C29" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3">
-        <v>6.8318852941438796E-3</v>
-      </c>
-      <c r="E29" s="18"/>
+        <v>2.4719477074411599E-3</v>
+      </c>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="18"/>
       <c r="B30" s="18"/>
       <c r="C30" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D30" s="3">
-        <v>3.3675964367588002E-3</v>
-      </c>
-      <c r="E30" s="18"/>
+        <v>2.3577404238525799E-3</v>
+      </c>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="18"/>
       <c r="B31" s="18"/>
       <c r="C31" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" s="3">
-        <v>2.7372032922601602E-3</v>
-      </c>
-      <c r="E31" s="18"/>
+        <v>2.5214018330325799E-3</v>
+      </c>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="18"/>
       <c r="B32" s="18"/>
       <c r="C32" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3">
-        <v>4.0609534836609498E-3</v>
-      </c>
-      <c r="E32" s="18"/>
+        <v>2.1215953440929698E-3</v>
+      </c>
+      <c r="E32" s="19"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="1">
+        <v>12</v>
+      </c>
+      <c r="D33" s="3">
+        <v>2.4312839018629301E-3</v>
+      </c>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="1">
+        <v>13</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2.5250084896155998E-3</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="1">
+        <v>14</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2.9121704531619602E-3</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2.38236765091248E-3</v>
+      </c>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="1">
+        <v>16</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="1">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="19"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="1">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="19"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="1">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="19"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="1">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="19"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2.0622498441260802E-3</v>
+      </c>
+      <c r="E42" s="19">
+        <f>AVERAGE(D42:D61)</f>
+        <v>2.3188578817489917E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="1">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3">
+        <v>2.3794685929811499E-3</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="3">
+        <v>2.2977682884525799E-3</v>
+      </c>
+      <c r="E44" s="19"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2.4343621971597198E-3</v>
+      </c>
+      <c r="E45" s="19"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3">
+        <v>2.1108189144734301E-3</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="1">
+        <v>6</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2.3621231197317998E-3</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="1">
+        <v>7</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2.4698851227879198E-3</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="1">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.47827370439321E-3</v>
+      </c>
+      <c r="E49" s="19"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3">
+        <v>2.3045136598095501E-3</v>
+      </c>
+      <c r="E50" s="19"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="3">
-        <v>3.6197936532585901E-3</v>
-      </c>
-      <c r="E33" s="18"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+      <c r="D51" s="3">
+        <v>2.2891153735744799E-3</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="1">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="1">
+        <v>12</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="1">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1">
+        <v>14</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="19"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="1">
+        <v>16</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="19"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="1">
+        <v>19</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="19"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="19"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="1">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3">
+        <v>2.40624284469741E-3</v>
+      </c>
+      <c r="E62" s="19">
+        <f>AVERAGE(D62:D81)</f>
+        <v>2.7249731492351528E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3">
+        <v>2.6630340728757999E-3</v>
+      </c>
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="1">
+        <v>3</v>
+      </c>
+      <c r="D64" s="3">
+        <v>3.1983295497875499E-3</v>
+      </c>
+      <c r="E64" s="19"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="1">
+        <v>4</v>
+      </c>
+      <c r="D65" s="3">
+        <v>2.7626672876672701E-3</v>
+      </c>
+      <c r="E65" s="19"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="1">
         <v>5</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+      <c r="D66" s="3">
+        <v>2.7638149916049798E-3</v>
+      </c>
+      <c r="E66" s="19"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="1">
+        <v>6</v>
+      </c>
+      <c r="D67" s="3">
+        <v>2.3583828748001199E-3</v>
+      </c>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="1">
+        <v>7</v>
+      </c>
+      <c r="D68" s="3">
+        <v>2.6027344446575501E-3</v>
+      </c>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="1">
+        <v>8</v>
+      </c>
+      <c r="D69" s="3">
+        <v>2.0609721425198001E-3</v>
+      </c>
+      <c r="E69" s="19"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="1">
+        <v>9</v>
+      </c>
+      <c r="D70" s="3">
+        <v>3.18934603992996E-3</v>
+      </c>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1">
+        <v>10</v>
+      </c>
+      <c r="D71" s="3">
+        <v>3.2442072438110901E-3</v>
+      </c>
+      <c r="E71" s="19"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="1">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="19"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="1">
+        <v>12</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="19"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="1">
+        <v>13</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="19"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="1">
+        <v>14</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="19"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="1">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="19"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="1">
+        <v>16</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="19"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="1">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="19"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="1">
+        <v>18</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="1">
+        <v>19</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="19"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="1">
+        <v>20</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B13:B23"/>
-    <mergeCell ref="E13:E23"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
+  <mergeCells count="12">
+    <mergeCell ref="A42:A61"/>
+    <mergeCell ref="B42:B61"/>
+    <mergeCell ref="E42:E61"/>
+    <mergeCell ref="A62:A81"/>
+    <mergeCell ref="B62:B81"/>
+    <mergeCell ref="E62:E81"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B21"/>
+    <mergeCell ref="E2:E21"/>
+    <mergeCell ref="A22:A41"/>
+    <mergeCell ref="B22:B41"/>
+    <mergeCell ref="E22:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
